--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756F3C92-69DA-4D8C-975D-5045B4442899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0588020A-651C-4EC9-BAE3-E46E48F9262C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="PHDNS T Kuala Pilah" sheetId="3" r:id="rId1"/>
@@ -216,10 +216,10 @@
     <t>https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing, https://drive.google.com/file/d/1LCdVC9g6WdQAOnPWE3zziD8GZEntiu9c/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing, https://drive.google.com/file/d/1TQnvMWjzdHqR-nEcwRLF9-ZGftC8Atpf/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -937,7 +937,7 @@
         <v>51</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
@@ -1089,7 +1089,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
@@ -1155,7 +1155,7 @@
     <hyperlink ref="G5" r:id="rId6" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{EA2C3863-D60F-41EB-AB6A-AA5F0ABFC2D9}"/>
     <hyperlink ref="G9" r:id="rId7" xr:uid="{582FD441-A415-407B-A2C2-3C7802A01407}"/>
     <hyperlink ref="G11" r:id="rId8" xr:uid="{2B85E27F-B7DA-493E-B4CB-31C52D8BB58F}"/>
-    <hyperlink ref="G13" r:id="rId9" xr:uid="{7FFA9277-00D6-468C-9219-E2D9E10B6DDF}"/>
+    <hyperlink ref="G13" r:id="rId9" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{7FFA9277-00D6-468C-9219-E2D9E10B6DDF}"/>
     <hyperlink ref="G7" r:id="rId10" xr:uid="{C8A72D82-9829-4481-9DBC-B809B2A67840}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0588020A-651C-4EC9-BAE3-E46E48F9262C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7C0BD4-9619-41AC-A10A-F933D22FC191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -210,9 +210,6 @@
     <t>https://drive.google.com/file/d/1CrucTqd84gbfVuo2rxZipDmqLKE7DS48/view?usp=sharing</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1R_raajVpCi7rzDTpoCcSJMrv35EYXkQ1/view?usp=sharing</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing</t>
   </si>
   <si>
@@ -220,6 +217,9 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing, https://drive.google.com/file/d/1TQnvMWjzdHqR-nEcwRLF9-ZGftC8Atpf/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1R_raajVpCi7rzDTpoCcSJMrv35EYXkQ1/view?usp=sharing, https://drive.google.com/file/d/1kgsZQKNF55vENr8uCvo4EJlcTyKG5ene/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -937,7 +937,7 @@
         <v>51</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
@@ -1013,7 +1013,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
@@ -1089,7 +1089,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
@@ -1153,7 +1153,7 @@
     <hyperlink ref="E12" r:id="rId4" xr:uid="{A3627ABE-8C59-41B0-9C05-F61764E8549C}"/>
     <hyperlink ref="E14" r:id="rId5" xr:uid="{6E7F3CB3-5CFD-4F03-891C-DD3A4D003B7F}"/>
     <hyperlink ref="G5" r:id="rId6" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{EA2C3863-D60F-41EB-AB6A-AA5F0ABFC2D9}"/>
-    <hyperlink ref="G9" r:id="rId7" xr:uid="{582FD441-A415-407B-A2C2-3C7802A01407}"/>
+    <hyperlink ref="G9" r:id="rId7" display="https://drive.google.com/file/d/1R_raajVpCi7rzDTpoCcSJMrv35EYXkQ1/view?usp=sharing" xr:uid="{582FD441-A415-407B-A2C2-3C7802A01407}"/>
     <hyperlink ref="G11" r:id="rId8" xr:uid="{2B85E27F-B7DA-493E-B4CB-31C52D8BB58F}"/>
     <hyperlink ref="G13" r:id="rId9" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{7FFA9277-00D6-468C-9219-E2D9E10B6DDF}"/>
     <hyperlink ref="G7" r:id="rId10" xr:uid="{C8A72D82-9829-4481-9DBC-B809B2A67840}"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7C0BD4-9619-41AC-A10A-F933D22FC191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1375DDDE-AE41-49C9-89A3-58FD16902BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -210,9 +210,6 @@
     <t>https://drive.google.com/file/d/1CrucTqd84gbfVuo2rxZipDmqLKE7DS48/view?usp=sharing</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing, https://drive.google.com/file/d/1LCdVC9g6WdQAOnPWE3zziD8GZEntiu9c/view?usp=sharing</t>
   </si>
   <si>
@@ -220,6 +217,9 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1R_raajVpCi7rzDTpoCcSJMrv35EYXkQ1/view?usp=sharing, https://drive.google.com/file/d/1kgsZQKNF55vENr8uCvo4EJlcTyKG5ene/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing, https://drive.google.com/file/d/1tFkHstrqcrYIA--j4YdF8aHvYdabDhFt/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -937,7 +937,7 @@
         <v>51</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
@@ -1013,7 +1013,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
@@ -1089,7 +1089,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
@@ -1154,7 +1154,7 @@
     <hyperlink ref="E14" r:id="rId5" xr:uid="{6E7F3CB3-5CFD-4F03-891C-DD3A4D003B7F}"/>
     <hyperlink ref="G5" r:id="rId6" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{EA2C3863-D60F-41EB-AB6A-AA5F0ABFC2D9}"/>
     <hyperlink ref="G9" r:id="rId7" display="https://drive.google.com/file/d/1R_raajVpCi7rzDTpoCcSJMrv35EYXkQ1/view?usp=sharing" xr:uid="{582FD441-A415-407B-A2C2-3C7802A01407}"/>
-    <hyperlink ref="G11" r:id="rId8" xr:uid="{2B85E27F-B7DA-493E-B4CB-31C52D8BB58F}"/>
+    <hyperlink ref="G11" r:id="rId8" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{2B85E27F-B7DA-493E-B4CB-31C52D8BB58F}"/>
     <hyperlink ref="G13" r:id="rId9" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{7FFA9277-00D6-468C-9219-E2D9E10B6DDF}"/>
     <hyperlink ref="G7" r:id="rId10" xr:uid="{C8A72D82-9829-4481-9DBC-B809B2A67840}"/>
   </hyperlinks>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,19 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6C43BE-9621-4EF0-AC8B-B08E84D2DC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5081FFEC-985D-43E2-880C-CAC5DF7245A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
     <sheet name="Pejabat Hutan" sheetId="3" r:id="rId2"/>
     <sheet name="Pusat Sitaan Gentam" sheetId="5" r:id="rId3"/>
+    <sheet name="Taman Negri Kenaboi" sheetId="12" r:id="rId4"/>
+    <sheet name="PD Forest" sheetId="13" r:id="rId5"/>
+    <sheet name="Kaunter Tiket" sheetId="14" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Pejabat Hutan'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Pejabat Hutan'!$A$1:$H$56</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negri Kenaboi'!$A$1:$G$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="85">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -234,6 +240,69 @@
   </si>
   <si>
     <t>Pusat Sitaan Gentam</t>
+  </si>
+  <si>
+    <t>PHDNSB</t>
+  </si>
+  <si>
+    <t>Pejabat Hutan Daerah Negeri Sembilan Barat</t>
+  </si>
+  <si>
+    <t>Seremban</t>
+  </si>
+  <si>
+    <t>Pejabat Renj Seremban</t>
+  </si>
+  <si>
+    <t>Gemencheh</t>
+  </si>
+  <si>
+    <t>Pejabat Renj Gemencheh</t>
+  </si>
+  <si>
+    <t>Seremban 2</t>
+  </si>
+  <si>
+    <t>Tampin</t>
+  </si>
+  <si>
+    <t>Taman Negeri Kenaboi</t>
+  </si>
+  <si>
+    <t>PD Forest</t>
+  </si>
+  <si>
+    <t>Port Dickson</t>
+  </si>
+  <si>
+    <t>Kenaboi</t>
+  </si>
+  <si>
+    <t>Jelebu</t>
+  </si>
+  <si>
+    <t>Kaunter Tiket Gunung Angsi</t>
+  </si>
+  <si>
+    <t>Bukit Putus</t>
+  </si>
+  <si>
+    <t>PHDNSU</t>
+  </si>
+  <si>
+    <t>Pejabat Hutan Daerah Negeri Sembilan Utara</t>
+  </si>
+  <si>
+    <t>Pejabat Renj Kuala Klawang</t>
+  </si>
+  <si>
+    <t>Pejabat Renj Simpang Pertang</t>
+  </si>
+  <si>
+    <t>Kuala Klawang</t>
+  </si>
+  <si>
+    <t>Simpang Pertang</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D54FEF-B8B0-455E-9719-4EECE694A16C}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -1660,7 +1729,7 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>17</v>
@@ -1696,7 +1765,7 @@
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>21</v>
@@ -1732,7 +1801,7 @@
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>21</v>
@@ -1768,7 +1837,7 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>24</v>
@@ -1802,10 +1871,670 @@
       <c r="G23" s="13"/>
       <c r="H23" s="5"/>
     </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="33"/>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="32"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="33"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="10">
+        <v>1</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H26" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="11"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="26"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="10">
+        <v>2</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="11"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="13"/>
+      <c r="H29" s="27"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>4</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="11"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" s="13"/>
+      <c r="H31" s="17"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>5</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="11"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="13"/>
+      <c r="H33" s="17"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>6</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="30"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="11"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="13"/>
+      <c r="H35" s="31"/>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>7</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="30"/>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="11"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="13"/>
+      <c r="H37" s="31"/>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>8</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="28"/>
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="11"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="13"/>
+      <c r="H39" s="29"/>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="33"/>
+    </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="32"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="33"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="10">
+        <v>1</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H42" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="11"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43" s="13"/>
+      <c r="H43" s="26"/>
+    </row>
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="10">
+        <v>2</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="11"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="13"/>
+      <c r="H45" s="27"/>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="10">
+        <v>4</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="11"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="13"/>
+      <c r="H47" s="17"/>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="10">
+        <v>5</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" s="27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="11"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="13"/>
+      <c r="H49" s="17"/>
+    </row>
+    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="10">
+        <v>6</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="30"/>
+    </row>
+    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="11"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="13"/>
+      <c r="H51" s="31"/>
+    </row>
+    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="10">
+        <v>7</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" s="30"/>
+    </row>
+    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="11"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="13"/>
+      <c r="H53" s="31"/>
+    </row>
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>8</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="28"/>
+    </row>
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="11"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="13"/>
+      <c r="H55" s="29"/>
+    </row>
   </sheetData>
-  <mergeCells count="62">
+  <mergeCells count="158">
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A40:H41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
     <mergeCell ref="H20:H21"/>
     <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A24:H25"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="D22:D23"/>
@@ -1882,12 +2611,34 @@
     <hyperlink ref="F19" r:id="rId12" xr:uid="{6156982A-9F67-4C39-B76A-A6002ED11587}"/>
     <hyperlink ref="F21" r:id="rId13" xr:uid="{AB7C8E70-FFD7-4DA2-9851-46F01C4C7FE9}"/>
     <hyperlink ref="F23" r:id="rId14" xr:uid="{C9F8004F-2006-467E-A196-CFC9352C9B68}"/>
+    <hyperlink ref="F27" r:id="rId15" xr:uid="{8A41AEDD-00D6-4798-BE58-4F607596CE5E}"/>
+    <hyperlink ref="F29" r:id="rId16" xr:uid="{62B78FFF-77DC-444D-90D0-1CA894377B57}"/>
+    <hyperlink ref="F31" r:id="rId17" xr:uid="{CB39D23E-1A2E-40EB-A68F-E8F7D4D0DC74}"/>
+    <hyperlink ref="F33" r:id="rId18" xr:uid="{663DF080-B326-4FD0-B69E-6E321D50216C}"/>
+    <hyperlink ref="H26" r:id="rId19" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{FB3E61E0-3CCB-44F1-B4A6-1AFE1F3CDF6F}"/>
+    <hyperlink ref="H30" r:id="rId20" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{766F845B-5791-46B9-A70C-900DBB353CB8}"/>
+    <hyperlink ref="H32" r:id="rId21" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{3B1F1F54-6E41-4B15-8C8B-3EFAD5BE0B2C}"/>
+    <hyperlink ref="H28" r:id="rId22" xr:uid="{12917566-A49D-451C-AE74-FF9FC1F43EF9}"/>
+    <hyperlink ref="F35" r:id="rId23" xr:uid="{E1BED91B-CAFE-4958-A8D4-FC59655467C6}"/>
+    <hyperlink ref="F37" r:id="rId24" xr:uid="{1988793E-9B89-4051-BF42-9A9BC2123B1F}"/>
+    <hyperlink ref="F39" r:id="rId25" xr:uid="{EF50FA91-35AE-4A95-B18B-E9A0DC2D867C}"/>
+    <hyperlink ref="F43" r:id="rId26" xr:uid="{00C82A6F-2C18-41D2-89AA-3C1C7095F3DC}"/>
+    <hyperlink ref="F45" r:id="rId27" xr:uid="{18FA63F7-AA33-4E60-A540-013BDF8F175E}"/>
+    <hyperlink ref="F47" r:id="rId28" xr:uid="{01447622-ADCD-4E8E-87E8-BDA8D1ADD1BF}"/>
+    <hyperlink ref="F49" r:id="rId29" xr:uid="{7136B4C8-E13F-412F-AD19-F4C4EE3C27A3}"/>
+    <hyperlink ref="H42" r:id="rId30" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{F63D11AF-4055-475B-BB25-6E5BFCF66740}"/>
+    <hyperlink ref="H46" r:id="rId31" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{84044B59-A767-4420-A6F8-CC0A7E9E718E}"/>
+    <hyperlink ref="H48" r:id="rId32" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{347BCBB6-C5EE-4148-88C5-C85C04A9BD1D}"/>
+    <hyperlink ref="H44" r:id="rId33" xr:uid="{D28BA95A-DCAF-4B84-A98A-CEA5DA6E2F09}"/>
+    <hyperlink ref="F51" r:id="rId34" xr:uid="{031E33FD-D835-47FF-B82E-B6EBE7FB15DD}"/>
+    <hyperlink ref="F53" r:id="rId35" xr:uid="{2F8B8258-D0AB-4F89-BE66-F01E10B039ED}"/>
+    <hyperlink ref="F55" r:id="rId36" xr:uid="{5D807F33-B9AD-4909-9D9B-0BAAFCAF8B82}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId15"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId37"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="9" max="7" man="1"/>
-    <brk id="15" max="4" man="1"/>
+    <brk id="15" max="7" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2080,4 +2831,574 @@
     <brk id="9" max="4" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FB98731-0E61-4137-ADA5-C08D15FE8083}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="63.28515625" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="50.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="47.42578125" style="2" customWidth="1"/>
+    <col min="8" max="12" width="9.5703125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="10">
+        <v>1</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="11"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10">
+        <v>2</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="11"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A3:G4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="9" max="4" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D41650E-8BFB-440F-9B08-19048F0F6751}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="63.28515625" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="50.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="47.42578125" style="2" customWidth="1"/>
+    <col min="8" max="12" width="9.5703125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="10">
+        <v>1</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="11"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10">
+        <v>2</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="11"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A3:G4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="9" max="4" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314B65D9-3D3B-4024-868B-A7B576C70DBC}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="63.28515625" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="50.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="47.42578125" style="2" customWidth="1"/>
+    <col min="8" max="12" width="9.5703125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="10">
+        <v>1</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="11"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10">
+        <v>2</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="11"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A3:G4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="9" max="4" man="1"/>
+  </rowBreaks>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5081FFEC-985D-43E2-880C-CAC5DF7245A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7655B3CC-76A3-4BB7-BD45-0F9A96A1B392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -21,12 +21,12 @@
     <sheet name="Kaunter Tiket" sheetId="14" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Pejabat Hutan'!$A$1:$H$56</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$G$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negri Kenaboi'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negri Kenaboi'!$A$1:$G$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="99">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -303,6 +303,48 @@
   </si>
   <si>
     <t>Simpang Pertang</t>
+  </si>
+  <si>
+    <t>Bangunan Kaunter Tiket</t>
+  </si>
+  <si>
+    <t>Blok Tandas</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q10</t>
+  </si>
+  <si>
+    <t>Blok Bangunan Utama</t>
+  </si>
+  <si>
+    <t>Blok Kafeteria</t>
+  </si>
+  <si>
+    <t>Blok Garaj</t>
+  </si>
+  <si>
+    <t>Blok Surau</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q11</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q12</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q13</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q14</t>
+  </si>
+  <si>
+    <t>Blok Kaunter Tiket</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q15</t>
+  </si>
+  <si>
+    <t>Blok Pejabat</t>
   </si>
 </sst>
 </file>
@@ -312,7 +354,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,6 +395,12 @@
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -468,7 +516,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -493,11 +541,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -505,19 +555,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -526,40 +567,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -568,7 +598,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -899,15 +941,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -915,13 +957,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -929,15 +971,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -945,13 +987,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -982,441 +1024,371 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="10">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="10">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+      <c r="A10" s="34">
         <v>3</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="21" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="17"/>
+      <c r="G11" s="21"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="10">
+      <c r="A12" s="16">
         <v>4</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="10">
+      <c r="A14" s="16">
         <v>5</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="11"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="13"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="18">
+      <c r="A16" s="34">
         <v>6</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="21" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
       <c r="F17" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="17"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="10">
+      <c r="A18" s="16">
         <v>7</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
       <c r="F19" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="17"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="10"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="12"/>
+      <c r="G20" s="14"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="13"/>
+      <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="10"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
       <c r="F22" s="8"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="13"/>
+      <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="10"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="17"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
       <c r="F25" s="6"/>
-      <c r="G25" s="17"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="10"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
       <c r="F27" s="6"/>
-      <c r="G27" s="13"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="10"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="14"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
       <c r="F29" s="6"/>
-      <c r="G29" s="13"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="10"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
       <c r="F30" s="8"/>
-      <c r="G30" s="17"/>
+      <c r="G30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
       <c r="F31" s="6"/>
-      <c r="G31" s="17"/>
+      <c r="G31" s="21"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="10"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
       <c r="F32" s="8"/>
-      <c r="G32" s="17"/>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
       <c r="F33" s="6"/>
-      <c r="G33" s="17"/>
+      <c r="G33" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A3:G4"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="E18:E19"/>
@@ -1433,6 +1405,76 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A3:G4"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D20:D21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
@@ -1460,54 +1502,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="24"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="31"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="24"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="33"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="25"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="29"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1538,945 +1580,999 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="26"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="27"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10">
+      <c r="A10" s="16">
         <v>3</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="27" t="s">
+      <c r="H10" s="20" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="17"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10">
+      <c r="A12" s="16">
         <v>4</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="H12" s="20" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="17"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="21"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="10">
+      <c r="A14" s="16">
         <v>5</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="27" t="s">
+      <c r="H14" s="20" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="17"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="21"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="10">
+      <c r="A16" s="16">
         <v>6</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="30"/>
+      <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
       <c r="F17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="31"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10">
+      <c r="A18" s="16">
         <v>7</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="30"/>
+      <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
       <c r="F19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="31"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="11"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="10">
+      <c r="A20" s="16">
         <v>8</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="28"/>
+      <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
       <c r="F21" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="29"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="13"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10">
+      <c r="A22" s="16">
         <v>9</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="14" t="s">
         <v>14</v>
       </c>
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
       <c r="F23" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="13"/>
+      <c r="G23" s="15"/>
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="33"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="25"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="33"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="25"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10">
+      <c r="A26" s="16">
         <v>1</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H26" s="25" t="s">
+      <c r="H26" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
       <c r="F27" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="26"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="10">
+      <c r="A28" s="16">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="27" t="s">
+      <c r="H28" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
       <c r="F29" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="13"/>
-      <c r="H29" s="27"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="20"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="10">
+      <c r="A30" s="16">
         <v>4</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="27" t="s">
+      <c r="H30" s="20" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
       <c r="F31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="13"/>
-      <c r="H31" s="17"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="10">
+      <c r="A32" s="16">
         <v>5</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="27" t="s">
+      <c r="H32" s="20" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
       <c r="F33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="13"/>
-      <c r="H33" s="17"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="21"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="10">
+      <c r="A34" s="16">
         <v>6</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="30"/>
+      <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
       <c r="F35" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="13"/>
-      <c r="H35" s="31"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="11"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="10">
+      <c r="A36" s="16">
         <v>7</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="30"/>
+      <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
       <c r="F37" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G37" s="13"/>
-      <c r="H37" s="31"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="11"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="10">
+      <c r="A38" s="16">
         <v>8</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="12" t="s">
+      <c r="G38" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H38" s="28"/>
+      <c r="H38" s="12"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
       <c r="F39" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G39" s="13"/>
-      <c r="H39" s="29"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="13"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="33"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="25"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="32"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="33"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="25"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="10">
+      <c r="A42" s="16">
         <v>1</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H42" s="25" t="s">
+      <c r="H42" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
       <c r="F43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G43" s="13"/>
-      <c r="H43" s="26"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="27"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="10">
+      <c r="A44" s="16">
         <v>2</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G44" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H44" s="27" t="s">
+      <c r="H44" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="11"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
       <c r="F45" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G45" s="13"/>
-      <c r="H45" s="27"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="20"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="10">
+      <c r="A46" s="16">
         <v>4</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="27" t="s">
+      <c r="H46" s="20" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="11"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
       <c r="F47" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G47" s="13"/>
-      <c r="H47" s="17"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="21"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="10">
+      <c r="A48" s="16">
         <v>5</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="12" t="s">
+      <c r="G48" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H48" s="27" t="s">
+      <c r="H48" s="20" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="11"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
       <c r="F49" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="13"/>
-      <c r="H49" s="17"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="21"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="10">
+      <c r="A50" s="16">
         <v>6</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G50" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H50" s="30"/>
+      <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="11"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
       <c r="F51" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G51" s="13"/>
-      <c r="H51" s="31"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="11"/>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="10">
+      <c r="A52" s="16">
         <v>7</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H52" s="30"/>
+      <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="11"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
       <c r="F53" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G53" s="13"/>
-      <c r="H53" s="31"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="11"/>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="10">
+      <c r="A54" s="16">
         <v>8</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H54" s="28"/>
+      <c r="H54" s="12"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="11"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
       <c r="F55" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G55" s="13"/>
-      <c r="H55" s="29"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="158">
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A24:H25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
     <mergeCell ref="A40:H41"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="B42:B43"/>
@@ -2501,100 +2597,46 @@
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="A24:H25"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="E52:E53"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{F0642C37-FB2E-4AFF-A3EE-AC391134171B}"/>
@@ -2658,15 +2700,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2674,13 +2716,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2688,15 +2730,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2704,13 +2746,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2741,72 +2783,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2835,7 +2877,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FB98731-0E61-4137-ADA5-C08D15FE8083}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -2848,15 +2890,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2864,13 +2906,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2878,15 +2920,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2894,13 +2936,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2931,80 +2973,315 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="15"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="16">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="17"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="15"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="16">
+        <v>4</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="15"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="16">
+        <v>5</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="15"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="16">
+        <v>6</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="17"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="15"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="16">
+        <v>7</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="17"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="15"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="16">
+        <v>8</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="17"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
+  <mergeCells count="50">
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3014,18 +3291,21 @@
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="9" max="4" man="1"/>
-  </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D41650E-8BFB-440F-9B08-19048F0F6751}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -3038,15 +3318,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3054,13 +3334,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3068,15 +3348,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3084,13 +3364,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3121,80 +3401,195 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="15"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="16">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="17"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="15"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="16">
+        <v>4</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="15"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="16">
+        <v>5</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
+  <mergeCells count="32">
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3204,7 +3599,13 @@
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
@@ -3215,7 +3616,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314B65D9-3D3B-4024-868B-A7B576C70DBC}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -3228,15 +3629,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3244,13 +3645,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3258,15 +3659,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3274,13 +3675,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3311,80 +3712,115 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="15"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="16">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="17"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
+  <mergeCells count="20">
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3394,11 +3830,14 @@
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="9" max="4" man="1"/>
-  </rowBreaks>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7655B3CC-76A3-4BB7-BD45-0F9A96A1B392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5588056A-DAF2-40C5-AED3-6464F6C80528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
     <sheet name="Pejabat Hutan" sheetId="3" r:id="rId2"/>
     <sheet name="Pusat Sitaan Gentam" sheetId="5" r:id="rId3"/>
-    <sheet name="Taman Negri Kenaboi" sheetId="12" r:id="rId4"/>
+    <sheet name="Taman Negeri Kenaboi" sheetId="12" r:id="rId4"/>
     <sheet name="PD Forest" sheetId="13" r:id="rId5"/>
     <sheet name="Kaunter Tiket" sheetId="14" r:id="rId6"/>
   </sheets>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Pejabat Hutan'!$A$1:$H$56</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$G$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negri Kenaboi'!$A$1:$G$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negeri Kenaboi'!$A$1:$G$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5588056A-DAF2-40C5-AED3-6464F6C80528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8361B899-A0D1-4DCD-962A-0605E3559EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
-    <sheet name="Pejabat Hutan" sheetId="3" r:id="rId2"/>
+    <sheet name="Pejabat" sheetId="3" r:id="rId2"/>
     <sheet name="Pusat Sitaan Gentam" sheetId="5" r:id="rId3"/>
     <sheet name="Taman Negeri Kenaboi" sheetId="12" r:id="rId4"/>
     <sheet name="PD Forest" sheetId="13" r:id="rId5"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$G$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Pejabat Hutan'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$56</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$G$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negeri Kenaboi'!$A$1:$G$23</definedName>
@@ -544,12 +544,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -567,12 +561,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -580,27 +568,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -609,8 +588,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -941,15 +941,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -957,13 +957,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -971,15 +971,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -987,13 +987,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -1024,371 +1024,441 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
       <c r="F9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="34">
+      <c r="A10" s="24">
         <v>3</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="23" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="34"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
       <c r="F11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="21"/>
+      <c r="G11" s="23"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+      <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
       <c r="F13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
       <c r="F15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="13"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="34">
+      <c r="A16" s="24">
         <v>6</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="23" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="34"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
       <c r="F17" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="21"/>
+      <c r="G17" s="23"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="16">
+      <c r="A18" s="14">
         <v>7</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="23" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
       <c r="F19" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="21"/>
+      <c r="G19" s="23"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="16"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="14"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="15"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="16"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
       <c r="F22" s="8"/>
-      <c r="G22" s="14"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="15"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="16"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="21"/>
+      <c r="G24" s="23"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="17"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
       <c r="F25" s="6"/>
-      <c r="G25" s="21"/>
+      <c r="G25" s="23"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="16"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="14"/>
+      <c r="G26" s="12"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
       <c r="F27" s="6"/>
-      <c r="G27" s="15"/>
+      <c r="G27" s="13"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="16"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="14"/>
+      <c r="G28" s="12"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="17"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
       <c r="F29" s="6"/>
-      <c r="G29" s="15"/>
+      <c r="G29" s="13"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="16"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
       <c r="F30" s="8"/>
-      <c r="G30" s="21"/>
+      <c r="G30" s="23"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="17"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
       <c r="F31" s="6"/>
-      <c r="G31" s="21"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="16"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
       <c r="F32" s="8"/>
-      <c r="G32" s="21"/>
+      <c r="G32" s="23"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="17"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
       <c r="F33" s="6"/>
-      <c r="G33" s="21"/>
+      <c r="G33" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="86">
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A3:G4"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="E18:E19"/>
@@ -1405,76 +1475,6 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A3:G4"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D20:D21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
@@ -1502,54 +1502,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="31"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="30"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="30"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="29"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="34"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1580,905 +1580,1039 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="28" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="27"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="27" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
       <c r="F9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="20"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="27" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
       <c r="F11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="21"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="23"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+      <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="27" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
       <c r="F13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="21"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="23"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="27" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
       <c r="F15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="21"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16">
+      <c r="A16" s="14">
         <v>6</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="12" t="s">
         <v>13</v>
       </c>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
       <c r="F17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="15"/>
+      <c r="G17" s="13"/>
       <c r="H17" s="11"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16">
+      <c r="A18" s="14">
         <v>7</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="12" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
       <c r="F19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="15"/>
+      <c r="G19" s="13"/>
       <c r="H19" s="11"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16">
+      <c r="A20" s="14">
         <v>8</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="12"/>
+      <c r="H20" s="31"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
       <c r="F21" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="32"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16">
+      <c r="A22" s="14">
         <v>9</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
       <c r="F23" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="13"/>
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="25"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="33"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="25"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="33"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16">
+      <c r="A26" s="14">
         <v>1</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="12" t="s">
         <v>64</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="H26" s="26" t="s">
+      <c r="H26" s="28" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
       <c r="F27" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="27"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="16">
+      <c r="A28" s="14">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="12" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G28" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="27" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="17"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
       <c r="F29" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="20"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="16">
+      <c r="A30" s="14">
         <v>4</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="12" t="s">
         <v>64</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="G30" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="20" t="s">
+      <c r="H30" s="27" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="17"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
       <c r="F31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="15"/>
-      <c r="H31" s="21"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="23"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="16">
+      <c r="A32" s="14">
         <v>5</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="12" t="s">
         <v>64</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="20" t="s">
+      <c r="H32" s="27" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="17"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
       <c r="F33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="15"/>
-      <c r="H33" s="21"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="23"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="16">
+      <c r="A34" s="14">
         <v>6</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="12" t="s">
         <v>64</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="G34" s="12" t="s">
         <v>13</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="17"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
       <c r="F35" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="15"/>
+      <c r="G35" s="13"/>
       <c r="H35" s="11"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="16">
+      <c r="A36" s="14">
         <v>7</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="12" t="s">
         <v>64</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="14" t="s">
+      <c r="G36" s="12" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="17"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
       <c r="F37" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G37" s="15"/>
+      <c r="G37" s="13"/>
       <c r="H37" s="11"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="16">
+      <c r="A38" s="14">
         <v>8</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="12" t="s">
         <v>64</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="14" t="s">
+      <c r="G38" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H38" s="12"/>
+      <c r="H38" s="31"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="17"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
       <c r="F39" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G39" s="15"/>
-      <c r="H39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="32"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="25"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="33"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="25"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="33"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="16">
+      <c r="A42" s="14">
         <v>1</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="14" t="s">
+      <c r="G42" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="H42" s="26" t="s">
+      <c r="H42" s="28" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="17"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
+      <c r="A43" s="15"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
       <c r="F43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G43" s="15"/>
-      <c r="H43" s="27"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="29"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="16">
+      <c r="A44" s="14">
         <v>2</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="14" t="s">
+      <c r="G44" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H44" s="20" t="s">
+      <c r="H44" s="27" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="17"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
+      <c r="A45" s="15"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
       <c r="F45" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G45" s="15"/>
-      <c r="H45" s="20"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="27"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="16">
+      <c r="A46" s="14">
         <v>4</v>
       </c>
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="20" t="s">
+      <c r="H46" s="27" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="17"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
+      <c r="A47" s="15"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
       <c r="F47" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G47" s="15"/>
-      <c r="H47" s="21"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="23"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="16">
+      <c r="A48" s="14">
         <v>5</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="22" t="s">
+      <c r="C48" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="14" t="s">
+      <c r="G48" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H48" s="20" t="s">
+      <c r="H48" s="27" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="17"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
       <c r="F49" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="15"/>
-      <c r="H49" s="21"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="23"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="16">
+      <c r="A50" s="14">
         <v>6</v>
       </c>
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="G50" s="12" t="s">
         <v>13</v>
       </c>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="17"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
       <c r="F51" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G51" s="15"/>
+      <c r="G51" s="13"/>
       <c r="H51" s="11"/>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="16">
+      <c r="A52" s="14">
         <v>7</v>
       </c>
-      <c r="B52" s="18" t="s">
+      <c r="B52" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G52" s="14" t="s">
+      <c r="G52" s="12" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="17"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
+      <c r="A53" s="15"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
       <c r="F53" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G53" s="15"/>
+      <c r="G53" s="13"/>
       <c r="H53" s="11"/>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="16">
+      <c r="A54" s="14">
         <v>8</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G54" s="14" t="s">
+      <c r="G54" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H54" s="12"/>
+      <c r="H54" s="31"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="17"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
+      <c r="A55" s="15"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
       <c r="F55" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G55" s="15"/>
-      <c r="H55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="158">
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A40:H41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A24:H25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D14:D15"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="H14:H15"/>
@@ -2503,140 +2637,6 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="A24:H25"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A40:H41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="E52:E53"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{F0642C37-FB2E-4AFF-A3EE-AC391134171B}"/>
@@ -2700,15 +2700,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2716,13 +2716,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2730,15 +2730,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2746,13 +2746,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2783,72 +2783,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2890,15 +2890,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2906,13 +2906,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2920,15 +2920,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2936,13 +2936,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2973,315 +2973,279 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
       <c r="F11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="13"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+      <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
       <c r="F13" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
       <c r="F15" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="13"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="16">
+      <c r="A16" s="14">
         <v>6</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
       <c r="F17" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="15"/>
+      <c r="G17" s="13"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="16">
+      <c r="A18" s="14">
         <v>7</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
       <c r="F19" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="15"/>
+      <c r="G19" s="13"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="16">
+      <c r="A20" s="14">
         <v>8</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
       <c r="F21" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="15"/>
+      <c r="G21" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3296,6 +3260,42 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3318,15 +3318,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3334,13 +3334,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3348,15 +3348,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3364,13 +3364,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3401,195 +3401,177 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
       <c r="F11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="13"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+      <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
       <c r="F13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
       <c r="F15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3604,6 +3586,24 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3629,15 +3629,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3645,13 +3645,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3659,15 +3659,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3675,13 +3675,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3712,115 +3712,109 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
       <c r="F11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3835,6 +3829,12 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8361B899-A0D1-4DCD-962A-0605E3559EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA09817-54E1-4920-AEC1-14C200EE274D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -19,9 +19,11 @@
     <sheet name="Taman Negeri Kenaboi" sheetId="12" r:id="rId4"/>
     <sheet name="PD Forest" sheetId="13" r:id="rId5"/>
     <sheet name="Kaunter Tiket" sheetId="14" r:id="rId6"/>
+    <sheet name="Kuarters" sheetId="15" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">Kuarters!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$56</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="99">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -544,6 +546,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -561,6 +569,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -568,19 +582,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -588,29 +605,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -941,15 +943,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -957,13 +959,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -971,15 +973,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -987,13 +989,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -1024,441 +1026,371 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="14">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="14">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="24">
+      <c r="A10" s="34">
         <v>3</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="21" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="23"/>
+      <c r="G11" s="21"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="14">
+      <c r="A12" s="16">
         <v>4</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="14">
+      <c r="A14" s="16">
         <v>5</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="13"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="24">
+      <c r="A16" s="34">
         <v>6</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="21" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="24"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
       <c r="F17" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="23"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="14">
+      <c r="A18" s="16">
         <v>7</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
       <c r="F19" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="23"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="12"/>
+      <c r="G20" s="14"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="13"/>
+      <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
       <c r="F22" s="8"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="13"/>
+      <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="14"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="23"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="15"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
       <c r="F25" s="6"/>
-      <c r="G25" s="23"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="14"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="15"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
       <c r="F27" s="6"/>
-      <c r="G27" s="13"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="14"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="14"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="15"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
       <c r="F29" s="6"/>
-      <c r="G29" s="13"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="14"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
       <c r="F30" s="8"/>
-      <c r="G30" s="23"/>
+      <c r="G30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="15"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
       <c r="F31" s="6"/>
-      <c r="G31" s="23"/>
+      <c r="G31" s="21"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="14"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
       <c r="F32" s="8"/>
-      <c r="G32" s="23"/>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
       <c r="F33" s="6"/>
-      <c r="G33" s="23"/>
+      <c r="G33" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A3:G4"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="E18:E19"/>
@@ -1475,6 +1407,76 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A3:G4"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D20:D21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
@@ -1502,54 +1504,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="30"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="33"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="25"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="34"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="29"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1580,945 +1582,999 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="29"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="27"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14">
+      <c r="A10" s="16">
         <v>3</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="27" t="s">
+      <c r="H10" s="20" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="15"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="23"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="14">
+      <c r="A12" s="16">
         <v>4</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="H12" s="20" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="23"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="21"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14">
+      <c r="A14" s="16">
         <v>5</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="27" t="s">
+      <c r="H14" s="20" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="23"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="21"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14">
+      <c r="A16" s="16">
         <v>6</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="14" t="s">
         <v>13</v>
       </c>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="15"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
       <c r="F17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="13"/>
+      <c r="G17" s="15"/>
       <c r="H17" s="11"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="14">
+      <c r="A18" s="16">
         <v>7</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="14" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
       <c r="F19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="13"/>
+      <c r="G19" s="15"/>
       <c r="H19" s="11"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14">
+      <c r="A20" s="16">
         <v>8</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="31"/>
+      <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
       <c r="F21" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="32"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="13"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="14">
+      <c r="A22" s="16">
         <v>9</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="14" t="s">
         <v>14</v>
       </c>
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
       <c r="F23" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="13"/>
+      <c r="G23" s="15"/>
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="33"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="25"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="33"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="25"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="14">
+      <c r="A26" s="16">
         <v>1</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H26" s="28" t="s">
+      <c r="H26" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="15"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
       <c r="F27" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="29"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="14">
+      <c r="A28" s="16">
         <v>2</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="27" t="s">
+      <c r="H28" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="15"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
       <c r="F29" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="13"/>
-      <c r="H29" s="27"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="20"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="14">
+      <c r="A30" s="16">
         <v>4</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="27" t="s">
+      <c r="H30" s="20" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="15"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
       <c r="F31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="13"/>
-      <c r="H31" s="23"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="14">
+      <c r="A32" s="16">
         <v>5</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="27" t="s">
+      <c r="H32" s="20" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
       <c r="F33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="13"/>
-      <c r="H33" s="23"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="21"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14">
+      <c r="A34" s="16">
         <v>6</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="14" t="s">
         <v>13</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="15"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
       <c r="F35" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="13"/>
+      <c r="G35" s="15"/>
       <c r="H35" s="11"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="14">
+      <c r="A36" s="16">
         <v>7</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="14" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="15"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
       <c r="F37" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G37" s="13"/>
+      <c r="G37" s="15"/>
       <c r="H37" s="11"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="14">
+      <c r="A38" s="16">
         <v>8</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="12" t="s">
+      <c r="G38" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H38" s="31"/>
+      <c r="H38" s="12"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="15"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
       <c r="F39" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G39" s="13"/>
-      <c r="H39" s="32"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="13"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="33"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="25"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="33"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="25"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="14">
+      <c r="A42" s="16">
         <v>1</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H42" s="28" t="s">
+      <c r="H42" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
       <c r="F43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G43" s="13"/>
-      <c r="H43" s="29"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="27"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="14">
+      <c r="A44" s="16">
         <v>2</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G44" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H44" s="27" t="s">
+      <c r="H44" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="15"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
       <c r="F45" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G45" s="13"/>
-      <c r="H45" s="27"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="20"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="14">
+      <c r="A46" s="16">
         <v>4</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="27" t="s">
+      <c r="H46" s="20" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="15"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
       <c r="F47" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G47" s="13"/>
-      <c r="H47" s="23"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="21"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="14">
+      <c r="A48" s="16">
         <v>5</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="12" t="s">
+      <c r="G48" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H48" s="27" t="s">
+      <c r="H48" s="20" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="15"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
       <c r="F49" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="13"/>
-      <c r="H49" s="23"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="21"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="14">
+      <c r="A50" s="16">
         <v>6</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G50" s="14" t="s">
         <v>13</v>
       </c>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="15"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
       <c r="F51" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G51" s="13"/>
+      <c r="G51" s="15"/>
       <c r="H51" s="11"/>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="14">
+      <c r="A52" s="16">
         <v>7</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="14" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="15"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
       <c r="F53" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G53" s="13"/>
+      <c r="G53" s="15"/>
       <c r="H53" s="11"/>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="14">
+      <c r="A54" s="16">
         <v>8</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="14" t="s">
         <v>79</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H54" s="31"/>
+      <c r="H54" s="12"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="15"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
       <c r="F55" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G55" s="13"/>
-      <c r="H55" s="32"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="158">
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A24:H25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
     <mergeCell ref="A40:H41"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="B42:B43"/>
@@ -2543,100 +2599,46 @@
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="A24:H25"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="E52:E53"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{F0642C37-FB2E-4AFF-A3EE-AC391134171B}"/>
@@ -2700,15 +2702,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2716,13 +2718,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2730,15 +2732,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2746,13 +2748,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2783,72 +2785,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2890,15 +2892,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2906,13 +2908,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2920,15 +2922,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2936,13 +2938,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2973,279 +2975,315 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="14">
+      <c r="A10" s="16">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="15"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="13"/>
+      <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="14">
+      <c r="A12" s="16">
         <v>4</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="14">
+      <c r="A14" s="16">
         <v>5</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="13"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="14">
+      <c r="A16" s="16">
         <v>6</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="15"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
       <c r="F17" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="13"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="14">
+      <c r="A18" s="16">
         <v>7</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
       <c r="F19" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="13"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="14">
+      <c r="A20" s="16">
         <v>8</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
       <c r="F21" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="13"/>
+      <c r="G21" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3260,42 +3298,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3318,15 +3320,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3334,13 +3336,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3348,15 +3350,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3364,13 +3366,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3401,177 +3403,195 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="14">
+      <c r="A10" s="16">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="15"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="13"/>
+      <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="14">
+      <c r="A12" s="16">
         <v>4</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="14">
+      <c r="A14" s="16">
         <v>5</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="14" t="s">
         <v>62</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="13"/>
+      <c r="G15" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3586,24 +3606,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3629,15 +3631,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3645,13 +3647,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3659,15 +3661,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3675,13 +3677,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3712,109 +3714,115 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="14">
+      <c r="A10" s="16">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="15"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="13"/>
+      <c r="G11" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3829,15 +3837,604 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G10:G11"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E170F7C-3708-4D08-8BEB-42E9580C600F}">
+  <dimension ref="A1:L27"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="61.7109375" style="2" customWidth="1"/>
+    <col min="3" max="4" width="21.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="57.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26" style="2" customWidth="1"/>
+    <col min="8" max="8" width="59.42578125" style="2" customWidth="1"/>
+    <col min="9" max="10" width="37.140625" style="3" customWidth="1"/>
+    <col min="11" max="12" width="9.5703125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="25"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="29"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="21"/>
+    </row>
+    <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="16">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="15"/>
+      <c r="H9" s="11"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="16">
+        <v>8</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="17"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="15"/>
+      <c r="H11" s="13"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="25"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="25"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="16">
+        <v>5</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="15"/>
+      <c r="H15" s="21"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="16">
+        <v>7</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="17"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="15"/>
+      <c r="H17" s="11"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="16">
+        <v>8</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="12"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="17"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="15"/>
+      <c r="H19" s="13"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="25"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="25"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="16">
+        <v>5</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="17"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="15"/>
+      <c r="H23" s="21"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="16">
+        <v>7</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="10"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="17"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="15"/>
+      <c r="H25" s="11"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="16">
+        <v>8</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="12"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="17"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="15"/>
+      <c r="H27" s="13"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="64">
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="A20:H21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A12:H13"/>
+    <mergeCell ref="H10:H11"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H4"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{09A6E995-6867-4571-9539-85B4B57268B9}"/>
+    <hyperlink ref="H6" r:id="rId2" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{7F2AA047-0289-4AA1-B7F3-27A4071C26EA}"/>
+    <hyperlink ref="F9" r:id="rId3" xr:uid="{C058A9F3-432B-4492-8FEF-75D95EA066B4}"/>
+    <hyperlink ref="F11" r:id="rId4" xr:uid="{7C84037B-C526-459E-AFCC-EC743894CAAF}"/>
+    <hyperlink ref="F15" r:id="rId5" xr:uid="{96E9467B-42A7-4426-8441-28CEC140C97E}"/>
+    <hyperlink ref="H14" r:id="rId6" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{6295704B-3F57-4B74-84C7-65DD0D71B850}"/>
+    <hyperlink ref="F17" r:id="rId7" xr:uid="{0A00E371-A13B-46B9-BC01-F406FBB354D1}"/>
+    <hyperlink ref="F19" r:id="rId8" xr:uid="{601C882C-4FB2-4B15-B5E8-BE4DA74B8401}"/>
+    <hyperlink ref="F23" r:id="rId9" xr:uid="{FAE427DB-1331-4082-96AF-A6A7E15395CA}"/>
+    <hyperlink ref="H22" r:id="rId10" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{3C09A598-0156-4A2F-8BE6-68F7CC7CFBEF}"/>
+    <hyperlink ref="F25" r:id="rId11" xr:uid="{B281539B-7428-4B1A-B9D0-CB060D2AAC76}"/>
+    <hyperlink ref="F27" r:id="rId12" xr:uid="{909E7EB9-3EB2-4837-B0AB-B170A1604C99}"/>
+  </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId13"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA09817-54E1-4920-AEC1-14C200EE274D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A19FCE-A34D-49D4-B374-2539D7FEDE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$G$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Kuarters!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$G$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negeri Kenaboi'!$A$1:$G$23</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="99">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -551,12 +551,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -568,6 +562,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -587,11 +587,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -599,20 +599,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -943,15 +943,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -959,13 +959,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -1026,87 +1026,87 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="34">
+      <c r="A10" s="30">
         <v>3</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="31" t="s">
         <v>39</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="7" t="s">
@@ -1117,98 +1117,98 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="34"/>
-      <c r="B11" s="31"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="32"/>
       <c r="C11" s="21"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="6" t="s">
         <v>34</v>
       </c>
       <c r="G11" s="21"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+      <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="23"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="34">
+      <c r="A16" s="30">
         <v>6</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F16" s="8" t="s">
@@ -1219,30 +1219,30 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="34"/>
-      <c r="B17" s="19"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="21"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="6" t="s">
         <v>34</v>
       </c>
       <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="16">
+      <c r="A18" s="14">
         <v>7</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="8" t="s">
@@ -1253,144 +1253,214 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="19"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="21"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
       <c r="F19" s="6" t="s">
         <v>34</v>
       </c>
       <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="16"/>
-      <c r="B20" s="18"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="14"/>
+      <c r="G20" s="18"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="19"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="23"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="15"/>
+      <c r="G21" s="19"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="16"/>
-      <c r="B22" s="18"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
       <c r="F22" s="8"/>
-      <c r="G22" s="14"/>
+      <c r="G22" s="18"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
-      <c r="B23" s="19"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="23"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="15"/>
+      <c r="G23" s="19"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="16"/>
-      <c r="B24" s="30"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="31"/>
       <c r="C24" s="21"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="7"/>
       <c r="G24" s="21"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="17"/>
-      <c r="B25" s="31"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="32"/>
       <c r="C25" s="21"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="6"/>
       <c r="G25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="16"/>
-      <c r="B26" s="18"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="22"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="14"/>
+      <c r="G26" s="18"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="19"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="23"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
       <c r="F27" s="6"/>
-      <c r="G27" s="15"/>
+      <c r="G27" s="19"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="16"/>
-      <c r="B28" s="18"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="22"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="14"/>
+      <c r="G28" s="18"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="17"/>
-      <c r="B29" s="19"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="23"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
       <c r="F29" s="6"/>
-      <c r="G29" s="15"/>
+      <c r="G29" s="19"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="16"/>
-      <c r="B30" s="18"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="16"/>
       <c r="C30" s="21"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
       <c r="F30" s="8"/>
       <c r="G30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="17"/>
-      <c r="B31" s="19"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="21"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
       <c r="F31" s="6"/>
       <c r="G31" s="21"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="16"/>
-      <c r="B32" s="18"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="16"/>
       <c r="C32" s="21"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
       <c r="F32" s="8"/>
       <c r="G32" s="21"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="17"/>
-      <c r="B33" s="19"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="21"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
       <c r="F33" s="6"/>
       <c r="G33" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="86">
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A3:G4"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="E18:E19"/>
@@ -1407,76 +1477,6 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A3:G4"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D20:D21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
@@ -1488,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D54FEF-B8B0-455E-9719-4EECE694A16C}">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -1504,28 +1504,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="27"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
@@ -1582,63 +1582,63 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="33" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="27"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="34"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="18" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="20" t="s">
@@ -1646,37 +1646,37 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="19"/>
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="18" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="20" t="s">
@@ -1684,37 +1684,37 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="19"/>
       <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+      <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="18" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="20" t="s">
@@ -1722,774 +1722,520 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="G13" s="19"/>
       <c r="H13" s="21"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
-        <v>5</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="14" t="s">
+      <c r="A14" s="14">
+        <v>6</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>52</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="21"/>
+        <v>19</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="H15" s="11"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16">
-        <v>6</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>17</v>
+      <c r="A16" s="14">
+        <v>9</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>24</v>
       </c>
       <c r="C16" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="10"/>
+      <c r="G16" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="19"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="23"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="11"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16">
+      <c r="A18" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="25"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="25"/>
+    </row>
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="14">
+        <v>1</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="15"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="G21" s="19"/>
+      <c r="H21" s="34"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="14">
+        <v>2</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="15"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20"/>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="14">
+        <v>4</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="15"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="19"/>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="14">
+        <v>6</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="6" t="s">
+      <c r="G26" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="10"/>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="15"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="11"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16">
-        <v>8</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="12"/>
-    </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="13"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16">
-        <v>9</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="25"/>
-    </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="25"/>
-    </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16">
+      <c r="G27" s="19"/>
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="25"/>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="25"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="14">
         <v>1</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="H26" s="26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="27"/>
-    </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="16">
-        <v>2</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="17"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="20"/>
-    </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="16">
-        <v>4</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>64</v>
+      <c r="B30" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="20" t="s">
-        <v>54</v>
+      <c r="G30" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="33" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="17"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
       <c r="F31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="15"/>
-      <c r="H31" s="21"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="34"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="16">
-        <v>5</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>64</v>
+      <c r="A32" s="14">
+        <v>2</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="14" t="s">
-        <v>16</v>
+      <c r="G32" s="18" t="s">
+        <v>13</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="17"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
       <c r="F33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="15"/>
-      <c r="H33" s="21"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="20"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="16">
+      <c r="A34" s="14">
+        <v>4</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="10"/>
+      <c r="G34" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="17"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
       <c r="F35" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="15"/>
-      <c r="H35" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="G35" s="19"/>
+      <c r="H35" s="21"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="16">
-        <v>7</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>64</v>
+      <c r="A36" s="14">
+        <v>6</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="14" t="s">
-        <v>22</v>
+      <c r="G36" s="18" t="s">
+        <v>13</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="17"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
       <c r="F37" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G37" s="15"/>
+      <c r="G37" s="19"/>
       <c r="H37" s="11"/>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="16">
-        <v>8</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="12"/>
-    </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="17"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G39" s="15"/>
-      <c r="H39" s="13"/>
-    </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="25"/>
-    </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="25"/>
-    </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="16">
-        <v>1</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="H42" s="26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="17"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G43" s="15"/>
-      <c r="H43" s="27"/>
-    </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="16">
-        <v>2</v>
-      </c>
-      <c r="B44" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="17"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45" s="15"/>
-      <c r="H45" s="20"/>
-    </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="16">
-        <v>4</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H46" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="17"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G47" s="15"/>
-      <c r="H47" s="21"/>
-    </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="16">
-        <v>5</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H48" s="20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="17"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G49" s="15"/>
-      <c r="H49" s="21"/>
-    </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="16">
-        <v>6</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" s="10"/>
-    </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="17"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" s="15"/>
-      <c r="H51" s="11"/>
-    </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="16">
-        <v>7</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="H52" s="10"/>
-    </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="17"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" s="15"/>
-      <c r="H53" s="11"/>
-    </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="16">
-        <v>8</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="12"/>
-    </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="17"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="15"/>
-      <c r="H55" s="13"/>
-    </row>
   </sheetData>
-  <mergeCells count="158">
+  <mergeCells count="98">
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A28:H29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A18:H19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
     <mergeCell ref="A1:H2"/>
-    <mergeCell ref="G14:G15"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E15"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
@@ -2499,190 +2245,42 @@
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:C15"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="H8:H9"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="A24:H25"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A40:H41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="E52:E53"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{F0642C37-FB2E-4AFF-A3EE-AC391134171B}"/>
     <hyperlink ref="F9" r:id="rId2" xr:uid="{00258999-4675-4877-9551-67DBB6D4835C}"/>
     <hyperlink ref="F11" r:id="rId3" xr:uid="{32C8CD77-D463-4CF6-8760-780448A0E47B}"/>
     <hyperlink ref="F13" r:id="rId4" xr:uid="{A3627ABE-8C59-41B0-9C05-F61764E8549C}"/>
-    <hyperlink ref="F15" r:id="rId5" xr:uid="{6E7F3CB3-5CFD-4F03-891C-DD3A4D003B7F}"/>
-    <hyperlink ref="H6" r:id="rId6" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{EA2C3863-D60F-41EB-AB6A-AA5F0ABFC2D9}"/>
-    <hyperlink ref="H10" r:id="rId7" display="https://drive.google.com/file/d/1R_raajVpCi7rzDTpoCcSJMrv35EYXkQ1/view?usp=sharing" xr:uid="{582FD441-A415-407B-A2C2-3C7802A01407}"/>
-    <hyperlink ref="H12" r:id="rId8" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{2B85E27F-B7DA-493E-B4CB-31C52D8BB58F}"/>
-    <hyperlink ref="H14" r:id="rId9" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{7FFA9277-00D6-468C-9219-E2D9E10B6DDF}"/>
-    <hyperlink ref="H8" r:id="rId10" xr:uid="{C8A72D82-9829-4481-9DBC-B809B2A67840}"/>
-    <hyperlink ref="F17" r:id="rId11" xr:uid="{C50B7E68-9B02-437B-AFE5-7D397007F6AF}"/>
-    <hyperlink ref="F19" r:id="rId12" xr:uid="{6156982A-9F67-4C39-B76A-A6002ED11587}"/>
-    <hyperlink ref="F21" r:id="rId13" xr:uid="{AB7C8E70-FFD7-4DA2-9851-46F01C4C7FE9}"/>
-    <hyperlink ref="F23" r:id="rId14" xr:uid="{C9F8004F-2006-467E-A196-CFC9352C9B68}"/>
-    <hyperlink ref="F27" r:id="rId15" xr:uid="{8A41AEDD-00D6-4798-BE58-4F607596CE5E}"/>
-    <hyperlink ref="F29" r:id="rId16" xr:uid="{62B78FFF-77DC-444D-90D0-1CA894377B57}"/>
-    <hyperlink ref="F31" r:id="rId17" xr:uid="{CB39D23E-1A2E-40EB-A68F-E8F7D4D0DC74}"/>
-    <hyperlink ref="F33" r:id="rId18" xr:uid="{663DF080-B326-4FD0-B69E-6E321D50216C}"/>
-    <hyperlink ref="H26" r:id="rId19" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{FB3E61E0-3CCB-44F1-B4A6-1AFE1F3CDF6F}"/>
-    <hyperlink ref="H30" r:id="rId20" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{766F845B-5791-46B9-A70C-900DBB353CB8}"/>
-    <hyperlink ref="H32" r:id="rId21" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{3B1F1F54-6E41-4B15-8C8B-3EFAD5BE0B2C}"/>
-    <hyperlink ref="H28" r:id="rId22" xr:uid="{12917566-A49D-451C-AE74-FF9FC1F43EF9}"/>
-    <hyperlink ref="F35" r:id="rId23" xr:uid="{E1BED91B-CAFE-4958-A8D4-FC59655467C6}"/>
-    <hyperlink ref="F37" r:id="rId24" xr:uid="{1988793E-9B89-4051-BF42-9A9BC2123B1F}"/>
-    <hyperlink ref="F39" r:id="rId25" xr:uid="{EF50FA91-35AE-4A95-B18B-E9A0DC2D867C}"/>
-    <hyperlink ref="F43" r:id="rId26" xr:uid="{00C82A6F-2C18-41D2-89AA-3C1C7095F3DC}"/>
-    <hyperlink ref="F45" r:id="rId27" xr:uid="{18FA63F7-AA33-4E60-A540-013BDF8F175E}"/>
-    <hyperlink ref="F47" r:id="rId28" xr:uid="{01447622-ADCD-4E8E-87E8-BDA8D1ADD1BF}"/>
-    <hyperlink ref="F49" r:id="rId29" xr:uid="{7136B4C8-E13F-412F-AD19-F4C4EE3C27A3}"/>
-    <hyperlink ref="H42" r:id="rId30" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{F63D11AF-4055-475B-BB25-6E5BFCF66740}"/>
-    <hyperlink ref="H46" r:id="rId31" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{84044B59-A767-4420-A6F8-CC0A7E9E718E}"/>
-    <hyperlink ref="H48" r:id="rId32" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{347BCBB6-C5EE-4148-88C5-C85C04A9BD1D}"/>
-    <hyperlink ref="H44" r:id="rId33" xr:uid="{D28BA95A-DCAF-4B84-A98A-CEA5DA6E2F09}"/>
-    <hyperlink ref="F51" r:id="rId34" xr:uid="{031E33FD-D835-47FF-B82E-B6EBE7FB15DD}"/>
-    <hyperlink ref="F53" r:id="rId35" xr:uid="{2F8B8258-D0AB-4F89-BE66-F01E10B039ED}"/>
-    <hyperlink ref="F55" r:id="rId36" xr:uid="{5D807F33-B9AD-4909-9D9B-0BAAFCAF8B82}"/>
+    <hyperlink ref="H6" r:id="rId5" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{EA2C3863-D60F-41EB-AB6A-AA5F0ABFC2D9}"/>
+    <hyperlink ref="H10" r:id="rId6" display="https://drive.google.com/file/d/1R_raajVpCi7rzDTpoCcSJMrv35EYXkQ1/view?usp=sharing" xr:uid="{582FD441-A415-407B-A2C2-3C7802A01407}"/>
+    <hyperlink ref="H12" r:id="rId7" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{2B85E27F-B7DA-493E-B4CB-31C52D8BB58F}"/>
+    <hyperlink ref="H8" r:id="rId8" xr:uid="{C8A72D82-9829-4481-9DBC-B809B2A67840}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{C50B7E68-9B02-437B-AFE5-7D397007F6AF}"/>
+    <hyperlink ref="F17" r:id="rId10" xr:uid="{C9F8004F-2006-467E-A196-CFC9352C9B68}"/>
+    <hyperlink ref="F21" r:id="rId11" xr:uid="{8A41AEDD-00D6-4798-BE58-4F607596CE5E}"/>
+    <hyperlink ref="F23" r:id="rId12" xr:uid="{62B78FFF-77DC-444D-90D0-1CA894377B57}"/>
+    <hyperlink ref="F25" r:id="rId13" xr:uid="{CB39D23E-1A2E-40EB-A68F-E8F7D4D0DC74}"/>
+    <hyperlink ref="H20" r:id="rId14" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{FB3E61E0-3CCB-44F1-B4A6-1AFE1F3CDF6F}"/>
+    <hyperlink ref="H24" r:id="rId15" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{766F845B-5791-46B9-A70C-900DBB353CB8}"/>
+    <hyperlink ref="H22" r:id="rId16" xr:uid="{12917566-A49D-451C-AE74-FF9FC1F43EF9}"/>
+    <hyperlink ref="F27" r:id="rId17" xr:uid="{E1BED91B-CAFE-4958-A8D4-FC59655467C6}"/>
+    <hyperlink ref="F31" r:id="rId18" xr:uid="{00C82A6F-2C18-41D2-89AA-3C1C7095F3DC}"/>
+    <hyperlink ref="F33" r:id="rId19" xr:uid="{18FA63F7-AA33-4E60-A540-013BDF8F175E}"/>
+    <hyperlink ref="F35" r:id="rId20" xr:uid="{01447622-ADCD-4E8E-87E8-BDA8D1ADD1BF}"/>
+    <hyperlink ref="H30" r:id="rId21" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{F63D11AF-4055-475B-BB25-6E5BFCF66740}"/>
+    <hyperlink ref="H34" r:id="rId22" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{84044B59-A767-4420-A6F8-CC0A7E9E718E}"/>
+    <hyperlink ref="H32" r:id="rId23" xr:uid="{D28BA95A-DCAF-4B84-A98A-CEA5DA6E2F09}"/>
+    <hyperlink ref="F37" r:id="rId24" xr:uid="{031E33FD-D835-47FF-B82E-B6EBE7FB15DD}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId37"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId25"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="9" max="7" man="1"/>
-    <brk id="15" max="7" man="1"/>
+    <brk id="13" max="7" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2702,15 +2300,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2718,13 +2316,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2785,72 +2383,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2892,15 +2490,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2908,13 +2506,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2975,315 +2573,279 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>96</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="19"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+      <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="23"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="16">
+      <c r="A16" s="14">
         <v>6</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>91</v>
       </c>
       <c r="C16" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="19"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="23"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="15"/>
+      <c r="G17" s="19"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="16">
+      <c r="A18" s="14">
         <v>7</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>86</v>
       </c>
       <c r="C18" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="19"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="23"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
       <c r="F19" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="15"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="16">
+      <c r="A20" s="14">
         <v>8</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="16" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="19"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="23"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="15"/>
+      <c r="G21" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3298,6 +2860,42 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3320,15 +2918,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3336,13 +2934,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3403,195 +3001,177 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>88</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="19"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+      <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>91</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="18" t="s">
         <v>62</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="23"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3606,6 +3186,24 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3631,15 +3229,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3647,13 +3245,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3714,115 +3312,109 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>85</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>86</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>33</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3837,6 +3429,12 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3862,28 +3460,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="27"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
@@ -3940,25 +3538,25 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="18" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="20" t="s">
@@ -3966,37 +3564,37 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="19"/>
       <c r="H7" s="21"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="18" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="10"/>
@@ -4004,39 +3602,39 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="19"/>
       <c r="H9" s="11"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="A10" s="14">
         <v>8</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="18" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="12"/>
@@ -4044,15 +3642,15 @@
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="19"/>
       <c r="H11" s="13"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -4084,25 +3682,25 @@
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="18" t="s">
         <v>64</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="18" t="s">
         <v>16</v>
       </c>
       <c r="H14" s="20" t="s">
@@ -4112,39 +3710,39 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="19"/>
       <c r="H15" s="21"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16">
+      <c r="A16" s="14">
         <v>7</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="18" t="s">
         <v>64</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="18" t="s">
         <v>22</v>
       </c>
       <c r="H16" s="10"/>
@@ -4152,39 +3750,39 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="15"/>
+      <c r="G17" s="19"/>
       <c r="H17" s="11"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16">
+      <c r="A18" s="14">
         <v>8</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="18" t="s">
         <v>64</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="18" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="12"/>
@@ -4192,15 +3790,15 @@
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
       <c r="F19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="15"/>
+      <c r="G19" s="19"/>
       <c r="H19" s="13"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -4232,25 +3830,25 @@
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16">
+      <c r="A22" s="14">
         <v>5</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="16" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="18" t="s">
         <v>79</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="18" t="s">
         <v>16</v>
       </c>
       <c r="H22" s="20" t="s">
@@ -4260,39 +3858,39 @@
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
-      <c r="B23" s="19"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="23"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
       <c r="F23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="19"/>
       <c r="H23" s="21"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="16">
+      <c r="A24" s="14">
         <v>7</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="18" t="s">
         <v>79</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="18" t="s">
         <v>22</v>
       </c>
       <c r="H24" s="10"/>
@@ -4300,39 +3898,39 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="17"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G25" s="15"/>
+      <c r="G25" s="19"/>
       <c r="H25" s="11"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16">
+      <c r="A26" s="14">
         <v>8</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="18" t="s">
         <v>79</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="18" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="12"/>
@@ -4340,33 +3938,65 @@
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
       <c r="F27" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="15"/>
+      <c r="G27" s="19"/>
       <c r="H27" s="13"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A12:H13"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="A20:H21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="A22:A23"/>
@@ -4375,50 +4005,18 @@
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="A20:H21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A12:H13"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{09A6E995-6867-4571-9539-85B4B57268B9}"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A19FCE-A34D-49D4-B374-2539D7FEDE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A19FCE-A34D-49D4-B374-2539D7FEDE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC822467-4747-4FE7-9E01-62E5F214EDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$G$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Kuarters!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$G$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negeri Kenaboi'!$A$1:$G$23</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="101">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -347,6 +347,12 @@
   </si>
   <si>
     <t>Blok Pejabat</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1D9YJMnMNMP2_VRcyXpY4PgZV8tHBMhty/view?usp=sharing,https://drive.google.com/file/d/13-gnjk2D5kvvgutQZ6busAoul0JsiSoH/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1R5E6lq_mvjMPibgC6ibuiWMZSYEV7FAG/view?usp=sharing,https://drive.google.com/file/d/1aBDJ3CoPGedvmATNRHHhz1p2zJqDeiOq/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -518,7 +524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -530,7 +536,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -545,22 +550,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -569,11 +571,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -581,17 +589,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -599,20 +607,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -943,15 +957,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -959,13 +973,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -973,15 +987,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -1015,7 +1029,7 @@
       <c r="D5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1029,365 +1043,365 @@
       <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="12" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="6" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="19"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="19"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="30">
+      <c r="A10" s="31">
         <v>3</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="30" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="30"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="6" t="s">
+      <c r="A11" s="31"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="21"/>
+      <c r="G11" s="30"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="12" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="6" t="s">
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="19"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="16" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="23"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="6" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="19"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="30">
+      <c r="A16" s="31">
         <v>6</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="30" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="30"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="6" t="s">
+      <c r="A17" s="31"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="21"/>
+      <c r="G17" s="30"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="14">
         <v>7</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="30" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="6" t="s">
+      <c r="B19" s="13"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="21"/>
+      <c r="G19" s="30"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="14"/>
-      <c r="B20" s="16"/>
+      <c r="B20" s="12"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="18"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
-      <c r="B21" s="17"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="23"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="19"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="17"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="14"/>
-      <c r="B22" s="16"/>
+      <c r="B22" s="12"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="18"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
-      <c r="B23" s="17"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="23"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="19"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="17"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="14"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="21"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="30"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="21"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="14"/>
-      <c r="B26" s="16"/>
+      <c r="B26" s="12"/>
       <c r="C26" s="22"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="18"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
-      <c r="B27" s="17"/>
+      <c r="B27" s="13"/>
       <c r="C27" s="23"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="19"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="17"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="12"/>
       <c r="C28" s="22"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="18"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
-      <c r="B29" s="17"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="23"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="19"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="17"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="14"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="21"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="30"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="15"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="21"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="30"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="14"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="21"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="30"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="15"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="21"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="86">
@@ -1504,42 +1518,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="21"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="21"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="27"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
@@ -1568,7 +1582,7 @@
       <c r="D5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1577,7 +1591,7 @@
       <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1585,577 +1599,570 @@
       <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="24" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="6" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="34"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="6" t="s">
+      <c r="B11" s="19"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="21"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="30"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="11" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="6" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="19"/>
-      <c r="H13" s="21"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="30"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14">
         <v>6</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="10"/>
+      <c r="H14" s="34" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="23"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="6" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="11"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14">
         <v>9</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="35" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="23"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="6" t="s">
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="19"/>
-      <c r="H17" s="5"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="36"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="25"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="27"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="25"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="27"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="14">
         <v>1</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C20" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="33" t="s">
-        <v>51</v>
-      </c>
+      <c r="H20" s="24"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
-      <c r="B21" s="17"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="23"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="6" t="s">
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="19"/>
-      <c r="H21" s="34"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="25"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="14">
         <v>2</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C22" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="20" t="s">
-        <v>50</v>
-      </c>
+      <c r="H22" s="11"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
-      <c r="B23" s="17"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="23"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="6" t="s">
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="19"/>
-      <c r="H23" s="20"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="11"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="14">
         <v>4</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="20" t="s">
-        <v>54</v>
-      </c>
+      <c r="H24" s="11"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="6" t="s">
+      <c r="B25" s="13"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="21"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="30"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="14">
         <v>6</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H26" s="10"/>
+      <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="6" t="s">
+      <c r="B27" s="13"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="19"/>
-      <c r="H27" s="11"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="25"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="25"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="14">
         <v>1</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="H30" s="33" t="s">
-        <v>51</v>
-      </c>
+      <c r="H30" s="24"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="15"/>
-      <c r="B31" s="17"/>
+      <c r="B31" s="13"/>
       <c r="C31" s="23"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="6" t="s">
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="19"/>
-      <c r="H31" s="34"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="25"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="14">
         <v>2</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="12" t="s">
         <v>81</v>
       </c>
       <c r="C32" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="20" t="s">
-        <v>50</v>
-      </c>
+      <c r="H32" s="11"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="15"/>
-      <c r="B33" s="17"/>
+      <c r="B33" s="13"/>
       <c r="C33" s="23"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="6" t="s">
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="19"/>
-      <c r="H33" s="20"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="11"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="14">
         <v>4</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="18" t="s">
+      <c r="G34" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="20" t="s">
-        <v>54</v>
-      </c>
+      <c r="H34" s="11"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="15"/>
-      <c r="B35" s="17"/>
+      <c r="B35" s="13"/>
       <c r="C35" s="23"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="6" t="s">
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="19"/>
-      <c r="H35" s="21"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="30"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="14">
         <v>6</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G36" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H36" s="10"/>
+      <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="6" t="s">
+      <c r="B37" s="13"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G37" s="19"/>
-      <c r="H37" s="11"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="98">
-    <mergeCell ref="A36:A37"/>
+  <mergeCells count="100">
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="C36:C37"/>
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E36:E37"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
     <mergeCell ref="G36:G37"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="H32:H33"/>
@@ -2171,6 +2178,7 @@
     <mergeCell ref="C32:C33"/>
     <mergeCell ref="D32:D33"/>
     <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A36:A37"/>
     <mergeCell ref="A28:H29"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
@@ -2184,34 +2192,38 @@
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="D26:D27"/>
     <mergeCell ref="E26:E27"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
     <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H24:H25"/>
     <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H20:H21"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H22:H23"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B14:B15"/>
     <mergeCell ref="A18:H19"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="C16:C17"/>
@@ -2219,16 +2231,6 @@
     <mergeCell ref="E16:E17"/>
     <mergeCell ref="G16:G17"/>
     <mergeCell ref="B16:B17"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="G10:G11"/>
@@ -2242,13 +2244,19 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="H8:H9"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{F0642C37-FB2E-4AFF-A3EE-AC391134171B}"/>
@@ -2264,23 +2272,18 @@
     <hyperlink ref="F21" r:id="rId11" xr:uid="{8A41AEDD-00D6-4798-BE58-4F607596CE5E}"/>
     <hyperlink ref="F23" r:id="rId12" xr:uid="{62B78FFF-77DC-444D-90D0-1CA894377B57}"/>
     <hyperlink ref="F25" r:id="rId13" xr:uid="{CB39D23E-1A2E-40EB-A68F-E8F7D4D0DC74}"/>
-    <hyperlink ref="H20" r:id="rId14" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{FB3E61E0-3CCB-44F1-B4A6-1AFE1F3CDF6F}"/>
-    <hyperlink ref="H24" r:id="rId15" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{766F845B-5791-46B9-A70C-900DBB353CB8}"/>
-    <hyperlink ref="H22" r:id="rId16" xr:uid="{12917566-A49D-451C-AE74-FF9FC1F43EF9}"/>
-    <hyperlink ref="F27" r:id="rId17" xr:uid="{E1BED91B-CAFE-4958-A8D4-FC59655467C6}"/>
-    <hyperlink ref="F31" r:id="rId18" xr:uid="{00C82A6F-2C18-41D2-89AA-3C1C7095F3DC}"/>
-    <hyperlink ref="F33" r:id="rId19" xr:uid="{18FA63F7-AA33-4E60-A540-013BDF8F175E}"/>
-    <hyperlink ref="F35" r:id="rId20" xr:uid="{01447622-ADCD-4E8E-87E8-BDA8D1ADD1BF}"/>
-    <hyperlink ref="H30" r:id="rId21" display="https://drive.google.com/file/d/1_ymiN-Qm_q0mKaKXcl-kbTueVyZuoI94/view?usp=sharing" xr:uid="{F63D11AF-4055-475B-BB25-6E5BFCF66740}"/>
-    <hyperlink ref="H34" r:id="rId22" display="https://drive.google.com/file/d/11pNgqUpVXv_beJ62XBYXVYDowLapmOeh/view?usp=sharing" xr:uid="{84044B59-A767-4420-A6F8-CC0A7E9E718E}"/>
-    <hyperlink ref="H32" r:id="rId23" xr:uid="{D28BA95A-DCAF-4B84-A98A-CEA5DA6E2F09}"/>
-    <hyperlink ref="F37" r:id="rId24" xr:uid="{031E33FD-D835-47FF-B82E-B6EBE7FB15DD}"/>
+    <hyperlink ref="F27" r:id="rId14" xr:uid="{E1BED91B-CAFE-4958-A8D4-FC59655467C6}"/>
+    <hyperlink ref="F31" r:id="rId15" xr:uid="{00C82A6F-2C18-41D2-89AA-3C1C7095F3DC}"/>
+    <hyperlink ref="F33" r:id="rId16" xr:uid="{18FA63F7-AA33-4E60-A540-013BDF8F175E}"/>
+    <hyperlink ref="F35" r:id="rId17" xr:uid="{01447622-ADCD-4E8E-87E8-BDA8D1ADD1BF}"/>
+    <hyperlink ref="F37" r:id="rId18" xr:uid="{031E33FD-D835-47FF-B82E-B6EBE7FB15DD}"/>
+    <hyperlink ref="H14" r:id="rId19" xr:uid="{6E25EBC1-DB77-4A7C-9B61-5D225D82B96F}"/>
+    <hyperlink ref="H16" r:id="rId20" xr:uid="{DC41D252-5B6D-49F4-B013-CBB47E46599C}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId25"/>
-  <rowBreaks count="2" manualBreakCount="2">
-    <brk id="9" max="7" man="1"/>
-    <brk id="13" max="7" man="1"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId21"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="43" max="7" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2300,15 +2303,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2316,13 +2319,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2330,15 +2333,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2372,7 +2375,7 @@
       <c r="D5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2386,69 +2389,69 @@
       <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="6" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="19"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="19"/>
+      <c r="G9" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2490,15 +2493,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2506,13 +2509,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2520,15 +2523,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2562,7 +2565,7 @@
       <c r="D5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2576,273 +2579,273 @@
       <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="6" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="19"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="19"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
-      <c r="B11" s="17"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="6" t="s">
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="19"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="6" t="s">
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G13" s="19"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="12" t="s">
         <v>89</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="23"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="6" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="19"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="14">
         <v>6</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="12" t="s">
         <v>91</v>
       </c>
       <c r="C16" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="23"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="6" t="s">
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="19"/>
+      <c r="G17" s="17"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="14">
         <v>7</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="12" t="s">
         <v>86</v>
       </c>
       <c r="C18" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
-      <c r="B19" s="17"/>
+      <c r="B19" s="13"/>
       <c r="C19" s="23"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="6" t="s">
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="19"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="14">
         <v>8</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="12" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
-      <c r="B21" s="17"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="23"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="6" t="s">
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="19"/>
+      <c r="G21" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -2918,15 +2921,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2934,13 +2937,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2948,15 +2951,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2990,7 +2993,7 @@
       <c r="D5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -3004,171 +3007,171 @@
       <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="6" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="19"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="19"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="12" t="s">
         <v>89</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
-      <c r="B11" s="17"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="6" t="s">
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="19"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="12" t="s">
         <v>90</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="6" t="s">
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="19"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="12" t="s">
         <v>91</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="23"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="6" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="19"/>
+      <c r="G15" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -3229,15 +3232,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3245,13 +3248,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3259,15 +3262,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3301,7 +3304,7 @@
       <c r="D5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -3315,103 +3318,103 @@
       <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="12" t="s">
         <v>85</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="6" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="19"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>86</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="19"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="12" t="s">
         <v>33</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
-      <c r="B11" s="17"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="6" t="s">
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="19"/>
+      <c r="G11" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -3460,42 +3463,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="21"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="21"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="27"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
@@ -3524,7 +3527,7 @@
       <c r="D5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -3533,7 +3536,7 @@
       <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3541,77 +3544,77 @@
       <c r="A6" s="14">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="6" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="21"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="30"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="10"/>
+      <c r="H8" s="9"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="11"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="10"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
@@ -3619,65 +3622,65 @@
       <c r="A10" s="14">
         <v>8</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="12"/>
+      <c r="H10" s="32"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
-      <c r="B11" s="17"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="6" t="s">
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="13"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="33"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="25"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="27"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="25"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="27"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
@@ -3685,25 +3688,25 @@
       <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="11" t="s">
         <v>52</v>
       </c>
       <c r="K14" s="2"/>
@@ -3711,15 +3714,15 @@
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="6" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="21"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="30"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
@@ -3727,39 +3730,39 @@
       <c r="A16" s="14">
         <v>7</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="10"/>
+      <c r="H16" s="9"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="6" t="s">
+      <c r="B17" s="13"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="19"/>
-      <c r="H17" s="11"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="10"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
@@ -3767,65 +3770,65 @@
       <c r="A18" s="14">
         <v>8</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="12"/>
+      <c r="H18" s="32"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="6" t="s">
+      <c r="B19" s="13"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="19"/>
-      <c r="H19" s="13"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="33"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="25"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="27"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="25"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="27"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
@@ -3833,25 +3836,25 @@
       <c r="A22" s="14">
         <v>5</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="H22" s="11" t="s">
         <v>52</v>
       </c>
       <c r="K22" s="2"/>
@@ -3859,15 +3862,15 @@
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
-      <c r="B23" s="17"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="23"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="6" t="s">
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="19"/>
-      <c r="H23" s="21"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="30"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
@@ -3875,39 +3878,39 @@
       <c r="A24" s="14">
         <v>7</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="10"/>
+      <c r="H24" s="9"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="6" t="s">
+      <c r="B25" s="13"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="11"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="10"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
@@ -3915,39 +3918,39 @@
       <c r="A26" s="14">
         <v>8</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="12"/>
+      <c r="H26" s="32"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="6" t="s">
+      <c r="B27" s="13"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="19"/>
-      <c r="H27" s="13"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="33"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC822467-4747-4FE7-9E01-62E5F214EDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A68425-E2DA-4F3F-A1B9-E21B5D11A24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -1749,7 +1749,7 @@
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>17</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>24</v>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>11</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>69</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>11</v>
@@ -2121,7 +2121,7 @@
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>82</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0A9DBA-0DCD-4FD1-A83B-8505A89E4CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC446F46-76B7-475E-BD4F-7891B5542752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="116">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -350,9 +350,6 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1CrucTqd84gbfVuo2rxZipDmqLKE7DS48/view?usp=sharing,https://drive.google.com/file/d/1iOJJh7hBj8CBX4rzlIhrRfc3neU3EIjt/view?usp=sharing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status </t>
   </si>
   <si>
     <t>Dalam Penambahbaikkan</t>
@@ -1658,7 +1655,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>48</v>
@@ -1684,7 +1681,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H6" s="26" t="s">
         <v>49</v>
@@ -1722,7 +1719,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H8" s="18" t="s">
         <v>99</v>
@@ -1760,7 +1757,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H10" s="18" t="s">
         <v>51</v>
@@ -1798,7 +1795,7 @@
         <v>6</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>52</v>
@@ -1836,7 +1833,7 @@
         <v>19</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>97</v>
@@ -1874,7 +1871,7 @@
         <v>19</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H16" s="16" t="s">
         <v>98</v>
@@ -1934,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H20" s="26"/>
     </row>
@@ -1970,7 +1967,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H22" s="18"/>
     </row>
@@ -1991,10 +1988,10 @@
         <v>3</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>104</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>105</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>64</v>
@@ -2003,13 +2000,13 @@
         <v>62</v>
       </c>
       <c r="F24" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="18" t="s">
         <v>107</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2019,7 +2016,7 @@
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="23"/>
@@ -2041,13 +2038,13 @@
         <v>62</v>
       </c>
       <c r="F26" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="42" t="s">
         <v>110</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="42" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2057,7 +2054,7 @@
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G27" s="14"/>
       <c r="H27" s="43"/>
@@ -2067,7 +2064,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>69</v>
@@ -2079,13 +2076,13 @@
         <v>62</v>
       </c>
       <c r="F28" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="H28" s="15" t="s">
         <v>115</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2095,7 +2092,7 @@
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC446F46-76B7-475E-BD4F-7891B5542752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8703AC6-A12F-4FC9-8674-B5655F776C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$G$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Kuarters!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$71</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$75</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$G$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negeri Kenaboi'!$A$1:$G$23</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="120">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -85,18 +85,12 @@
     <t>Pejabat Renj Kuala Pilah</t>
   </si>
   <si>
-    <t>Bangunan Blok Pengawal Keselamatan</t>
-  </si>
-  <si>
     <t>Blok Kuarters Pegawai</t>
   </si>
   <si>
     <t>Dalam Keadaan Baik Dan Diduduki / Bangunan Pejabat</t>
   </si>
   <si>
-    <t>Dalam Keadaan Baik Dan Diduduki / Bangunan Blok Pengawal Keselamatan</t>
-  </si>
-  <si>
     <t>Perlu Penyelenggaraan Dan Tidak Diduduki / Bangunan Kuarters Pegawai</t>
   </si>
   <si>
@@ -181,9 +175,6 @@
     <t>Dalam Keadaan Baik Dan Diguna Pakai  / Blok Penginapan Asrama</t>
   </si>
   <si>
-    <t>Blok Bangunan Pejabat Taman Eko Rimba</t>
-  </si>
-  <si>
     <t>Dalam Keadaan Baik Dan Diguna Pakai  / Blok Pejabat</t>
   </si>
   <si>
@@ -223,9 +214,6 @@
     <t xml:space="preserve">Blok Bilik Mesyuarat </t>
   </si>
   <si>
-    <t>Rosak / Bangunan Pejabat</t>
-  </si>
-  <si>
     <t>Perkara</t>
   </si>
   <si>
@@ -398,6 +386,30 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/18PYaffP-sjWduJyRAyPOdlZV2Xy7Txer/view?usp=sharing,https://drive.google.com/file/d/19-HzjW4bIhsRIpyEfiOt81JFy3rEwaYj/view?usp=sharing,https://drive.google.com/file/d/1g9RhW9AFBHOOimXZ3NErgj7IBsJpXGfn/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1m40F6ktURyJyeAjzWD8aif-jMdCHYSLc/view?usp=sharing,https://drive.google.com/file/d/19ffLV4BSIdZxaqBtLEyBZzmaedn4DogM/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/j3MGHQt3E5ripU116</t>
+  </si>
+  <si>
+    <t>2°56'07.5"N 102°04'04.8"E</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1IuUenu8Z8xCeDQGerieJf59rdDYIRgXZ/view?usp=sharing,https://drive.google.com/file/d/1-BemQso3UbyuTTCRle6d5jmEa1JJuWG5/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1D8l5SldA1H9y8mWiiMteWXTZD75KBEfX/view?usp=sharing,https://drive.google.com/file/d/1opKsmaqQ99XOYsPBPTyZ57Xi5Zly4jby/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Blok Pengawal Keselamatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blok Surau </t>
+  </si>
+  <si>
+    <t>Blok Pejabat Taman Eko Rimba</t>
   </si>
 </sst>
 </file>
@@ -464,7 +476,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -564,12 +576,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -595,6 +627,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -688,11 +732,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1023,15 +1076,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -1039,13 +1092,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -1053,15 +1106,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="A3" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -1069,13 +1122,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -1093,10 +1146,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -1106,368 +1159,368 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="A6" s="23">
         <v>1</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="G6" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="24"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="23">
+        <v>2</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="C8" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="13" t="s">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="24"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="38">
+        <v>3</v>
+      </c>
+      <c r="B10" s="36" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="5" t="s">
+      <c r="C10" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
-        <v>2</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="D10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="7" t="s">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="38"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="27"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="23">
+        <v>4</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="5" t="s">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="24"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="23">
+        <v>5</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="34">
-        <v>3</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="34"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="5" t="s">
+      <c r="D14" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="24"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="38">
+        <v>6</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="23"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
-        <v>4</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="5" t="s">
+      <c r="D16" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="38"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="27"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="23">
+        <v>7</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
-        <v>5</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="34">
-        <v>6</v>
-      </c>
-      <c r="B16" s="11" t="s">
+      <c r="D18" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="34"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="23"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="19">
-        <v>7</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="23"/>
+        <v>31</v>
+      </c>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="19"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="13"/>
+      <c r="G20" s="17"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="20"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="14"/>
+      <c r="G21" s="18"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="13"/>
+      <c r="G22" s="17"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="14"/>
+      <c r="G23" s="18"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="23"/>
+      <c r="G24" s="27"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="23"/>
+      <c r="G25" s="27"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="13"/>
+      <c r="G26" s="17"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="14"/>
+      <c r="G27" s="18"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
+      <c r="A28" s="23"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="13"/>
+      <c r="G28" s="17"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="14"/>
+      <c r="G29" s="18"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="23"/>
+      <c r="G30" s="27"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="20"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="23"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="23"/>
+      <c r="G32" s="27"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="20"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="23"/>
+      <c r="G33" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="86">
@@ -1568,7 +1621,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D54FEF-B8B0-455E-9719-4EECE694A16C}">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -1584,54 +1637,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="29"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
+      <c r="A3" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="31"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="35"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1640,16 +1693,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -1658,673 +1711,719 @@
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="A6" s="23">
         <v>1</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>55</v>
+      <c r="D6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>49</v>
+      <c r="G6" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="27"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
+      <c r="A8" s="23">
         <v>2</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>55</v>
+      <c r="D8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>99</v>
+      <c r="G8" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="22"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19">
+      <c r="A10" s="23">
         <v>3</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>55</v>
+      <c r="D10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>51</v>
+      <c r="G10" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="23"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="27"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
+      <c r="A12" s="23">
         <v>4</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="13" t="s">
+      <c r="B12" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>55</v>
+      <c r="D12" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>52</v>
+      <c r="G12" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
       <c r="F13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="23"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="27"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
+      <c r="A14" s="23">
         <v>5</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="24"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="23">
+        <v>6</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" s="15" t="s">
+      <c r="G16" s="17" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19">
-        <v>6</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>98</v>
+      <c r="H16" s="20" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
       <c r="F17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="14"/>
-      <c r="H17" s="17"/>
+        <v>16</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="21"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="25"/>
+      <c r="A18" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19">
+      <c r="A20" s="23">
         <v>1</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="13" t="s">
+      <c r="B20" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>62</v>
+      <c r="D20" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H20" s="26"/>
+      <c r="G20" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="30"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="20"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
       <c r="F21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="14"/>
-      <c r="H21" s="27"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="31"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19">
+      <c r="A22" s="23">
         <v>2</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="B22" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>62</v>
+      <c r="D22" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22" s="18"/>
+      <c r="G22" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" s="22"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="22"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19">
+      <c r="A24" s="23">
         <v>3</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="13" t="s">
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="24"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="18"/>
+      <c r="H25" s="27"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="23">
+        <v>4</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="24"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H24" s="18" t="s">
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="23">
+        <v>5</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G25" s="14"/>
-      <c r="H25" s="23"/>
-    </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19">
-        <v>4</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="C28" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="G26" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H26" s="42" t="s">
+      <c r="G28" s="17" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="5" t="s">
+      <c r="H28" s="19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="24"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="43"/>
-    </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="19">
-        <v>5</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F28" s="7" t="s">
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="41"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="45"/>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="41"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="45"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="41"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="45"/>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="41"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="45"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="41"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="45"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="41"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="45"/>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="29"/>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="23">
+        <v>1</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H38" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="24"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G39" s="18"/>
+      <c r="H39" s="31"/>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="23">
+        <v>2</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="G40" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H40" s="22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="24"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G41" s="18"/>
+      <c r="H41" s="22"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="23">
+        <v>3</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H42" s="22" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-    </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="37"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="41"/>
-    </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="37"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="41"/>
-    </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="37"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="41"/>
-    </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="37"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="41"/>
-    </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="41"/>
-    </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="41"/>
-    </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="24" t="s">
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="24"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G43" s="18"/>
+      <c r="H43" s="27"/>
+    </row>
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="11"/>
+      <c r="B44" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="25"/>
-    </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="24"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="25"/>
-    </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="19">
-        <v>1</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="H38" s="26"/>
-    </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="27"/>
-    </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19">
-        <v>2</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="18"/>
-    </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" s="14"/>
-      <c r="H41" s="18"/>
-    </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19">
-        <v>3</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="18"/>
-    </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="20"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G43" s="14"/>
-      <c r="H43" s="23"/>
-    </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="19">
-        <v>4</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" s="9"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="13"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="20"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="14"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="26"/>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
-      <c r="F45" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G45" s="14"/>
-      <c r="H45" s="10"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="13"/>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="46"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="50"/>
+      <c r="H46" s="13"/>
+    </row>
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="46"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="13"/>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="23">
+        <v>4</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F48" s="6"/>
+      <c r="G48" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H48" s="9"/>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="24"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="108">
+  <mergeCells count="112">
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="C28:C29"/>
@@ -2399,7 +2498,7 @@
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="D26:D27"/>
     <mergeCell ref="E26:E27"/>
-    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A48:A49"/>
     <mergeCell ref="A36:H37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="B38:B39"/>
@@ -2408,6 +2507,10 @@
     <mergeCell ref="E38:E39"/>
     <mergeCell ref="G38:G39"/>
     <mergeCell ref="H38:H39"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
     <mergeCell ref="C40:C41"/>
@@ -2418,13 +2521,13 @@
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="D42:D43"/>
     <mergeCell ref="E42:E43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
     <mergeCell ref="H14:H15"/>
     <mergeCell ref="H16:H17"/>
-    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G48:G49"/>
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="G42:G43"/>
@@ -2448,20 +2551,19 @@
     <hyperlink ref="F17" r:id="rId10" xr:uid="{C9F8004F-2006-467E-A196-CFC9352C9B68}"/>
     <hyperlink ref="F21" r:id="rId11" xr:uid="{8A41AEDD-00D6-4798-BE58-4F607596CE5E}"/>
     <hyperlink ref="F23" r:id="rId12" xr:uid="{62B78FFF-77DC-444D-90D0-1CA894377B57}"/>
-    <hyperlink ref="F39" r:id="rId13" xr:uid="{00C82A6F-2C18-41D2-89AA-3C1C7095F3DC}"/>
-    <hyperlink ref="F41" r:id="rId14" xr:uid="{18FA63F7-AA33-4E60-A540-013BDF8F175E}"/>
-    <hyperlink ref="F43" r:id="rId15" xr:uid="{01447622-ADCD-4E8E-87E8-BDA8D1ADD1BF}"/>
-    <hyperlink ref="F45" r:id="rId16" xr:uid="{031E33FD-D835-47FF-B82E-B6EBE7FB15DD}"/>
-    <hyperlink ref="H14" r:id="rId17" xr:uid="{6E25EBC1-DB77-4A7C-9B61-5D225D82B96F}"/>
-    <hyperlink ref="H16" r:id="rId18" xr:uid="{DC41D252-5B6D-49F4-B013-CBB47E46599C}"/>
-    <hyperlink ref="H24" r:id="rId19" xr:uid="{DAD5F602-20B1-420C-A71A-F100947483DF}"/>
-    <hyperlink ref="H26" r:id="rId20" xr:uid="{D31AC8CF-A4BB-4C9E-B22B-29F22A8F60A5}"/>
-    <hyperlink ref="H28" r:id="rId21" xr:uid="{151049AE-803B-48F6-BBC4-0E67775E894B}"/>
+    <hyperlink ref="H14" r:id="rId13" xr:uid="{6E25EBC1-DB77-4A7C-9B61-5D225D82B96F}"/>
+    <hyperlink ref="H16" r:id="rId14" xr:uid="{DC41D252-5B6D-49F4-B013-CBB47E46599C}"/>
+    <hyperlink ref="H24" r:id="rId15" xr:uid="{DAD5F602-20B1-420C-A71A-F100947483DF}"/>
+    <hyperlink ref="H26" r:id="rId16" xr:uid="{D31AC8CF-A4BB-4C9E-B22B-29F22A8F60A5}"/>
+    <hyperlink ref="H28" r:id="rId17" xr:uid="{151049AE-803B-48F6-BBC4-0E67775E894B}"/>
+    <hyperlink ref="H38" r:id="rId18" xr:uid="{996CE196-A38F-4809-96BC-C29C09152A5F}"/>
+    <hyperlink ref="H40" r:id="rId19" xr:uid="{465C1FFD-FC17-4DCC-B800-9D541E2DFD49}"/>
+    <hyperlink ref="H42" r:id="rId20" xr:uid="{8037C977-2882-407E-8610-AA6EA33F1A19}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId22"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId21"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="51" max="7" man="1"/>
+    <brk id="55" max="7" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2481,15 +2583,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2497,13 +2599,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2511,15 +2613,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="A3" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2527,13 +2629,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2551,10 +2653,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -2564,72 +2666,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="A6" s="23">
         <v>1</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="24"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="23">
+        <v>2</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
-        <v>2</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>47</v>
+      <c r="G8" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="14"/>
+        <v>26</v>
+      </c>
+      <c r="G9" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2671,15 +2773,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2687,13 +2789,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2701,15 +2803,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="A3" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2717,13 +2819,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2741,10 +2843,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -2754,276 +2856,276 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="A6" s="23">
         <v>1</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="24"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="23">
+        <v>2</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
-        <v>2</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>47</v>
+      <c r="G8" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="14"/>
+        <v>26</v>
+      </c>
+      <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="19">
+      <c r="A10" s="23">
         <v>3</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>60</v>
+      <c r="B10" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>47</v>
+        <v>29</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="23">
+        <v>4</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="24"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="23">
+        <v>5</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="24"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="23">
+        <v>6</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
-        <v>4</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
-        <v>5</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="5" t="s">
+      <c r="C16" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="24"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="23">
+        <v>7</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="24"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="23">
+        <v>8</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="19">
-        <v>6</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="19">
-        <v>7</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="19">
-        <v>8</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="20"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G21" s="14"/>
+      <c r="G21" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -3099,15 +3201,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3115,13 +3217,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3129,15 +3231,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="A3" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3145,13 +3247,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3169,10 +3271,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3182,174 +3284,174 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="A6" s="23">
         <v>1</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="24"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="23">
+        <v>2</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
-        <v>2</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>47</v>
+      <c r="G8" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="14"/>
+        <v>26</v>
+      </c>
+      <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="19">
+      <c r="A10" s="23">
         <v>3</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>60</v>
+      <c r="B10" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>47</v>
+        <v>29</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="14"/>
+        <v>26</v>
+      </c>
+      <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
+      <c r="A12" s="23">
         <v>4</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>60</v>
+      <c r="B12" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>47</v>
+        <v>29</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
       <c r="F13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="14"/>
+        <v>26</v>
+      </c>
+      <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
+      <c r="A14" s="23">
         <v>5</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>60</v>
+      <c r="B14" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>47</v>
+        <v>29</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
       <c r="F15" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="14"/>
+        <v>81</v>
+      </c>
+      <c r="G15" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -3410,15 +3512,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3426,13 +3528,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3440,15 +3542,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="A3" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3456,13 +3558,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3480,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3493,106 +3595,106 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="A6" s="23">
         <v>1</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>55</v>
+      <c r="B6" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="13" t="s">
         <v>29</v>
       </c>
+      <c r="G6" s="17" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="14"/>
+        <v>26</v>
+      </c>
+      <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
+      <c r="A8" s="23">
         <v>2</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>55</v>
+      <c r="B8" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>47</v>
+        <v>29</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="14"/>
+        <v>26</v>
+      </c>
+      <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="19">
+      <c r="A10" s="23">
         <v>3</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>55</v>
+      <c r="B10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>47</v>
+        <v>29</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="14"/>
+        <v>81</v>
+      </c>
+      <c r="G11" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -3641,54 +3743,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="29"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
+      <c r="A3" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="31"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="35"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -3697,16 +3799,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3715,420 +3817,420 @@
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="A6" s="23">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>55</v>
+      <c r="D6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>50</v>
+      <c r="G6" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="23"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
+      <c r="A8" s="23">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="21" t="s">
+      <c r="B8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="17" t="s">
         <v>19</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>21</v>
       </c>
       <c r="H8" s="9"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="14"/>
+        <v>16</v>
+      </c>
+      <c r="G9" s="18"/>
       <c r="H9" s="10"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19">
+      <c r="A10" s="23">
         <v>8</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="39"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="36"/>
+        <v>16</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="H11" s="40"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="25"/>
+      <c r="A12" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="25"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="29"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
+      <c r="A14" s="23">
         <v>5</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="13" t="s">
+      <c r="B14" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>62</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>50</v>
+      <c r="G14" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
       <c r="F15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="23"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="27"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19">
+      <c r="A16" s="23">
         <v>7</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="13" t="s">
+      <c r="B16" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>62</v>
       </c>
+      <c r="D16" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>58</v>
+      </c>
       <c r="F16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="17" t="s">
         <v>19</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>21</v>
       </c>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
       <c r="F17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="14"/>
+        <v>16</v>
+      </c>
+      <c r="G17" s="18"/>
       <c r="H17" s="10"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19">
+      <c r="A18" s="23">
         <v>8</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="35"/>
+      <c r="H18" s="39"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="36"/>
+        <v>16</v>
+      </c>
+      <c r="G19" s="18"/>
+      <c r="H19" s="40"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="25"/>
+      <c r="A20" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="29"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="25"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="29"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19">
+      <c r="A22" s="23">
         <v>5</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="13" t="s">
+      <c r="B22" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="25" t="s">
         <v>77</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>73</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>50</v>
+      <c r="G22" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="23"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="27"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19">
+      <c r="A24" s="23">
         <v>7</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>77</v>
+      <c r="B24" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>73</v>
       </c>
       <c r="F24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="17" t="s">
         <v>19</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>21</v>
       </c>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="14"/>
+        <v>16</v>
+      </c>
+      <c r="G25" s="18"/>
       <c r="H25" s="10"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19">
+      <c r="A26" s="23">
         <v>8</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="35"/>
+      <c r="H26" s="39"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
       <c r="F27" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="36"/>
+        <v>16</v>
+      </c>
+      <c r="G27" s="18"/>
+      <c r="H27" s="40"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8703AC6-A12F-4FC9-8674-B5655F776C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D7A7B3-DC4F-46DA-AF43-D26039A8EE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="127">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -106,9 +106,6 @@
     <t>2°48'33.0"N 102°23'33.8"E</t>
   </si>
   <si>
-    <t>Blok Kuarters kakitangan</t>
-  </si>
-  <si>
     <t>Dalam Keadaan Baik Dan Diduduki / Bangunan Kuarters</t>
   </si>
   <si>
@@ -340,9 +337,6 @@
     <t>https://drive.google.com/file/d/1CrucTqd84gbfVuo2rxZipDmqLKE7DS48/view?usp=sharing,https://drive.google.com/file/d/1iOJJh7hBj8CBX4rzlIhrRfc3neU3EIjt/view?usp=sharing</t>
   </si>
   <si>
-    <t>Dalam Penambahbaikkan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dalam Keadaan Baik Dan Diduduki </t>
   </si>
   <si>
@@ -410,6 +404,33 @@
   </si>
   <si>
     <t>Blok Pejabat Taman Eko Rimba</t>
+  </si>
+  <si>
+    <t>Dalam Proses Penyelenggaraan &amp; Penambahbaikan</t>
+  </si>
+  <si>
+    <t>Blok Kuarters kakitangan 1 Renj Jempol</t>
+  </si>
+  <si>
+    <t>Blok Kuarters kakitangan 2 Renj Jempol</t>
+  </si>
+  <si>
+    <t>Blok Kuarters kakitangan 1 Renj Gemencheh</t>
+  </si>
+  <si>
+    <t>Blok Kuarters kakitangan 2 Renj Gemencheh</t>
+  </si>
+  <si>
+    <t>Blok Kuarters kakitangan 3 Renj Gemencheh</t>
+  </si>
+  <si>
+    <t>Blok Kuarters kakitangan 1 Simpang Pertang</t>
+  </si>
+  <si>
+    <t>Blok Kuarters kakitangan 2 Simpang Pertang</t>
+  </si>
+  <si>
+    <t>Blok Kuarters kakitangan 3 Simpang Pertang</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1128,7 @@
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -1146,10 +1167,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -1163,22 +1184,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>33</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1188,7 +1209,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="18"/>
     </row>
@@ -1197,22 +1218,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="17" t="s">
         <v>33</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1222,7 +1243,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="18"/>
     </row>
@@ -1231,22 +1252,22 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="27" t="s">
         <v>36</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1256,7 +1277,7 @@
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="27"/>
     </row>
@@ -1265,22 +1286,22 @@
         <v>4</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="17" t="s">
         <v>33</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -1290,7 +1311,7 @@
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" s="18"/>
     </row>
@@ -1299,22 +1320,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="17" t="s">
         <v>39</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1324,7 +1345,7 @@
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" s="18"/>
     </row>
@@ -1333,22 +1354,22 @@
         <v>6</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1358,7 +1379,7 @@
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" s="27"/>
     </row>
@@ -1367,22 +1388,22 @@
         <v>7</v>
       </c>
       <c r="B18" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="27" t="s">
         <v>42</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -1392,7 +1413,7 @@
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="27"/>
     </row>
@@ -1664,7 +1685,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -1693,16 +1714,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -1711,7 +1732,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1725,19 +1746,19 @@
         <v>8</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1763,19 +1784,19 @@
         <v>8</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1795,25 +1816,25 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1833,25 +1854,25 @@
         <v>4</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1877,19 +1898,19 @@
         <v>15</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1909,25 +1930,25 @@
         <v>6</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1944,7 +1965,7 @@
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
@@ -1969,22 +1990,22 @@
         <v>1</v>
       </c>
       <c r="B20" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>60</v>
-      </c>
       <c r="E20" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H20" s="30"/>
     </row>
@@ -2005,22 +2026,22 @@
         <v>2</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H22" s="22"/>
     </row>
@@ -2041,25 +2062,25 @@
         <v>3</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C24" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>102</v>
-      </c>
       <c r="G24" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2069,7 +2090,7 @@
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
       <c r="F25" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G25" s="18"/>
       <c r="H25" s="27"/>
@@ -2079,25 +2100,25 @@
         <v>4</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2107,7 +2128,7 @@
       <c r="D27" s="18"/>
       <c r="E27" s="18"/>
       <c r="F27" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
@@ -2117,25 +2138,25 @@
         <v>5</v>
       </c>
       <c r="B28" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F28" s="7" t="s">
+      <c r="G28" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H28" s="19" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2145,7 +2166,7 @@
       <c r="D29" s="18"/>
       <c r="E29" s="18"/>
       <c r="F29" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
@@ -2212,7 +2233,7 @@
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
@@ -2237,25 +2258,25 @@
         <v>1</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H38" s="30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2265,7 +2286,7 @@
       <c r="D39" s="18"/>
       <c r="E39" s="18"/>
       <c r="F39" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G39" s="18"/>
       <c r="H39" s="31"/>
@@ -2275,25 +2296,25 @@
         <v>2</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F40" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H40" s="22" t="s">
         <v>114</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H40" s="22" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2303,7 +2324,7 @@
       <c r="D41" s="18"/>
       <c r="E41" s="18"/>
       <c r="F41" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G41" s="18"/>
       <c r="H41" s="22"/>
@@ -2313,25 +2334,25 @@
         <v>3</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2341,7 +2362,7 @@
       <c r="D43" s="18"/>
       <c r="E43" s="18"/>
       <c r="F43" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G43" s="18"/>
       <c r="H43" s="27"/>
@@ -2349,10 +2370,10 @@
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
       <c r="B44" s="15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
@@ -2395,16 +2416,16 @@
         <v>4</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="17" t="s">
@@ -2614,7 +2635,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -2653,10 +2674,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -2670,22 +2691,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25" t="s">
-        <v>25</v>
-      </c>
       <c r="D6" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -2695,7 +2716,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="18"/>
     </row>
@@ -2704,22 +2725,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="G8" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -2729,7 +2750,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" s="18"/>
     </row>
@@ -2804,7 +2825,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -2843,10 +2864,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -2860,22 +2881,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="E6" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -2885,7 +2906,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="18"/>
     </row>
@@ -2894,22 +2915,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="E8" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -2919,7 +2940,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" s="18"/>
     </row>
@@ -2928,22 +2949,22 @@
         <v>3</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="E10" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -2953,7 +2974,7 @@
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11" s="18"/>
     </row>
@@ -2962,22 +2983,22 @@
         <v>4</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="E12" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -2987,7 +3008,7 @@
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G13" s="18"/>
     </row>
@@ -2996,22 +3017,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="E14" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -3021,7 +3042,7 @@
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G15" s="18"/>
     </row>
@@ -3030,22 +3051,22 @@
         <v>6</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="E16" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -3055,7 +3076,7 @@
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G17" s="18"/>
     </row>
@@ -3064,22 +3085,22 @@
         <v>7</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="E18" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -3089,7 +3110,7 @@
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G19" s="18"/>
     </row>
@@ -3098,22 +3119,22 @@
         <v>8</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C20" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="E20" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -3123,7 +3144,7 @@
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
       <c r="F21" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G21" s="18"/>
     </row>
@@ -3232,7 +3253,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -3271,10 +3292,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3288,22 +3309,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -3313,7 +3334,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="18"/>
     </row>
@@ -3322,22 +3343,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3347,7 +3368,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" s="18"/>
     </row>
@@ -3356,22 +3377,22 @@
         <v>3</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3381,7 +3402,7 @@
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="18"/>
     </row>
@@ -3390,22 +3411,22 @@
         <v>4</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -3415,7 +3436,7 @@
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" s="18"/>
     </row>
@@ -3424,22 +3445,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -3449,7 +3470,7 @@
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G15" s="18"/>
     </row>
@@ -3543,7 +3564,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -3582,10 +3603,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3599,22 +3620,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -3624,7 +3645,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="18"/>
     </row>
@@ -3633,22 +3654,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3658,7 +3679,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" s="18"/>
     </row>
@@ -3667,22 +3688,22 @@
         <v>3</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3692,7 +3713,7 @@
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11" s="18"/>
     </row>
@@ -3770,7 +3791,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -3799,16 +3820,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3817,7 +3838,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3831,10 +3852,10 @@
         <v>8</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
@@ -3843,7 +3864,7 @@
         <v>13</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3863,22 +3884,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H8" s="9"/>
       <c r="K8" s="2"/>
@@ -3903,22 +3924,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H10" s="39"/>
       <c r="K10" s="2"/>
@@ -3940,7 +3961,7 @@
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="28"/>
       <c r="C12" s="28"/>
@@ -3969,16 +3990,16 @@
         <v>5</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
@@ -3987,7 +4008,7 @@
         <v>13</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -4011,22 +4032,22 @@
         <v>7</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
@@ -4051,22 +4072,22 @@
         <v>8</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H18" s="39"/>
       <c r="K18" s="2"/>
@@ -4088,7 +4109,7 @@
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
@@ -4117,16 +4138,16 @@
         <v>5</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
@@ -4135,7 +4156,7 @@
         <v>13</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -4159,22 +4180,22 @@
         <v>7</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
@@ -4199,22 +4220,22 @@
         <v>8</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H26" s="39"/>
       <c r="K26" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D7A7B3-DC4F-46DA-AF43-D26039A8EE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109B076B-E5A5-4565-823F-8D91CD27239B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="136">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -112,9 +112,6 @@
     <t>Dalam Keadaan Baik Dan Tidak Diduduki / Bangunan Kuarters</t>
   </si>
   <si>
-    <t>Blok Bilik Mesyuarat</t>
-  </si>
-  <si>
     <t>Kuala Pilah</t>
   </si>
   <si>
@@ -139,9 +136,6 @@
     <t>2°45'32.6"N 102°15'10.0"E</t>
   </si>
   <si>
-    <t>Blok Tandas 1</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/v7rucZ23Gzn931dv9</t>
   </si>
   <si>
@@ -154,30 +148,15 @@
     <t>Dalam Keadaan Baik Dan Diguna Pakai  / Blok Tandas</t>
   </si>
   <si>
-    <t>Blok Tandas 2</t>
-  </si>
-  <si>
-    <t>Blok Surau Terbuka</t>
-  </si>
-  <si>
     <t>Dalam Keadaan Baik Dan Diguna Pakai  / Blok Surau Terbuka</t>
   </si>
   <si>
-    <t>Blok Tandas 3</t>
-  </si>
-  <si>
-    <t>Blok Asrama</t>
-  </si>
-  <si>
     <t>Dalam Keadaan Baik Dan Diguna Pakai  / Blok Penginapan Asrama</t>
   </si>
   <si>
     <t>Dalam Keadaan Baik Dan Diguna Pakai  / Blok Pejabat</t>
   </si>
   <si>
-    <t xml:space="preserve">Blok Bangunan Gerai </t>
-  </si>
-  <si>
     <t>Dalam Keadaan Baik Dan Tidak Diguna Pakai  / Blok Pejabat</t>
   </si>
   <si>
@@ -208,9 +187,6 @@
     <t>PHDNST</t>
   </si>
   <si>
-    <t xml:space="preserve">Blok Bilik Mesyuarat </t>
-  </si>
-  <si>
     <t>Perkara</t>
   </si>
   <si>
@@ -289,24 +265,9 @@
     <t>Bangunan Kaunter Tiket</t>
   </si>
   <si>
-    <t>Blok Tandas</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q10</t>
   </si>
   <si>
-    <t>Blok Bangunan Utama</t>
-  </si>
-  <si>
-    <t>Blok Kafeteria</t>
-  </si>
-  <si>
-    <t>Blok Garaj</t>
-  </si>
-  <si>
-    <t>Blok Surau</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q11</t>
   </si>
   <si>
@@ -319,15 +280,9 @@
     <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q14</t>
   </si>
   <si>
-    <t>Blok Kaunter Tiket</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q15</t>
   </si>
   <si>
-    <t>Blok Pejabat</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1D9YJMnMNMP2_VRcyXpY4PgZV8tHBMhty/view?usp=sharing,https://drive.google.com/file/d/13-gnjk2D5kvvgutQZ6busAoul0JsiSoH/view?usp=sharing</t>
   </si>
   <si>
@@ -397,12 +352,6 @@
     <t>https://drive.google.com/file/d/1D8l5SldA1H9y8mWiiMteWXTZD75KBEfX/view?usp=sharing,https://drive.google.com/file/d/1opKsmaqQ99XOYsPBPTyZ57Xi5Zly4jby/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve"> Blok Pengawal Keselamatan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blok Surau </t>
-  </si>
-  <si>
     <t>Blok Pejabat Taman Eko Rimba</t>
   </si>
   <si>
@@ -431,6 +380,84 @@
   </si>
   <si>
     <t>Blok Kuarters kakitangan 3 Simpang Pertang</t>
+  </si>
+  <si>
+    <t>Blok Tandas 1 Kaunter Tiket Gunung Angsi</t>
+  </si>
+  <si>
+    <t>Blok Tandas 2 Kaunter Tiket Gunung Angsi</t>
+  </si>
+  <si>
+    <t>Blok Pengawal Keselamatan PD Forest</t>
+  </si>
+  <si>
+    <t>Blok Surau PD Forest</t>
+  </si>
+  <si>
+    <t>Blok Tandas 1 TER Tengkek</t>
+  </si>
+  <si>
+    <t>Blok Tandas 2 TER Tengkek</t>
+  </si>
+  <si>
+    <t>Blok Surau Terbuka TER Tengkek</t>
+  </si>
+  <si>
+    <t>Blok Tandas 3 TER Tengkek</t>
+  </si>
+  <si>
+    <t>Blok Asrama TER Tengkek</t>
+  </si>
+  <si>
+    <t>Blok Bangunan Gerai TER Tengkek</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Blok Pengawal Keselamatan PHDNSU</t>
+  </si>
+  <si>
+    <t>Blok Surau PHDNSU</t>
+  </si>
+  <si>
+    <t>Blok Bilik Mesyuarat PHDNST</t>
+  </si>
+  <si>
+    <t>Blok Pengawal Keselamatan PHDNST</t>
+  </si>
+  <si>
+    <t>Blok Bilik Mesyuarat Renj Jempol</t>
+  </si>
+  <si>
+    <t>Blok Pengawal Keselamatan TNK</t>
+  </si>
+  <si>
+    <t>Blok Kaunter Tiket TNK</t>
+  </si>
+  <si>
+    <t>Blok Asrama TNK</t>
+  </si>
+  <si>
+    <t>Blok Bilik Mesyuarat TNK</t>
+  </si>
+  <si>
+    <t>Blok Kafeteria TNK</t>
+  </si>
+  <si>
+    <t>Blok Surau TNK</t>
+  </si>
+  <si>
+    <t>Blok Tandas 1 TNK</t>
+  </si>
+  <si>
+    <t>Blok Pejabat TNK</t>
+  </si>
+  <si>
+    <t>Blok Bangunan Utama PD Forest</t>
+  </si>
+  <si>
+    <t>Blok Kafeteria PD Forest</t>
+  </si>
+  <si>
+    <t>Blok Garaj PD Forest</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1155,7 @@
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -1167,10 +1194,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -1184,22 +1211,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="17" t="s">
         <v>31</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1209,7 +1236,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G7" s="18"/>
     </row>
@@ -1218,22 +1245,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="17" t="s">
         <v>31</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1243,7 +1270,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G9" s="18"/>
     </row>
@@ -1252,22 +1279,22 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="C10" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="27" t="s">
         <v>32</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1277,7 +1304,7 @@
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G11" s="27"/>
     </row>
@@ -1286,22 +1313,22 @@
         <v>4</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="17" t="s">
         <v>31</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -1311,7 +1338,7 @@
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G13" s="18"/>
     </row>
@@ -1320,22 +1347,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1345,7 +1372,7 @@
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G15" s="18"/>
     </row>
@@ -1354,22 +1381,22 @@
         <v>6</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1379,7 +1406,7 @@
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G17" s="27"/>
     </row>
@@ -1388,22 +1415,22 @@
         <v>7</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -1413,7 +1440,7 @@
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G19" s="27"/>
     </row>
@@ -1685,7 +1712,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -1714,16 +1741,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -1732,7 +1759,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1746,19 +1773,19 @@
         <v>8</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1784,19 +1811,19 @@
         <v>8</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1816,25 +1843,25 @@
         <v>3</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1854,25 +1881,25 @@
         <v>4</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1898,19 +1925,19 @@
         <v>15</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1930,25 +1957,25 @@
         <v>6</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1965,7 +1992,7 @@
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="28" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
@@ -1990,22 +2017,22 @@
         <v>1</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="H20" s="30"/>
     </row>
@@ -2026,22 +2053,22 @@
         <v>2</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="H22" s="22"/>
     </row>
@@ -2062,25 +2089,25 @@
         <v>3</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2090,7 +2117,7 @@
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
       <c r="F25" s="5" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="G25" s="18"/>
       <c r="H25" s="27"/>
@@ -2100,25 +2127,25 @@
         <v>4</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2128,7 +2155,7 @@
       <c r="D27" s="18"/>
       <c r="E27" s="18"/>
       <c r="F27" s="5" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
@@ -2138,25 +2165,25 @@
         <v>5</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2166,7 +2193,7 @@
       <c r="D29" s="18"/>
       <c r="E29" s="18"/>
       <c r="F29" s="5" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
@@ -2233,7 +2260,7 @@
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="28" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
@@ -2258,25 +2285,25 @@
         <v>1</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="H38" s="30" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2286,7 +2313,7 @@
       <c r="D39" s="18"/>
       <c r="E39" s="18"/>
       <c r="F39" s="5" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G39" s="18"/>
       <c r="H39" s="31"/>
@@ -2296,25 +2323,25 @@
         <v>2</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2324,7 +2351,7 @@
       <c r="D41" s="18"/>
       <c r="E41" s="18"/>
       <c r="F41" s="5" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G41" s="18"/>
       <c r="H41" s="22"/>
@@ -2334,25 +2361,25 @@
         <v>3</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2362,7 +2389,7 @@
       <c r="D43" s="18"/>
       <c r="E43" s="18"/>
       <c r="F43" s="5" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G43" s="18"/>
       <c r="H43" s="27"/>
@@ -2370,10 +2397,10 @@
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
       <c r="B44" s="15" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
@@ -2416,16 +2443,16 @@
         <v>4</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="17" t="s">
@@ -2635,7 +2662,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -2674,10 +2701,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -2691,22 +2718,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="25" t="s">
-        <v>24</v>
-      </c>
       <c r="D6" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -2716,7 +2743,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" s="18"/>
     </row>
@@ -2725,22 +2752,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="G8" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -2750,7 +2777,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="18"/>
     </row>
@@ -2825,7 +2852,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -2864,10 +2891,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -2881,22 +2908,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -2906,7 +2933,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" s="18"/>
     </row>
@@ -2915,22 +2942,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -2940,7 +2967,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="18"/>
     </row>
@@ -2949,22 +2976,22 @@
         <v>3</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -2974,7 +3001,7 @@
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G11" s="18"/>
     </row>
@@ -2983,22 +3010,22 @@
         <v>4</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -3008,7 +3035,7 @@
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="5" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="G13" s="18"/>
     </row>
@@ -3017,22 +3044,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -3042,7 +3069,7 @@
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G15" s="18"/>
     </row>
@@ -3051,22 +3078,22 @@
         <v>6</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -3076,7 +3103,7 @@
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G17" s="18"/>
     </row>
@@ -3085,22 +3112,22 @@
         <v>7</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -3110,7 +3137,7 @@
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="5" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G19" s="18"/>
     </row>
@@ -3119,22 +3146,22 @@
         <v>8</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -3144,7 +3171,7 @@
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
       <c r="F21" s="5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G21" s="18"/>
     </row>
@@ -3253,7 +3280,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -3292,10 +3319,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3309,22 +3336,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -3334,7 +3361,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" s="18"/>
     </row>
@@ -3343,22 +3370,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3368,7 +3395,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="18"/>
     </row>
@@ -3377,22 +3404,22 @@
         <v>3</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3402,7 +3429,7 @@
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="18"/>
     </row>
@@ -3411,22 +3438,22 @@
         <v>4</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -3436,7 +3463,7 @@
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G13" s="18"/>
     </row>
@@ -3445,22 +3472,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -3470,7 +3497,7 @@
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="5" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G15" s="18"/>
     </row>
@@ -3564,7 +3591,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -3603,10 +3630,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3620,22 +3647,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -3645,7 +3672,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" s="18"/>
     </row>
@@ -3654,22 +3681,22 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3679,7 +3706,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="18"/>
     </row>
@@ -3688,22 +3715,22 @@
         <v>3</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3713,7 +3740,7 @@
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="5" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G11" s="18"/>
     </row>
@@ -3791,7 +3818,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -3820,16 +3847,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3838,7 +3865,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3852,10 +3879,10 @@
         <v>8</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
@@ -3864,7 +3891,7 @@
         <v>13</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3884,16 +3911,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>17</v>
@@ -3924,16 +3951,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>17</v>
@@ -3961,7 +3988,7 @@
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="28" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B12" s="28"/>
       <c r="C12" s="28"/>
@@ -3990,16 +4017,16 @@
         <v>5</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
@@ -4008,7 +4035,7 @@
         <v>13</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -4032,16 +4059,16 @@
         <v>7</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
@@ -4072,16 +4099,16 @@
         <v>8</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>17</v>
@@ -4109,7 +4136,7 @@
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="28" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
@@ -4138,16 +4165,16 @@
         <v>5</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
@@ -4156,7 +4183,7 @@
         <v>13</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -4180,16 +4207,16 @@
         <v>7</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>17</v>
@@ -4220,16 +4247,16 @@
         <v>8</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>17</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109B076B-E5A5-4565-823F-8D91CD27239B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B5E9AD-0207-42FA-8921-E4EA513C35A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$75</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$H$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negeri Kenaboi'!$A$1:$G$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="136">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -145,21 +145,6 @@
     <t>Kg Tengkek, Batu Kikir</t>
   </si>
   <si>
-    <t>Dalam Keadaan Baik Dan Diguna Pakai  / Blok Tandas</t>
-  </si>
-  <si>
-    <t>Dalam Keadaan Baik Dan Diguna Pakai  / Blok Surau Terbuka</t>
-  </si>
-  <si>
-    <t>Dalam Keadaan Baik Dan Diguna Pakai  / Blok Penginapan Asrama</t>
-  </si>
-  <si>
-    <t>Dalam Keadaan Baik Dan Diguna Pakai  / Blok Pejabat</t>
-  </si>
-  <si>
-    <t>Dalam Keadaan Baik Dan Tidak Diguna Pakai  / Blok Pejabat</t>
-  </si>
-  <si>
     <t>Bangunan Digunakan</t>
   </si>
   <si>
@@ -458,6 +443,21 @@
   </si>
   <si>
     <t>Blok Garaj PD Forest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalam Keadaan Baik Dan Diguna Pakai </t>
+  </si>
+  <si>
+    <t>Dalam Keadaan Baik Dan Diguna Pakai</t>
+  </si>
+  <si>
+    <t>Dalam Keadaan Baik Dan Tidak Diguna Pakai</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-L3CNy2gkeuaMnbhqt0l33UL4FMto5eH/view?usp=sharing,https://drive.google.com/file/d/16XGy9sR2a0oiokqPSBaqFLgbo9fCnNG3/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1AkRQqdkMOvYudE11K9rValJUxH-2RD_D/view?usp=sharing,https://drive.google.com/file/d/12cJUBgEnt2r0L3wtz7pAUko8bxqrxJil/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -649,7 +649,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -687,6 +687,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -699,6 +738,54 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -708,92 +795,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1110,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76EB4F4A-ECE0-4AF1-B89E-C181A1ABEC5E}">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -1119,65 +1122,66 @@
     <col min="5" max="5" width="16.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="51.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="43.140625" style="2" customWidth="1"/>
-    <col min="8" max="12" width="9.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="59.42578125" style="2" customWidth="1"/>
+    <col min="9" max="12" width="9.5703125" style="2" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="3"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="3"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="3"/>
+      <c r="A3" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="1"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1194,10 +1198,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -1205,373 +1209,584 @@
       <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="H5" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="23">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="25" t="s">
+      <c r="B6" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>44</v>
+      <c r="E6" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>31</v>
+      <c r="G6" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="18"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="23">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="25" t="s">
+      <c r="B8" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>44</v>
+      <c r="E8" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>31</v>
+      <c r="G8" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="18"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="38">
+      <c r="A10" s="42">
         <v>3</v>
       </c>
-      <c r="B10" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="27" t="s">
+      <c r="B10" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>44</v>
+      <c r="E10" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="27" t="s">
-        <v>32</v>
-      </c>
+      <c r="G10" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H10" s="32"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="38"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="42"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="23">
+      <c r="A12" s="26">
         <v>4</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="25" t="s">
+      <c r="B12" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="17" t="s">
-        <v>44</v>
+      <c r="E12" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="17" t="s">
-        <v>31</v>
-      </c>
+      <c r="G12" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="18"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="33"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="23">
+      <c r="A14" s="26">
         <v>5</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="25" t="s">
+      <c r="B14" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="17" t="s">
-        <v>44</v>
+      <c r="E14" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>33</v>
-      </c>
+      <c r="G14" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="48"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
       <c r="F15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="18"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="38">
+      <c r="A16" s="42">
         <v>6</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="27" t="s">
+      <c r="B16" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>44</v>
+      <c r="E16" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="38"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="G16" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="49"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="42"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="27"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="23">
+      <c r="G17" s="33"/>
+      <c r="H17" s="50"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="26">
         <v>7</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" s="27" t="s">
+      <c r="B18" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>44</v>
+      <c r="E18" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="G18" s="33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="27"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
       <c r="F19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="27"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="G19" s="33"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="17"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="45"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="27"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="18"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="23"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="46"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="26"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="17"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="32"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="27"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="32"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="26"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="27"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="24"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="32"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="27"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="27"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="23"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="26"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="17"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="24"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="48"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="27"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="26"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="17"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="24"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="48"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="27"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="23"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="26"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="27"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="24"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="19"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="27"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="27"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="19"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="26"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="27"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="24"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="19"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="27"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="27"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="19"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H34" s="19"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H35" s="19"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="51"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="51"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="51"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="51"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="51"/>
+      <c r="J46" s="51"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="51"/>
+      <c r="J47" s="51"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G48" s="51"/>
+      <c r="H48" s="51"/>
+      <c r="I48" s="51"/>
+      <c r="J48" s="51"/>
+    </row>
+    <row r="49" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G49" s="51"/>
+      <c r="H49" s="51"/>
+      <c r="I49" s="51"/>
+      <c r="J49" s="51"/>
+    </row>
+    <row r="50" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G50" s="51"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="51"/>
+      <c r="J50" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="86">
+  <mergeCells count="98">
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G36:J50"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="E18:E19"/>
@@ -1588,81 +1803,16 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A3:G4"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D20:D21"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{08DF4C9A-9F75-4524-A39E-D32455244FE2}"/>
+    <hyperlink ref="H6" r:id="rId2" xr:uid="{0E376E79-FCE9-48B0-8EAF-4D83CAA38CDB}"/>
+    <hyperlink ref="H8" r:id="rId3" xr:uid="{155D159D-7B91-4625-A34E-FB6AA605219D}"/>
+  </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId4"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="19" max="5" man="1"/>
+    <brk id="19" max="7" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1685,54 +1835,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="39"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="39"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="29"/>
+      <c r="A3" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="37"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="41"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1741,16 +1891,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -1759,719 +1909,807 @@
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>44</v>
+      <c r="E6" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>38</v>
+      <c r="G6" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="45" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="23">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>44</v>
+      <c r="E8" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="22" t="s">
-        <v>79</v>
+      <c r="G8" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="22"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23">
+      <c r="A10" s="26">
         <v>3</v>
       </c>
-      <c r="B10" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>44</v>
+      <c r="E10" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>40</v>
+      <c r="G10" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="27"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="23">
+      <c r="A12" s="26">
         <v>4</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="17" t="s">
+      <c r="B12" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="17" t="s">
-        <v>44</v>
+      <c r="E12" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>41</v>
+      <c r="G12" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="27"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="23">
+      <c r="A14" s="26">
         <v>5</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="17" t="s">
-        <v>44</v>
+      <c r="E14" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>77</v>
+      <c r="G14" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="48" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
       <c r="F15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="23">
+      <c r="A16" s="26">
         <v>6</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="25" t="s">
+      <c r="B16" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>44</v>
+      <c r="E16" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="20" t="s">
-        <v>78</v>
+      <c r="G16" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="24"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="21"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="50"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
+      <c r="A18" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="37"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="23">
+      <c r="A20" s="26">
         <v>1</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>49</v>
+      <c r="D20" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>44</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H20" s="30"/>
+      <c r="G20" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="45"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
       <c r="F21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="18"/>
-      <c r="H21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="46"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="23">
+      <c r="A22" s="26">
         <v>2</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>49</v>
+      <c r="B22" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>44</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" s="22"/>
+      <c r="G22" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="22"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="32"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="23">
+      <c r="A24" s="26">
         <v>3</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="27"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" s="31"/>
+      <c r="H25" s="33"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="26">
+        <v>4</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G26" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="48" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="27"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="17" t="s">
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="26">
+        <v>5</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H24" s="22" t="s">
+      <c r="D28" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="H28" s="48" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="27"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25" s="18"/>
-      <c r="H25" s="27"/>
-    </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="23">
-        <v>4</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="17" t="s">
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="15"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="19"/>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="15"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="19"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="15"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="19"/>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="15"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="19"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="15"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="19"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="15"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="19"/>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="37"/>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="36"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="37"/>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="26">
+        <v>1</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="24"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-    </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="23">
-        <v>5</v>
-      </c>
-      <c r="B28" s="15" t="s">
+      <c r="E38" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G38" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="H38" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="17" t="s">
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="27"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G39" s="31"/>
+      <c r="H39" s="46"/>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="26">
+        <v>2</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="E40" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G40" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="H40" s="32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="27"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G41" s="31"/>
+      <c r="H41" s="32"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="26">
+        <v>3</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="F28" s="7" t="s">
+      <c r="E42" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="G42" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="H42" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="24"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="5" t="s">
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="27"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-    </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="41"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="45"/>
-    </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="41"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="45"/>
-    </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="41"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="45"/>
-    </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="41"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="45"/>
-    </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="41"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="45"/>
-    </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="41"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="45"/>
-    </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
-    </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="29"/>
-    </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="23">
-        <v>1</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="H38" s="30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="24"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G39" s="18"/>
-      <c r="H39" s="31"/>
-    </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23">
-        <v>2</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="H40" s="22" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="24"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G41" s="18"/>
-      <c r="H41" s="22"/>
-    </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="23">
-        <v>3</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G42" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="H42" s="22" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="24"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G43" s="18"/>
-      <c r="H43" s="27"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="33"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>68</v>
+      <c r="B44" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>63</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
       <c r="F44" s="5"/>
-      <c r="G44" s="17"/>
+      <c r="G44" s="30"/>
       <c r="H44" s="13"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="26"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="35"/>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="5"/>
-      <c r="G45" s="18"/>
+      <c r="G45" s="31"/>
       <c r="H45" s="13"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="46"/>
-      <c r="B46" s="47"/>
-      <c r="C46" s="49"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="50"/>
+      <c r="G46" s="47"/>
       <c r="H46" s="13"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="46"/>
-      <c r="B47" s="47"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
       <c r="F47" s="5"/>
-      <c r="G47" s="18"/>
+      <c r="G47" s="31"/>
       <c r="H47" s="13"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="23">
+      <c r="A48" s="26">
         <v>4</v>
       </c>
-      <c r="B48" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E48" s="17" t="s">
+      <c r="B48" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="30" t="s">
         <v>64</v>
       </c>
+      <c r="D48" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>59</v>
+      </c>
       <c r="F48" s="6"/>
-      <c r="G48" s="17" t="s">
+      <c r="G48" s="30" t="s">
         <v>12</v>
       </c>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="24"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
       <c r="F49" s="5"/>
-      <c r="G49" s="18"/>
+      <c r="G49" s="31"/>
       <c r="H49" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A36:H37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A14:A15"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="C28:C29"/>
@@ -2496,94 +2734,6 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="A18:H19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A36:H37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -2631,15 +2781,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2647,13 +2797,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2661,15 +2811,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="A3" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2677,13 +2827,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2701,10 +2851,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -2714,72 +2864,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>47</v>
+      <c r="E6" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="30" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="18"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="23">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>47</v>
+      <c r="E8" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>36</v>
+      <c r="G8" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="18"/>
+      <c r="G9" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2821,15 +2971,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2837,13 +2987,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2851,15 +3001,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="A3" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2867,13 +3017,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2891,10 +3041,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -2904,315 +3054,279 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>47</v>
+      <c r="B6" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="30" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="18"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="23">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>47</v>
+      <c r="B8" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>36</v>
+      <c r="G8" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="18"/>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="23">
+      <c r="A10" s="26">
         <v>3</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>47</v>
+      <c r="B10" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>36</v>
+      <c r="G10" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="18"/>
+        <v>66</v>
+      </c>
+      <c r="G11" s="31"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="23">
+      <c r="A12" s="26">
         <v>4</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>47</v>
+      <c r="B12" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="17" t="s">
-        <v>36</v>
+      <c r="G12" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="18"/>
+        <v>67</v>
+      </c>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="23">
+      <c r="A14" s="26">
         <v>5</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>47</v>
+      <c r="B14" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>36</v>
+      <c r="G14" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
       <c r="F15" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="18"/>
+        <v>68</v>
+      </c>
+      <c r="G15" s="31"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="23">
+      <c r="A16" s="26">
         <v>6</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>47</v>
+      <c r="B16" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="17" t="s">
-        <v>36</v>
+      <c r="G16" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="24"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="18"/>
+        <v>69</v>
+      </c>
+      <c r="G17" s="31"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="23">
+      <c r="A18" s="26">
         <v>7</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>47</v>
+      <c r="B18" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="17" t="s">
-        <v>36</v>
+      <c r="G18" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
       <c r="F19" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" s="18"/>
+        <v>70</v>
+      </c>
+      <c r="G19" s="31"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="23">
+      <c r="A20" s="26">
         <v>8</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>47</v>
+      <c r="B20" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G20" s="17" t="s">
-        <v>36</v>
+      <c r="G20" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
       <c r="F21" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="18"/>
+        <v>71</v>
+      </c>
+      <c r="G21" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3227,6 +3341,42 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3249,15 +3399,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3265,13 +3415,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3279,15 +3429,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="A3" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3295,13 +3445,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3319,10 +3469,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3332,195 +3482,177 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>47</v>
+      <c r="B6" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="30" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="18"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="23">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>47</v>
+      <c r="B8" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>36</v>
+      <c r="G8" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="18"/>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="23">
+      <c r="A10" s="26">
         <v>3</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>47</v>
+      <c r="B10" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>36</v>
+      <c r="G10" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="18"/>
+      <c r="G11" s="31"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="23">
+      <c r="A12" s="26">
         <v>4</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>47</v>
+      <c r="B12" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="17" t="s">
-        <v>36</v>
+      <c r="G12" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="18"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="23">
+      <c r="A14" s="26">
         <v>5</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>47</v>
+      <c r="B14" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>36</v>
+      <c r="G14" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
       <c r="F15" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="18"/>
+        <v>66</v>
+      </c>
+      <c r="G15" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3535,6 +3667,24 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3560,15 +3710,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3576,13 +3726,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3590,15 +3740,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="A3" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3606,13 +3756,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3630,10 +3780,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3643,115 +3793,109 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="17" t="s">
+      <c r="B6" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>44</v>
+      <c r="E6" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="30" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="18"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="23">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="17" t="s">
+      <c r="B8" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>44</v>
+      <c r="E8" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>36</v>
+      <c r="G8" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="18"/>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="23">
+      <c r="A10" s="26">
         <v>3</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="17" t="s">
+      <c r="B10" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>44</v>
+      <c r="E10" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>36</v>
+      <c r="G10" s="30" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="18"/>
+        <v>66</v>
+      </c>
+      <c r="G11" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3766,6 +3910,12 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3791,54 +3941,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="39"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="39"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="29"/>
+      <c r="A3" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="37"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="41"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -3847,16 +3997,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3865,67 +4015,67 @@
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23">
+      <c r="A6" s="26">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>44</v>
+      <c r="E6" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="22" t="s">
-        <v>39</v>
+      <c r="H6" s="32" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="27"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="23">
+      <c r="A8" s="26">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="25" t="s">
+      <c r="B8" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>44</v>
+      <c r="E8" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="30" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="9"/>
@@ -3933,147 +4083,147 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="18"/>
+      <c r="G9" s="31"/>
       <c r="H9" s="10"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23">
+      <c r="A10" s="26">
         <v>8</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="25" t="s">
+      <c r="B10" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>44</v>
+      <c r="E10" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="39"/>
+      <c r="H10" s="24"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="40"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="25"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="A12" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="37"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="A13" s="36"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="37"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="23">
+      <c r="A14" s="26">
         <v>5</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>49</v>
+      <c r="B14" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>44</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="22" t="s">
-        <v>39</v>
+      <c r="H14" s="32" t="s">
+        <v>34</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
       <c r="F15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="27"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="33"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="23">
+      <c r="A16" s="26">
         <v>7</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>49</v>
+      <c r="B16" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>44</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="30" t="s">
         <v>18</v>
       </c>
       <c r="H16" s="9"/>
@@ -4081,147 +4231,147 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="24"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="18"/>
+      <c r="G17" s="31"/>
       <c r="H17" s="10"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="23">
+      <c r="A18" s="26">
         <v>8</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>49</v>
+      <c r="B18" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>44</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="39"/>
+      <c r="H18" s="24"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
       <c r="F19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="18"/>
-      <c r="H19" s="40"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="25"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
+      <c r="A20" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="37"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="23">
+      <c r="A22" s="26">
         <v>5</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>64</v>
+      <c r="B22" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>59</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="22" t="s">
-        <v>39</v>
+      <c r="H22" s="32" t="s">
+        <v>34</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="27"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="33"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="23">
+      <c r="A24" s="26">
         <v>7</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="B24" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="30" t="s">
         <v>64</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>59</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="30" t="s">
         <v>18</v>
       </c>
       <c r="H24" s="9"/>
@@ -4229,110 +4379,61 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
       <c r="F25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="18"/>
+      <c r="G25" s="31"/>
       <c r="H25" s="10"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="23">
+      <c r="A26" s="26">
         <v>8</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="17" t="s">
+      <c r="B26" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="30" t="s">
         <v>64</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>59</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="G26" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="39"/>
+      <c r="H26" s="24"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="24"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
       <c r="F27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="18"/>
-      <c r="H27" s="40"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="25"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="A20:H21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A12:H13"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H4"/>
@@ -4348,6 +4449,55 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A12:H13"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="A20:H21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{09A6E995-6867-4571-9539-85B4B57268B9}"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B5E9AD-0207-42FA-8921-E4EA513C35A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226E6F04-68FE-4C79-8BB2-E773BC0E5288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Kuarters" sheetId="15" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$H$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Kuarters!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$75</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="141">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -458,6 +458,21 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1AkRQqdkMOvYudE11K9rValJUxH-2RD_D/view?usp=sharing,https://drive.google.com/file/d/12cJUBgEnt2r0L3wtz7pAUko8bxqrxJil/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Kaunter Tiket Gunung Berembun</t>
+  </si>
+  <si>
+    <t>Jalan Pantai</t>
+  </si>
+  <si>
+    <t>2°48'07.5"N 102°01'22.6"E</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vgaK1zGTVhZ8RKev5</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xMWDjbZWJYSQOFUlnUYkBz7-xHnsBm6C/view?usp=sharing,https://drive.google.com/file/d/19uSQqvkkzH7NrhXQUQv108WjC4sYYejW/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -524,7 +539,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -644,12 +659,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -714,12 +742,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -732,71 +793,66 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1128,60 +1184,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1214,25 +1270,25 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="37">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="36" t="s">
         <v>131</v>
       </c>
       <c r="H6" s="32" t="s">
@@ -1240,37 +1296,37 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="26"/>
       <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="37">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="36" t="s">
         <v>131</v>
       </c>
       <c r="H8" s="32" t="s">
@@ -1278,19 +1334,19 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="26"/>
       <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="42">
+      <c r="A10" s="48">
         <v>3</v>
       </c>
       <c r="B10" s="43" t="s">
@@ -1299,10 +1355,10 @@
       <c r="C10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
@@ -1314,11 +1370,11 @@
       <c r="H10" s="32"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="42"/>
+      <c r="A11" s="48"/>
       <c r="B11" s="44"/>
       <c r="C11" s="33"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="5" t="s">
         <v>28</v>
       </c>
@@ -1326,91 +1382,91 @@
       <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="26">
+      <c r="A12" s="37">
         <v>4</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="36" t="s">
         <v>132</v>
       </c>
       <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="26"/>
       <c r="H13" s="33"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
+      <c r="A14" s="37">
         <v>5</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="H14" s="48"/>
+      <c r="H14" s="32"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="42">
+      <c r="A16" s="48">
         <v>6</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="39" t="s">
         <v>95</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F16" s="7" t="s">
@@ -1419,34 +1475,34 @@
       <c r="G16" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="H16" s="49"/>
+      <c r="H16" s="28"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="42"/>
-      <c r="B17" s="29"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="40"/>
       <c r="C17" s="33"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="33"/>
-      <c r="H17" s="50"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="26">
+      <c r="A18" s="37">
         <v>7</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="39" t="s">
         <v>114</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F18" s="7" t="s">
@@ -1455,154 +1511,156 @@
       <c r="G18" s="33" t="s">
         <v>133</v>
       </c>
+      <c r="H18" s="34"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="33"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="33"/>
+      <c r="H19" s="35"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="45"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="30"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="46"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="31"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="26"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="30"/>
+      <c r="G22" s="36"/>
       <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="31"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="32"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="26"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="43"/>
       <c r="C24" s="33"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
       <c r="F24" s="6"/>
       <c r="G24" s="33"/>
       <c r="H24" s="32"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
+      <c r="A25" s="38"/>
       <c r="B25" s="44"/>
       <c r="C25" s="33"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
       <c r="F25" s="5"/>
       <c r="G25" s="33"/>
       <c r="H25" s="33"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="26"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="48"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="25"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="26"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="48"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="25"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="27"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="26"/>
-      <c r="B30" s="28"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="33"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
       <c r="F30" s="7"/>
       <c r="G30" s="33"/>
       <c r="H30" s="19"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="27"/>
-      <c r="B31" s="29"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="40"/>
       <c r="C31" s="33"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
       <c r="F31" s="5"/>
       <c r="G31" s="33"/>
       <c r="H31" s="19"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="26"/>
-      <c r="B32" s="28"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="39"/>
       <c r="C32" s="33"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="7"/>
       <c r="G32" s="33"/>
       <c r="H32" s="19"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="27"/>
-      <c r="B33" s="29"/>
+      <c r="A33" s="38"/>
+      <c r="B33" s="40"/>
       <c r="C33" s="33"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
       <c r="F33" s="5"/>
       <c r="G33" s="33"/>
       <c r="H33" s="19"/>
@@ -1614,179 +1672,97 @@
       <c r="H35" s="19"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="51"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G42" s="51"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="27"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G43" s="51"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="51"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G44" s="51"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="51"/>
-      <c r="J44" s="51"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G45" s="51"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="51"/>
-      <c r="J45" s="51"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
+      <c r="I45" s="27"/>
+      <c r="J45" s="27"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G46" s="51"/>
-      <c r="H46" s="51"/>
-      <c r="I46" s="51"/>
-      <c r="J46" s="51"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="27"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G47" s="51"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="51"/>
-      <c r="J47" s="51"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="27"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G48" s="51"/>
-      <c r="H48" s="51"/>
-      <c r="I48" s="51"/>
-      <c r="J48" s="51"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G49" s="51"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="51"/>
-      <c r="J49" s="51"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="27"/>
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G50" s="51"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="51"/>
-      <c r="J50" s="51"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+      <c r="J50" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="98">
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="G36:J50"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B10:B11"/>
+  <mergeCells count="99">
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="E18:E19"/>
@@ -1803,6 +1779,89 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G36:J50"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H18:H19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{08DF4C9A-9F75-4524-A39E-D32455244FE2}"/>
@@ -1835,54 +1894,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="53"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="39"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="53"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="37"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="51"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="54"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1913,63 +1972,63 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="37">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="30" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="46"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="37">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="36" t="s">
         <v>75</v>
       </c>
       <c r="H8" s="32" t="s">
@@ -1977,37 +2036,37 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="26"/>
       <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="A10" s="37">
         <v>3</v>
       </c>
       <c r="B10" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="36" t="s">
         <v>76</v>
       </c>
       <c r="H10" s="32" t="s">
@@ -2015,37 +2074,37 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="44"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="31"/>
+      <c r="G11" s="26"/>
       <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="26">
+      <c r="A12" s="37">
         <v>4</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="36" t="s">
         <v>75</v>
       </c>
       <c r="H12" s="32" t="s">
@@ -2053,75 +2112,75 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="26"/>
       <c r="H13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
+      <c r="A14" s="37">
         <v>5</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="H14" s="48" t="s">
+      <c r="H14" s="25" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26">
+      <c r="A16" s="37">
         <v>6</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G16" s="36" t="s">
         <v>75</v>
       </c>
       <c r="H16" s="49" t="s">
@@ -2129,131 +2188,131 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="31"/>
+      <c r="G17" s="26"/>
       <c r="H17" s="50"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="51"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="51"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="26">
+      <c r="A20" s="37">
         <v>1</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="36" t="s">
         <v>44</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G20" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="H20" s="45"/>
+      <c r="H20" s="30"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="31"/>
-      <c r="H21" s="46"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="31"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="26">
+      <c r="A22" s="37">
         <v>2</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="36" t="s">
         <v>44</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="30" t="s">
+      <c r="G22" s="36" t="s">
         <v>75</v>
       </c>
       <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="31"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="32"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26">
+      <c r="A24" s="37">
         <v>3</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="36" t="s">
         <v>44</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G24" s="30" t="s">
+      <c r="G24" s="36" t="s">
         <v>75</v>
       </c>
       <c r="H24" s="32" t="s">
@@ -2261,92 +2320,92 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
       <c r="F25" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G25" s="31"/>
+      <c r="G25" s="26"/>
       <c r="H25" s="33"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="26">
+      <c r="A26" s="37">
         <v>4</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="36" t="s">
         <v>44</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="30" t="s">
+      <c r="G26" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="H26" s="48" t="s">
+      <c r="H26" s="25" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="26">
+      <c r="A28" s="37">
         <v>5</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="30" t="s">
+      <c r="E28" s="36" t="s">
         <v>44</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="H28" s="48" t="s">
+      <c r="H28" s="25" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="27"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
       <c r="F29" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="15"/>
@@ -2409,85 +2468,85 @@
       <c r="H35" s="19"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="36" t="s">
+      <c r="A36" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="37"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="51"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="36"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="37"/>
+      <c r="A37" s="46"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="51"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="26">
+      <c r="A38" s="37">
         <v>1</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="30" t="s">
+      <c r="E38" s="36" t="s">
         <v>59</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G38" s="30" t="s">
+      <c r="G38" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="30" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="27"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
+      <c r="A39" s="38"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
       <c r="F39" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G39" s="31"/>
-      <c r="H39" s="46"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="31"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="26">
+      <c r="A40" s="37">
         <v>2</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="30" t="s">
+      <c r="D40" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="30" t="s">
+      <c r="E40" s="36" t="s">
         <v>59</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G40" s="30" t="s">
+      <c r="G40" s="36" t="s">
         <v>76</v>
       </c>
       <c r="H40" s="32" t="s">
@@ -2495,37 +2554,37 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="27"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
+      <c r="A41" s="38"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
       <c r="F41" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G41" s="31"/>
+      <c r="G41" s="26"/>
       <c r="H41" s="32"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="26">
+      <c r="A42" s="37">
         <v>3</v>
       </c>
-      <c r="B42" s="28" t="s">
+      <c r="B42" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="36" t="s">
         <v>59</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G42" s="30" t="s">
+      <c r="G42" s="36" t="s">
         <v>76</v>
       </c>
       <c r="H42" s="32" t="s">
@@ -2533,39 +2592,39 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="27"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
+      <c r="A43" s="38"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
       <c r="F43" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G43" s="31"/>
+      <c r="G43" s="26"/>
       <c r="H43" s="33"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="34" t="s">
+      <c r="C44" s="41" t="s">
         <v>63</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
       <c r="F44" s="5"/>
-      <c r="G44" s="30"/>
+      <c r="G44" s="36"/>
       <c r="H44" s="13"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="35"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="42"/>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="5"/>
-      <c r="G45" s="31"/>
+      <c r="G45" s="26"/>
       <c r="H45" s="13"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2575,7 +2634,7 @@
       <c r="D46" s="22"/>
       <c r="E46" s="22"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="47"/>
+      <c r="G46" s="52"/>
       <c r="H46" s="13"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2585,57 +2644,117 @@
       <c r="D47" s="22"/>
       <c r="E47" s="22"/>
       <c r="F47" s="5"/>
-      <c r="G47" s="31"/>
+      <c r="G47" s="26"/>
       <c r="H47" s="13"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="26">
+      <c r="A48" s="37">
         <v>4</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="30" t="s">
+      <c r="C48" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D48" s="30" t="s">
+      <c r="D48" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E48" s="30" t="s">
+      <c r="E48" s="36" t="s">
         <v>59</v>
       </c>
       <c r="F48" s="6"/>
-      <c r="G48" s="30" t="s">
+      <c r="G48" s="36" t="s">
         <v>12</v>
       </c>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="27"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
+      <c r="A49" s="38"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
       <c r="F49" s="5"/>
-      <c r="G49" s="31"/>
+      <c r="G49" s="26"/>
       <c r="H49" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A18:H19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="A36:H37"/>
     <mergeCell ref="A38:A39"/>
@@ -2660,80 +2779,20 @@
     <mergeCell ref="D42:D43"/>
     <mergeCell ref="E42:E43"/>
     <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A18:H19"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -2781,15 +2840,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2797,13 +2856,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2811,15 +2870,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2827,13 +2886,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2864,72 +2923,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="37">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="36" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="37">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2971,15 +3030,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2987,13 +3046,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3001,15 +3060,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3017,13 +3076,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3054,279 +3113,315 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="37">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="36" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="37">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="A10" s="37">
         <v>3</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="31"/>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="26">
+      <c r="A12" s="37">
         <v>4</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
+      <c r="A14" s="37">
         <v>5</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="31"/>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="26">
+      <c r="A16" s="37">
         <v>6</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G16" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="31"/>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="26">
+      <c r="A18" s="37">
         <v>7</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G18" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="31"/>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="26">
+      <c r="A20" s="37">
         <v>8</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G20" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="31"/>
+      <c r="G21" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3341,42 +3436,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3399,15 +3458,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3415,13 +3474,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3429,15 +3488,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3445,13 +3504,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3482,177 +3541,195 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="37">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="36" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="37">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="A10" s="37">
         <v>3</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="31"/>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="26">
+      <c r="A12" s="37">
         <v>4</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
+      <c r="A14" s="37">
         <v>5</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="36" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G15" s="31"/>
+      <c r="G15" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3667,24 +3744,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3697,7 +3756,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314B65D9-3D3B-4024-868B-A7B576C70DBC}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -3705,20 +3764,21 @@
     <col min="3" max="5" width="16.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="50.28515625" style="2" customWidth="1"/>
     <col min="7" max="7" width="47.42578125" style="2" customWidth="1"/>
-    <col min="8" max="12" width="9.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="59.42578125" style="2" customWidth="1"/>
+    <col min="9" max="12" width="9.5703125" style="2" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3726,13 +3786,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3740,15 +3800,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3756,13 +3816,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3791,111 +3851,266 @@
       <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="H5" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="37">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="41" t="s">
         <v>25</v>
       </c>
+      <c r="H6" s="32"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="37">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="41" t="s">
         <v>31</v>
       </c>
+      <c r="H8" s="34"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="35"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="A10" s="37">
         <v>3</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="41" t="s">
         <v>31</v>
       </c>
+      <c r="H10" s="60"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="31"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="60"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="58"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="58"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="47"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="61"/>
+    </row>
+    <row r="15" spans="1:12" ht="31.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="24"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="37">
+        <v>1</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="38"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G17" s="42"/>
+      <c r="H17" s="33"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H18" s="59"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H19" s="59"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H20" s="58"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H21" s="58"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H22" s="56"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H23" s="57"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H24" s="58"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H25" s="58"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H26" s="59"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H27" s="59"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H28" s="58"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H29" s="58"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H30" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="34">
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A13:G14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3910,16 +4125,13 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H16" r:id="rId1" xr:uid="{CC9E818B-DE15-4C2A-AB73-EE01589CCF9D}"/>
+  </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3941,54 +4153,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="53"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="39"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="53"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="37"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="51"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="54"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -4019,25 +4231,25 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
-        <v>5</v>
-      </c>
-      <c r="B6" s="28" t="s">
+      <c r="A6" s="37">
+        <v>1</v>
+      </c>
+      <c r="B6" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="36" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="32" t="s">
@@ -4045,37 +4257,37 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="26"/>
       <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
-        <v>7</v>
-      </c>
-      <c r="B8" s="28" t="s">
+      <c r="A8" s="37">
+        <v>2</v>
+      </c>
+      <c r="B8" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="36" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="9"/>
@@ -4083,105 +4295,105 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="26"/>
       <c r="H9" s="10"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
-        <v>8</v>
-      </c>
-      <c r="B10" s="28" t="s">
+      <c r="A10" s="37">
+        <v>3</v>
+      </c>
+      <c r="B10" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="24"/>
+      <c r="H10" s="34"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="25"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="35"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="37"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="51"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="37"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="51"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
-        <v>5</v>
-      </c>
-      <c r="B14" s="28" t="s">
+      <c r="A14" s="37">
+        <v>4</v>
+      </c>
+      <c r="B14" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="36" t="s">
         <v>44</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="36" t="s">
         <v>13</v>
       </c>
       <c r="H14" s="32" t="s">
@@ -4191,39 +4403,39 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="31"/>
+      <c r="G15" s="26"/>
       <c r="H15" s="33"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26">
-        <v>7</v>
-      </c>
-      <c r="B16" s="28" t="s">
+      <c r="A16" s="37">
+        <v>5</v>
+      </c>
+      <c r="B16" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="36" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G16" s="36" t="s">
         <v>18</v>
       </c>
       <c r="H16" s="9"/>
@@ -4231,105 +4443,105 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="31"/>
+      <c r="G17" s="26"/>
       <c r="H17" s="10"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="26">
-        <v>8</v>
-      </c>
-      <c r="B18" s="28" t="s">
+      <c r="A18" s="37">
+        <v>6</v>
+      </c>
+      <c r="B18" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="36" t="s">
         <v>44</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G18" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="24"/>
+      <c r="H18" s="34"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="31"/>
-      <c r="H19" s="25"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="35"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="51"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="37"/>
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="51"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="26">
-        <v>5</v>
-      </c>
-      <c r="B22" s="28" t="s">
+      <c r="A22" s="37">
+        <v>7</v>
+      </c>
+      <c r="B22" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="36" t="s">
         <v>59</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="30" t="s">
+      <c r="G22" s="36" t="s">
         <v>13</v>
       </c>
       <c r="H22" s="32" t="s">
@@ -4339,39 +4551,39 @@
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="31"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="33"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26">
-        <v>7</v>
-      </c>
-      <c r="B24" s="28" t="s">
+      <c r="A24" s="37">
+        <v>8</v>
+      </c>
+      <c r="B24" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="36" t="s">
         <v>59</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="30" t="s">
+      <c r="G24" s="36" t="s">
         <v>18</v>
       </c>
       <c r="H24" s="9"/>
@@ -4379,61 +4591,110 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
       <c r="F25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="31"/>
+      <c r="G25" s="26"/>
       <c r="H25" s="10"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="26">
-        <v>8</v>
-      </c>
-      <c r="B26" s="28" t="s">
+      <c r="A26" s="37">
+        <v>9</v>
+      </c>
+      <c r="B26" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="36" t="s">
         <v>59</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="30" t="s">
+      <c r="G26" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="24"/>
+      <c r="H26" s="34"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="31"/>
-      <c r="H27" s="25"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="35"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="A20:H21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A12:H13"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H4"/>
@@ -4449,55 +4710,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="A12:H13"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="A20:H21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{09A6E995-6867-4571-9539-85B4B57268B9}"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226E6F04-68FE-4C79-8BB2-E773BC0E5288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B350CEE-7AB1-4F54-97A4-C5C06E6257FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Kuarters" sheetId="15" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Kuarters!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$75</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="153">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -473,6 +473,42 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1xMWDjbZWJYSQOFUlnUYkBz7-xHnsBm6C/view?usp=sharing,https://drive.google.com/file/d/19uSQqvkkzH7NrhXQUQv108WjC4sYYejW/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VU6mi4lDFdur_uSGKGtvik6mv-5e6ZVS/view?usp=sharing,https://drive.google.com/file/d/1VU6mi4lDFdur_uSGKGtvik6mv-5e6ZVS/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Dalam Keadaan Baik Dan Digunakan</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1niC1z85LQ_Tp0472K16FnZaZQvYdk6ho/view?usp=sharing,https://drive.google.com/file/d/18sgwy2Y6XkrL8Rd9WUb_ju5NF0Myim22/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-mBPz7fEKoBaRq7T6R6dhYL2UtEj8fWS/view?usp=sharing,https://drive.google.com/file/d/1A8FH6covQMHBxL52Xlm0S3mbXfUIzf9c/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Kaunter Tiket Gunung Datuk</t>
+  </si>
+  <si>
+    <t>Rembau</t>
+  </si>
+  <si>
+    <t>Kota</t>
+  </si>
+  <si>
+    <t>2°32'34.5"N 102°10'08.4"E</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7XX2xzekMcwB35oj8</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pB_4qNjO_UD2U0VIEMoxL_4eI734C7Ew/view?usp=sharing,https://drive.google.com/file/d/1gjGdmz5MN7rvaQB1Fb3kO0ecMZak418r/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Blok Tandas 1 Kaunter Tiket Gunung Datuk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18wRTkqY7ki4Xv9_0-HrhuYDeJdGg55VT/view?usp=sharing,https://drive.google.com/file/d/1LbD5bsjxU1eVru6cfLvnR_JwwiMvPQHx/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -677,7 +713,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -742,30 +778,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -837,22 +870,19 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1184,60 +1214,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1270,399 +1300,399 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="37">
+      <c r="A6" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="31" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="38"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="33"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="32"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="37">
+      <c r="A8" s="36">
         <v>2</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="31" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="38"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="31"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="48">
+      <c r="A10" s="47">
         <v>3</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="31"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="A11" s="47"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="37">
+      <c r="A12" s="36">
         <v>4</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="36" t="s">
+      <c r="G12" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="H12" s="32"/>
+      <c r="H12" s="31"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="38"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="26"/>
-      <c r="H13" s="33"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="32"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="37">
+      <c r="A14" s="36">
         <v>5</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="36" t="s">
+      <c r="G14" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="H14" s="32"/>
+      <c r="H14" s="31"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="38"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="33"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="32"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="48">
+      <c r="A16" s="47">
         <v>6</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="H16" s="28"/>
+      <c r="H16" s="27"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="48"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="33"/>
-      <c r="H17" s="29"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="28"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="37">
+      <c r="A18" s="36">
         <v>7</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="33"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="38"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
       <c r="F19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="33"/>
-      <c r="H19" s="35"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="34"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="37"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="30"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="38"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="31"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="30"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="37"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="32"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="31"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="38"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="32"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="31"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="37"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
+      <c r="A24" s="36"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="31"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="38"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="37"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
+      <c r="A26" s="36"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="25"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="24"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="38"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="37"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
+      <c r="A28" s="36"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="25"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="24"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="38"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="37"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
+      <c r="A30" s="36"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="19"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="38"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="33"/>
+      <c r="G31" s="32"/>
       <c r="H31" s="19"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="37"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
+      <c r="A32" s="36"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="19"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="38"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="33"/>
+      <c r="G33" s="32"/>
       <c r="H33" s="19"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -1672,94 +1702,94 @@
       <c r="H35" s="19"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="27"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G48" s="27"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="27"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="26"/>
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G50" s="27"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="27"/>
-      <c r="J50" s="27"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="99">
@@ -1894,54 +1924,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="53"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="52"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="53"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="52"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="51"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="50"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="54"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="53"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1972,440 +2002,440 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="37">
+      <c r="A6" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="29" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="38"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="31"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37">
+      <c r="A8" s="36">
         <v>2</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="31" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="38"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="31"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="37">
+      <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="31" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="38"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="26"/>
-      <c r="H11" s="33"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="37">
+      <c r="A12" s="36">
         <v>4</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="36" t="s">
+      <c r="G12" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="31" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="38"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="26"/>
-      <c r="H13" s="33"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="32"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="37">
+      <c r="A14" s="36">
         <v>5</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="36" t="s">
+      <c r="G14" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="24" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="38"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="37">
+      <c r="A16" s="36">
         <v>6</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="36" t="s">
+      <c r="G16" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H16" s="49" t="s">
+      <c r="H16" s="48" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="38"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="26"/>
-      <c r="H17" s="50"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="49"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="51"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="50"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="46"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="51"/>
+      <c r="A19" s="45"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="50"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="37">
+      <c r="A20" s="36">
         <v>1</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="36" t="s">
+      <c r="G20" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H20" s="30"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="38"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
       <c r="F21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="26"/>
-      <c r="H21" s="31"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="30"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="37">
+      <c r="A22" s="36">
         <v>2</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="36" t="s">
+      <c r="E22" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="36" t="s">
+      <c r="G22" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H22" s="32"/>
+      <c r="H22" s="31"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="38"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="26"/>
-      <c r="H23" s="32"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="31"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="37">
+      <c r="A24" s="36">
         <v>3</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="36" t="s">
+      <c r="D24" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G24" s="36" t="s">
+      <c r="G24" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" s="31" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="38"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
       <c r="F25" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G25" s="26"/>
-      <c r="H25" s="33"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="32"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="37">
+      <c r="A26" s="36">
         <v>4</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="36" t="s">
+      <c r="D26" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="36" t="s">
+      <c r="E26" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="36" t="s">
+      <c r="G26" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="H26" s="25" t="s">
+      <c r="H26" s="24" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="38"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
       <c r="F27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="37">
+      <c r="A28" s="36">
         <v>5</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="36" t="s">
+      <c r="D28" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="36" t="s">
+      <c r="E28" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G28" s="36" t="s">
+      <c r="G28" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="H28" s="25" t="s">
+      <c r="H28" s="24" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="38"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
       <c r="F29" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="15"/>
@@ -2468,163 +2498,163 @@
       <c r="H35" s="19"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="46" t="s">
+      <c r="A36" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="51"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="50"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="46"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="51"/>
+      <c r="A37" s="45"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="50"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="37">
+      <c r="A38" s="36">
         <v>1</v>
       </c>
-      <c r="B38" s="39" t="s">
+      <c r="B38" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="41" t="s">
+      <c r="C38" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="36" t="s">
+      <c r="E38" s="35" t="s">
         <v>59</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G38" s="36" t="s">
+      <c r="G38" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="H38" s="30" t="s">
+      <c r="H38" s="29" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="38"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="42"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
       <c r="F39" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G39" s="26"/>
-      <c r="H39" s="31"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="30"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="37">
+      <c r="A40" s="36">
         <v>2</v>
       </c>
-      <c r="B40" s="39" t="s">
+      <c r="B40" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="41" t="s">
+      <c r="C40" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="36" t="s">
+      <c r="E40" s="35" t="s">
         <v>59</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G40" s="36" t="s">
+      <c r="G40" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="H40" s="32" t="s">
+      <c r="H40" s="31" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="38"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
       <c r="F41" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G41" s="26"/>
-      <c r="H41" s="32"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="31"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="37">
+      <c r="A42" s="36">
         <v>3</v>
       </c>
-      <c r="B42" s="39" t="s">
+      <c r="B42" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="C42" s="41" t="s">
+      <c r="C42" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="36" t="s">
+      <c r="D42" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="36" t="s">
+      <c r="E42" s="35" t="s">
         <v>59</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G42" s="36" t="s">
+      <c r="G42" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="H42" s="32" t="s">
+      <c r="H42" s="31" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="38"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
       <c r="F43" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G43" s="26"/>
-      <c r="H43" s="33"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="32"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="39" t="s">
+      <c r="B44" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="41" t="s">
+      <c r="C44" s="40" t="s">
         <v>63</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
       <c r="F44" s="5"/>
-      <c r="G44" s="36"/>
+      <c r="G44" s="35"/>
       <c r="H44" s="13"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="42"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="41"/>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="5"/>
-      <c r="G45" s="26"/>
+      <c r="G45" s="25"/>
       <c r="H45" s="13"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2634,7 +2664,7 @@
       <c r="D46" s="22"/>
       <c r="E46" s="22"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="52"/>
+      <c r="G46" s="51"/>
       <c r="H46" s="13"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2644,39 +2674,39 @@
       <c r="D47" s="22"/>
       <c r="E47" s="22"/>
       <c r="F47" s="5"/>
-      <c r="G47" s="26"/>
+      <c r="G47" s="25"/>
       <c r="H47" s="13"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="37">
+      <c r="A48" s="36">
         <v>4</v>
       </c>
-      <c r="B48" s="39" t="s">
+      <c r="B48" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="36" t="s">
+      <c r="C48" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D48" s="36" t="s">
+      <c r="D48" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E48" s="36" t="s">
+      <c r="E48" s="35" t="s">
         <v>59</v>
       </c>
       <c r="F48" s="6"/>
-      <c r="G48" s="36" t="s">
+      <c r="G48" s="35" t="s">
         <v>12</v>
       </c>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="38"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
+      <c r="A49" s="37"/>
+      <c r="B49" s="39"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
       <c r="F49" s="5"/>
-      <c r="G49" s="26"/>
+      <c r="G49" s="25"/>
       <c r="H49" s="10"/>
     </row>
   </sheetData>
@@ -2840,15 +2870,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2856,13 +2886,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2870,15 +2900,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2886,13 +2916,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2923,72 +2953,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="37">
+      <c r="A6" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="35" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="38"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37">
+      <c r="A8" s="36">
         <v>2</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="38"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="26"/>
+      <c r="G9" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3030,15 +3060,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3046,13 +3076,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3060,15 +3090,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3076,13 +3106,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3113,276 +3143,276 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="37">
+      <c r="A6" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="35" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="38"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37">
+      <c r="A8" s="36">
         <v>2</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="38"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="26"/>
+      <c r="G9" s="25"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="37">
+      <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="38"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="37">
+      <c r="A12" s="36">
         <v>4</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="36" t="s">
+      <c r="G12" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="38"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="25"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="37">
+      <c r="A14" s="36">
         <v>5</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="36" t="s">
+      <c r="G14" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="38"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="26"/>
+      <c r="G15" s="25"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="37">
+      <c r="A16" s="36">
         <v>6</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="36" t="s">
+      <c r="G16" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="38"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="26"/>
+      <c r="G17" s="25"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="37">
+      <c r="A18" s="36">
         <v>7</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="36" t="s">
+      <c r="G18" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="38"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
       <c r="F19" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="26"/>
+      <c r="G19" s="25"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="37">
+      <c r="A20" s="36">
         <v>8</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G20" s="36" t="s">
+      <c r="G20" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="38"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
       <c r="F21" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="26"/>
+      <c r="G21" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -3458,15 +3488,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3474,13 +3504,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3488,15 +3518,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3504,13 +3534,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3541,174 +3571,174 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="37">
+      <c r="A6" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="35" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="38"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37">
+      <c r="A8" s="36">
         <v>2</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="38"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="26"/>
+      <c r="G9" s="25"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="37">
+      <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="38"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="37">
+      <c r="A12" s="36">
         <v>4</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="36" t="s">
+      <c r="G12" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="38"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="25"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="37">
+      <c r="A14" s="36">
         <v>5</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="35" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="36" t="s">
+      <c r="G14" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="38"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G15" s="26"/>
+      <c r="G15" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -3756,7 +3786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314B65D9-3D3B-4024-868B-A7B576C70DBC}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -3770,15 +3800,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3786,13 +3816,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3800,15 +3830,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3816,13 +3846,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3856,137 +3886,143 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="37">
+      <c r="A6" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="32"/>
+      <c r="G6" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="38"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="42"/>
-      <c r="H7" s="33"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="32"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37">
+      <c r="A8" s="36">
         <v>2</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="34"/>
+      <c r="G8" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="58" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="38"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="42"/>
-      <c r="H9" s="35"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="59"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="37">
+      <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="60"/>
+      <c r="G10" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="38"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="42"/>
-      <c r="H11" s="60"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H12" s="58"/>
+      <c r="H12" s="55"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="58"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="55"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="47"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="61"/>
+      <c r="A14" s="46"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="57"/>
     </row>
     <row r="15" spans="1:12" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
@@ -4007,93 +4043,202 @@
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="55" t="s">
+      <c r="G15" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="24"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="37">
+      <c r="H15" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="36">
         <v>1</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="G16" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="32" t="s">
+      <c r="G16" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="31" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="38"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="G17" s="42"/>
-      <c r="H17" s="33"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="32"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H18" s="59"/>
+      <c r="H18" s="56"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H19" s="59"/>
+      <c r="A19" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="56"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H20" s="58"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H21" s="58"/>
+      <c r="A20" s="46"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="55"/>
+    </row>
+    <row r="21" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H22" s="56"/>
+      <c r="A22" s="36">
+        <v>1</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="31" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H23" s="57"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="41"/>
+      <c r="H23" s="32"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H24" s="58"/>
+      <c r="A24" s="36">
+        <v>2</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="58" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H25" s="58"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" s="41"/>
+      <c r="H25" s="59"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H26" s="59"/>
+      <c r="H26" s="55"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H27" s="59"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H28" s="58"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H29" s="58"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H30" s="58"/>
+      <c r="H27" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="H26:H27"/>
+  <mergeCells count="47">
+    <mergeCell ref="H24:H25"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="H8:H9"/>
+    <mergeCell ref="A19:G20"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H18:H19"/>
@@ -4129,9 +4274,14 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H16" r:id="rId1" xr:uid="{CC9E818B-DE15-4C2A-AB73-EE01589CCF9D}"/>
+    <hyperlink ref="H6" r:id="rId2" xr:uid="{0D91745A-4E24-487B-B31B-3DC86DA471F7}"/>
+    <hyperlink ref="H8" r:id="rId3" xr:uid="{181B3597-36C9-4302-B883-B24381B1588C}"/>
+    <hyperlink ref="H10" r:id="rId4" xr:uid="{BD83B39D-F7E1-487C-AB32-F38D53F58F54}"/>
+    <hyperlink ref="H22" r:id="rId5" xr:uid="{B3AC0619-88F5-4437-A739-122B6177B438}"/>
+    <hyperlink ref="H24" r:id="rId6" xr:uid="{07F1428F-3A28-4A82-A92D-36ABC3CEA967}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -4153,54 +4303,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="53"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="52"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="53"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="52"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="51"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="50"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="54"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="53"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -4231,63 +4381,63 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="37">
+      <c r="A6" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="31" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="38"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="33"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="32"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37">
+      <c r="A8" s="36">
         <v>2</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="35" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="9"/>
@@ -4295,147 +4445,147 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="38"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="26"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="10"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="37">
+      <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="35" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="33"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="38"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="26"/>
-      <c r="H11" s="35"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="34"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="51"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="50"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="46"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="51"/>
+      <c r="A13" s="45"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="50"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="37">
+      <c r="A14" s="36">
         <v>4</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="36" t="s">
+      <c r="G14" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="31" t="s">
         <v>34</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="38"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="33"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="32"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="37">
+      <c r="A16" s="36">
         <v>5</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="36" t="s">
+      <c r="G16" s="35" t="s">
         <v>18</v>
       </c>
       <c r="H16" s="9"/>
@@ -4443,147 +4593,147 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="38"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="26"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="10"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="37">
+      <c r="A18" s="36">
         <v>6</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="36" t="s">
+      <c r="G18" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="33"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="38"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
       <c r="F19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="26"/>
-      <c r="H19" s="35"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="34"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="51"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="50"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="46"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="51"/>
+      <c r="A21" s="45"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="50"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="37">
+      <c r="A22" s="36">
         <v>7</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="36" t="s">
+      <c r="E22" s="35" t="s">
         <v>59</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="36" t="s">
+      <c r="G22" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="H22" s="31" t="s">
         <v>34</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="38"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="26"/>
-      <c r="H23" s="33"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="32"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="37">
+      <c r="A24" s="36">
         <v>8</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="36" t="s">
+      <c r="D24" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="35" t="s">
         <v>59</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="36" t="s">
+      <c r="G24" s="35" t="s">
         <v>18</v>
       </c>
       <c r="H24" s="9"/>
@@ -4591,56 +4741,56 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="38"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
       <c r="F25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="26"/>
+      <c r="G25" s="25"/>
       <c r="H25" s="10"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="37">
+      <c r="A26" s="36">
         <v>9</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="36" t="s">
+      <c r="D26" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="36" t="s">
+      <c r="E26" s="35" t="s">
         <v>59</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="36" t="s">
+      <c r="G26" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="34"/>
+      <c r="H26" s="33"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="38"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
       <c r="F27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="26"/>
-      <c r="H27" s="35"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="34"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B350CEE-7AB1-4F54-97A4-C5C06E6257FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B28422-65B2-42FE-B5EE-D41A8A8D5131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="155">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -247,9 +247,6 @@
     <t>Simpang Pertang</t>
   </si>
   <si>
-    <t>Bangunan Kaunter Tiket</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q10</t>
   </si>
   <si>
@@ -509,6 +506,15 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/18wRTkqY7ki4Xv9_0-HrhuYDeJdGg55VT/view?usp=sharing,https://drive.google.com/file/d/1LbD5bsjxU1eVru6cfLvnR_JwwiMvPQHx/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Bangunan Kaunter Tiket Gunung Datuk</t>
+  </si>
+  <si>
+    <t>Bangunan Kaunter Tiket Gunung Berembun</t>
+  </si>
+  <si>
+    <t>Bangunan Kaunter Tiket Gunung Angsi</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1310,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="40" t="s">
         <v>30</v>
@@ -1319,10 +1325,10 @@
         <v>29</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1342,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="40" t="s">
         <v>30</v>
@@ -1357,10 +1363,10 @@
         <v>29</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1380,7 +1386,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>30</v>
@@ -1395,7 +1401,7 @@
         <v>29</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H10" s="31"/>
     </row>
@@ -1416,7 +1422,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12" s="40" t="s">
         <v>30</v>
@@ -1431,7 +1437,7 @@
         <v>29</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H12" s="31"/>
     </row>
@@ -1452,7 +1458,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" s="40" t="s">
         <v>30</v>
@@ -1467,7 +1473,7 @@
         <v>29</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H14" s="31"/>
     </row>
@@ -1488,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16" s="32" t="s">
         <v>30</v>
@@ -1503,7 +1509,7 @@
         <v>29</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H16" s="27"/>
     </row>
@@ -1524,7 +1530,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C18" s="32" t="s">
         <v>30</v>
@@ -1539,7 +1545,7 @@
         <v>29</v>
       </c>
       <c r="G18" s="32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H18" s="33"/>
     </row>
@@ -2021,7 +2027,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H6" s="29" t="s">
         <v>33</v>
@@ -2059,10 +2065,10 @@
         <v>6</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2082,7 +2088,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>8</v>
@@ -2097,7 +2103,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H10" s="31" t="s">
         <v>35</v>
@@ -2120,7 +2126,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>8</v>
@@ -2135,7 +2141,7 @@
         <v>6</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H12" s="31" t="s">
         <v>36</v>
@@ -2173,10 +2179,10 @@
         <v>17</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2196,7 +2202,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="40" t="s">
         <v>15</v>
@@ -2211,10 +2217,10 @@
         <v>17</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H16" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2271,7 +2277,7 @@
         <v>6</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H20" s="29"/>
     </row>
@@ -2307,7 +2313,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H22" s="31"/>
     </row>
@@ -2328,10 +2334,10 @@
         <v>3</v>
       </c>
       <c r="B24" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="35" t="s">
         <v>77</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>78</v>
       </c>
       <c r="D24" s="35" t="s">
         <v>46</v>
@@ -2340,13 +2346,13 @@
         <v>44</v>
       </c>
       <c r="F24" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" s="31" t="s">
         <v>80</v>
-      </c>
-      <c r="G24" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="H24" s="31" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2356,7 +2362,7 @@
       <c r="D25" s="25"/>
       <c r="E25" s="25"/>
       <c r="F25" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="32"/>
@@ -2378,13 +2384,13 @@
         <v>44</v>
       </c>
       <c r="F26" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="24" t="s">
         <v>83</v>
-      </c>
-      <c r="G26" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2394,7 +2400,7 @@
       <c r="D27" s="25"/>
       <c r="E27" s="25"/>
       <c r="F27" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G27" s="25"/>
       <c r="H27" s="25"/>
@@ -2404,7 +2410,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" s="35" t="s">
         <v>51</v>
@@ -2416,13 +2422,13 @@
         <v>44</v>
       </c>
       <c r="F28" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G28" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="G28" s="35" t="s">
+      <c r="H28" s="24" t="s">
         <v>88</v>
-      </c>
-      <c r="H28" s="24" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2432,7 +2438,7 @@
       <c r="D29" s="25"/>
       <c r="E29" s="25"/>
       <c r="F29" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
@@ -2536,13 +2542,13 @@
         <v>59</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G38" s="35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2552,7 +2558,7 @@
       <c r="D39" s="25"/>
       <c r="E39" s="25"/>
       <c r="F39" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G39" s="25"/>
       <c r="H39" s="30"/>
@@ -2574,13 +2580,13 @@
         <v>59</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G40" s="35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2590,7 +2596,7 @@
       <c r="D41" s="25"/>
       <c r="E41" s="25"/>
       <c r="F41" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G41" s="25"/>
       <c r="H41" s="31"/>
@@ -2600,7 +2606,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C42" s="40" t="s">
         <v>63</v>
@@ -2612,13 +2618,13 @@
         <v>59</v>
       </c>
       <c r="F42" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G42" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="H42" s="31" t="s">
         <v>92</v>
-      </c>
-      <c r="G42" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="H42" s="31" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2628,7 +2634,7 @@
       <c r="D43" s="25"/>
       <c r="E43" s="25"/>
       <c r="F43" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G43" s="25"/>
       <c r="H43" s="32"/>
@@ -2636,7 +2642,7 @@
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
       <c r="B44" s="38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C44" s="40" t="s">
         <v>63</v>
@@ -3147,7 +3153,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C6" s="40" t="s">
         <v>55</v>
@@ -3181,7 +3187,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="40" t="s">
         <v>55</v>
@@ -3215,7 +3221,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" s="40" t="s">
         <v>55</v>
@@ -3240,7 +3246,7 @@
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="25"/>
     </row>
@@ -3249,7 +3255,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="40" t="s">
         <v>55</v>
@@ -3274,7 +3280,7 @@
       <c r="D13" s="25"/>
       <c r="E13" s="25"/>
       <c r="F13" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13" s="25"/>
     </row>
@@ -3283,7 +3289,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="40" t="s">
         <v>55</v>
@@ -3308,7 +3314,7 @@
       <c r="D15" s="25"/>
       <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15" s="25"/>
     </row>
@@ -3317,7 +3323,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C16" s="40" t="s">
         <v>55</v>
@@ -3342,7 +3348,7 @@
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="25"/>
     </row>
@@ -3351,7 +3357,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>55</v>
@@ -3376,7 +3382,7 @@
       <c r="D19" s="25"/>
       <c r="E19" s="25"/>
       <c r="F19" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G19" s="25"/>
     </row>
@@ -3385,7 +3391,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C20" s="40" t="s">
         <v>55</v>
@@ -3410,7 +3416,7 @@
       <c r="D21" s="25"/>
       <c r="E21" s="25"/>
       <c r="F21" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="25"/>
     </row>
@@ -3575,7 +3581,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="40" t="s">
         <v>54</v>
@@ -3609,7 +3615,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="40" t="s">
         <v>54</v>
@@ -3643,7 +3649,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C10" s="40" t="s">
         <v>54</v>
@@ -3677,7 +3683,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C12" s="40" t="s">
         <v>54</v>
@@ -3711,7 +3717,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" s="40" t="s">
         <v>54</v>
@@ -3736,7 +3742,7 @@
       <c r="D15" s="25"/>
       <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15" s="25"/>
     </row>
@@ -3890,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="C6" s="40" t="s">
         <v>58</v>
@@ -3905,10 +3911,10 @@
         <v>27</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -3928,7 +3934,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="40" t="s">
         <v>58</v>
@@ -3943,10 +3949,10 @@
         <v>27</v>
       </c>
       <c r="G8" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="58" t="s">
         <v>142</v>
-      </c>
-      <c r="H8" s="58" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3966,7 +3972,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="40" t="s">
         <v>58</v>
@@ -3981,10 +3987,10 @@
         <v>27</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3994,7 +4000,7 @@
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="41"/>
       <c r="H11" s="32"/>
@@ -4004,7 +4010,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="45" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B13" s="45"/>
       <c r="C13" s="45"/>
@@ -4055,10 +4061,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D16" s="35" t="s">
         <v>46</v>
@@ -4067,13 +4073,13 @@
         <v>44</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G16" s="40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -4083,7 +4089,7 @@
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G17" s="41"/>
       <c r="H17" s="32"/>
@@ -4093,7 +4099,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="45" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B19" s="45"/>
       <c r="C19" s="45"/>
@@ -4144,25 +4150,25 @@
         <v>1</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>65</v>
+        <v>152</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G22" s="40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -4172,7 +4178,7 @@
       <c r="D23" s="25"/>
       <c r="E23" s="25"/>
       <c r="F23" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G23" s="41"/>
       <c r="H23" s="32"/>
@@ -4182,25 +4188,25 @@
         <v>2</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E24" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G24" s="40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H24" s="58" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -4210,7 +4216,7 @@
       <c r="D25" s="25"/>
       <c r="E25" s="25"/>
       <c r="F25" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G25" s="41"/>
       <c r="H25" s="59"/>
@@ -4423,7 +4429,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="40" t="s">
         <v>15</v>
@@ -4463,7 +4469,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="40" t="s">
         <v>15</v>
@@ -4529,7 +4535,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" s="35" t="s">
         <v>48</v>
@@ -4571,7 +4577,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C16" s="35" t="s">
         <v>48</v>
@@ -4611,7 +4617,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C18" s="35" t="s">
         <v>48</v>
@@ -4677,7 +4683,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="40" t="s">
         <v>63</v>
@@ -4719,7 +4725,7 @@
         <v>8</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C24" s="35" t="s">
         <v>64</v>
@@ -4759,7 +4765,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C26" s="35" t="s">
         <v>64</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B28422-65B2-42FE-B5EE-D41A8A8D5131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160D67E0-7D6B-4F49-939C-912EFDF8925B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Kuarters" sheetId="15" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$H$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Kuarters!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$75</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="161">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -515,6 +515,24 @@
   </si>
   <si>
     <t>Bangunan Kaunter Tiket Gunung Angsi</t>
+  </si>
+  <si>
+    <t>Kaunter Tiket Gunung Tampin</t>
+  </si>
+  <si>
+    <t>Bangunan Kaunter Tiket Gunung Tampin</t>
+  </si>
+  <si>
+    <t>2°29'24.7"N 102°13'03.5"E</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/5LFxR6uAtn4LhNQE6</t>
+  </si>
+  <si>
+    <t>Perlu Penyelenggaraan Dan Tidak Diduduki</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1MMBxS8irr5zyWbBP7mB-ymgWlmZqxvXD/view?usp=sharing,https://drive.google.com/file/d/1-6GqoLt0XhSdeCUKF1kMXrIv5hYr4PIY/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -878,9 +896,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -890,6 +905,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3792,7 +3808,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314B65D9-3D3B-4024-868B-A7B576C70DBC}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -3951,7 +3967,7 @@
       <c r="G8" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="57" t="s">
         <v>142</v>
       </c>
     </row>
@@ -3965,7 +3981,7 @@
         <v>24</v>
       </c>
       <c r="G9" s="41"/>
-      <c r="H9" s="59"/>
+      <c r="H9" s="58"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="36">
@@ -4028,7 +4044,7 @@
       <c r="E14" s="46"/>
       <c r="F14" s="46"/>
       <c r="G14" s="46"/>
-      <c r="H14" s="57"/>
+      <c r="H14" s="56"/>
     </row>
     <row r="15" spans="1:12" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
@@ -4095,7 +4111,7 @@
       <c r="H17" s="32"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H18" s="56"/>
+      <c r="H18" s="59"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="45" t="s">
@@ -4107,7 +4123,7 @@
       <c r="E19" s="45"/>
       <c r="F19" s="45"/>
       <c r="G19" s="45"/>
-      <c r="H19" s="56"/>
+      <c r="H19" s="59"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="46"/>
@@ -4205,7 +4221,7 @@
       <c r="G24" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="H24" s="58" t="s">
+      <c r="H24" s="57" t="s">
         <v>151</v>
       </c>
     </row>
@@ -4219,16 +4235,107 @@
         <v>148</v>
       </c>
       <c r="G25" s="41"/>
-      <c r="H25" s="59"/>
+      <c r="H25" s="58"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H26" s="55"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H27" s="55"/>
+      <c r="A27" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="59"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="55"/>
+    </row>
+    <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="36">
+        <v>1</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="H30" s="31" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="37"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G31" s="41"/>
+      <c r="H31" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="54">
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="A27:G28"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="H8:H9"/>
@@ -4247,7 +4354,6 @@
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H18:H19"/>
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="A13:G14"/>
     <mergeCell ref="A16:A17"/>
@@ -4285,9 +4391,10 @@
     <hyperlink ref="H10" r:id="rId4" xr:uid="{BD83B39D-F7E1-487C-AB32-F38D53F58F54}"/>
     <hyperlink ref="H22" r:id="rId5" xr:uid="{B3AC0619-88F5-4437-A739-122B6177B438}"/>
     <hyperlink ref="H24" r:id="rId6" xr:uid="{07F1428F-3A28-4A82-A92D-36ABC3CEA967}"/>
+    <hyperlink ref="H30" r:id="rId7" xr:uid="{0CE6EA5D-7C7C-4C81-AE6D-0751AA196926}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId7"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId8"/>
 </worksheet>
 </file>
 

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160D67E0-7D6B-4F49-939C-912EFDF8925B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D9F5DA-42F3-483E-83DB-DF866A8E871B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="161">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -4659,9 +4659,7 @@
       <c r="G14" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="31" t="s">
-        <v>34</v>
-      </c>
+      <c r="H14" s="31"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
@@ -4807,9 +4805,7 @@
       <c r="G22" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="31" t="s">
-        <v>34</v>
-      </c>
+      <c r="H22" s="31"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
@@ -4980,15 +4976,13 @@
     <hyperlink ref="F9" r:id="rId3" xr:uid="{C058A9F3-432B-4492-8FEF-75D95EA066B4}"/>
     <hyperlink ref="F11" r:id="rId4" xr:uid="{7C84037B-C526-459E-AFCC-EC743894CAAF}"/>
     <hyperlink ref="F15" r:id="rId5" xr:uid="{96E9467B-42A7-4426-8441-28CEC140C97E}"/>
-    <hyperlink ref="H14" r:id="rId6" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{6295704B-3F57-4B74-84C7-65DD0D71B850}"/>
-    <hyperlink ref="F17" r:id="rId7" xr:uid="{0A00E371-A13B-46B9-BC01-F406FBB354D1}"/>
-    <hyperlink ref="F19" r:id="rId8" xr:uid="{601C882C-4FB2-4B15-B5E8-BE4DA74B8401}"/>
-    <hyperlink ref="F23" r:id="rId9" xr:uid="{FAE427DB-1331-4082-96AF-A6A7E15395CA}"/>
-    <hyperlink ref="H22" r:id="rId10" display="https://drive.google.com/file/d/1RpzqhNLcy6Ls52MPIHlLSWTc2yxZ-Z6E/view?usp=sharing" xr:uid="{3C09A598-0156-4A2F-8BE6-68F7CC7CFBEF}"/>
-    <hyperlink ref="F25" r:id="rId11" xr:uid="{B281539B-7428-4B1A-B9D0-CB060D2AAC76}"/>
-    <hyperlink ref="F27" r:id="rId12" xr:uid="{909E7EB9-3EB2-4837-B0AB-B170A1604C99}"/>
+    <hyperlink ref="F17" r:id="rId6" xr:uid="{0A00E371-A13B-46B9-BC01-F406FBB354D1}"/>
+    <hyperlink ref="F19" r:id="rId7" xr:uid="{601C882C-4FB2-4B15-B5E8-BE4DA74B8401}"/>
+    <hyperlink ref="F23" r:id="rId8" xr:uid="{FAE427DB-1331-4082-96AF-A6A7E15395CA}"/>
+    <hyperlink ref="F25" r:id="rId9" xr:uid="{B281539B-7428-4B1A-B9D0-CB060D2AAC76}"/>
+    <hyperlink ref="F27" r:id="rId10" xr:uid="{909E7EB9-3EB2-4837-B0AB-B170A1604C99}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId13"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId11"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D9F5DA-42F3-483E-83DB-DF866A8E871B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13DED4A8-2692-4954-B59F-AC5443093628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$H$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Kuarters!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$73</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$H$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negeri Kenaboi'!$A$1:$G$23</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="162">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -533,6 +533,9 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1MMBxS8irr5zyWbBP7mB-ymgWlmZqxvXD/view?usp=sharing,https://drive.google.com/file/d/1-6GqoLt0XhSdeCUKF1kMXrIv5hYr4PIY/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perlu Penyelenggaraan Dan Tidak Diduduki </t>
   </si>
 </sst>
 </file>
@@ -599,7 +602,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -703,26 +706,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -737,7 +720,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -763,12 +746,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -790,22 +767,76 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -823,81 +854,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -905,7 +866,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1236,60 +1196,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1322,499 +1282,582 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
+      <c r="A6" s="22">
         <v>1</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="28" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="37"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="36">
+      <c r="A8" s="22">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="28" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
       <c r="F9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="31"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="47">
+      <c r="A10" s="38">
         <v>3</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="31"/>
+      <c r="H10" s="28"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="47"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="36">
+      <c r="A12" s="22">
         <v>4</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="H12" s="31"/>
+      <c r="H12" s="28"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="37"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
       <c r="F13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="32"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="36">
+      <c r="A14" s="22">
         <v>5</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="35" t="s">
+      <c r="G14" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="H14" s="31"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="32"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="47">
+      <c r="A16" s="38">
         <v>6</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="H16" s="27"/>
+      <c r="H16" s="43"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="47"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="32"/>
-      <c r="H17" s="28"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="44"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="36">
+      <c r="A18" s="22">
         <v>7</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="H18" s="33"/>
+      <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="37"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
       <c r="F19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="32"/>
-      <c r="H19" s="34"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="36"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="29"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="45"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="37"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="30"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="46"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="36"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="31"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="28"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="37"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="31"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="28"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="36"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="31"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="28"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="37"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="36"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="24"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="41"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="37"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="36"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="24"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="41"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="37"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="36"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="19"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="17"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="37"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="19"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="36"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="19"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="37"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="19"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H34" s="19"/>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H35" s="19"/>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G44" s="26"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="26"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G50" s="26"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="26"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="99">
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G36:J50"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="E18:E19"/>
@@ -1831,89 +1874,6 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="G36:J50"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H18:H19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{08DF4C9A-9F75-4524-A39E-D32455244FE2}"/>
@@ -1930,7 +1890,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D54FEF-B8B0-455E-9719-4EECE694A16C}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -1946,54 +1906,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="52"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="35"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="52"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="35"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="50"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="53"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="37"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -2024,715 +1984,785 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
+      <c r="A6" s="22">
         <v>1</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="45" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="37"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="30"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="36">
+      <c r="A8" s="22">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="28" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
       <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="31"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="36">
+      <c r="A10" s="22">
         <v>3</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="28" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="37"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="32"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="36">
+      <c r="A12" s="22">
         <v>4</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="31" t="s">
+      <c r="H12" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="37"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
       <c r="F13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="32"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="36">
+      <c r="A14" s="22">
         <v>5</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="35" t="s">
+      <c r="G14" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="H14" s="41" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="36">
+      <c r="A16" s="22">
         <v>6</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="48" t="s">
+      <c r="H16" s="47" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="25"/>
-      <c r="H17" s="49"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="48"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="50"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="33"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="45"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="50"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="33"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="36">
-        <v>1</v>
-      </c>
-      <c r="B20" s="38" t="s">
+      <c r="A20" s="22">
+        <v>7</v>
+      </c>
+      <c r="B20" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H20" s="29"/>
+      <c r="H20" s="45"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="37"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
       <c r="F21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="25"/>
-      <c r="H21" s="30"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="46"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="36">
-        <v>2</v>
-      </c>
-      <c r="B22" s="38" t="s">
+      <c r="A22" s="22">
+        <v>8</v>
+      </c>
+      <c r="B22" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="31"/>
+      <c r="H22" s="28"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="37"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="31"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="28"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="36">
-        <v>3</v>
-      </c>
-      <c r="B24" s="38" t="s">
+      <c r="A24" s="22">
+        <v>9</v>
+      </c>
+      <c r="B24" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G24" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="31" t="s">
+      <c r="H24" s="28" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="37"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
       <c r="F25" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="25"/>
-      <c r="H25" s="32"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="29"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="36">
-        <v>4</v>
-      </c>
-      <c r="B26" s="38" t="s">
+      <c r="A26" s="22">
+        <v>10</v>
+      </c>
+      <c r="B26" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="35" t="s">
+      <c r="D26" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="H26" s="24" t="s">
+      <c r="H26" s="41" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="37"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
       <c r="F27" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="36">
-        <v>5</v>
-      </c>
-      <c r="B28" s="38" t="s">
+      <c r="A28" s="22">
+        <v>11</v>
+      </c>
+      <c r="B28" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G28" s="35" t="s">
+      <c r="G28" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="H28" s="24" t="s">
+      <c r="H28" s="41" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="37"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
       <c r="F29" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="15"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="19"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="17"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="15"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="19"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="19"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="19"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="15"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="15"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="19"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="50"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="33"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="45"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="50"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="33"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="36">
-        <v>1</v>
-      </c>
-      <c r="B38" s="38" t="s">
+      <c r="A38" s="22">
+        <v>12</v>
+      </c>
+      <c r="B38" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="40" t="s">
+      <c r="C38" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="35" t="s">
+      <c r="D38" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="35" t="s">
+      <c r="E38" s="26" t="s">
         <v>59</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="35" t="s">
+      <c r="G38" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="H38" s="29" t="s">
+      <c r="H38" s="45" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="37"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
       <c r="F39" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G39" s="25"/>
-      <c r="H39" s="30"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="46"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="36">
-        <v>2</v>
-      </c>
-      <c r="B40" s="38" t="s">
+      <c r="A40" s="22">
+        <v>13</v>
+      </c>
+      <c r="B40" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="35" t="s">
+      <c r="D40" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="35" t="s">
+      <c r="E40" s="26" t="s">
         <v>59</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G40" s="35" t="s">
+      <c r="G40" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="H40" s="31" t="s">
+      <c r="H40" s="28" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="37"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
+      <c r="A41" s="23"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
       <c r="F41" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G41" s="25"/>
-      <c r="H41" s="31"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="28"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="36">
-        <v>3</v>
-      </c>
-      <c r="B42" s="38" t="s">
+      <c r="A42" s="22">
+        <v>14</v>
+      </c>
+      <c r="B42" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C42" s="40" t="s">
+      <c r="C42" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="35" t="s">
+      <c r="E42" s="26" t="s">
         <v>59</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="35" t="s">
+      <c r="G42" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="H42" s="31" t="s">
+      <c r="H42" s="28" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="37"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
       <c r="F43" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G43" s="25"/>
-      <c r="H43" s="32"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="29"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="11"/>
-      <c r="B44" s="38" t="s">
+      <c r="A44" s="22">
+        <v>15</v>
+      </c>
+      <c r="B44" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C44" s="40" t="s">
+      <c r="C44" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
       <c r="F44" s="5"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="13"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="11"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="12"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
       <c r="F45" s="5"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="13"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="11"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="20"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="13"/>
+      <c r="A46" s="22">
+        <v>16</v>
+      </c>
+      <c r="B46" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F46" s="6"/>
+      <c r="G46" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="20"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
+      <c r="A47" s="23"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
       <c r="F47" s="5"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="13"/>
-    </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="36">
-        <v>4</v>
-      </c>
-      <c r="B48" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="C48" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="37"/>
-      <c r="B49" s="39"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="10"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A36:H37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A14:A15"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="C28:C29"/>
@@ -2757,94 +2787,6 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="A18:H19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A36:H37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -2872,7 +2814,7 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId21"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="55" max="7" man="1"/>
+    <brk id="53" max="7" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2892,15 +2834,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2908,13 +2850,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2922,15 +2864,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2938,13 +2880,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2975,72 +2917,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
+      <c r="A6" s="22">
         <v>1</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="26" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="37"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="36">
+      <c r="A8" s="22">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3082,15 +3024,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3098,13 +3040,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3112,15 +3054,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3128,13 +3070,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3165,315 +3107,279 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
+      <c r="A6" s="22">
         <v>1</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="26" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="37"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="36">
+      <c r="A8" s="22">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="36">
+      <c r="A10" s="22">
         <v>3</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="37"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="36">
+      <c r="A12" s="22">
         <v>4</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="37"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
       <c r="F13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="36">
+      <c r="A14" s="22">
         <v>5</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="35" t="s">
+      <c r="G14" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G15" s="25"/>
+      <c r="G15" s="27"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="36">
+      <c r="A16" s="22">
         <v>6</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="27"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="36">
+      <c r="A18" s="22">
         <v>7</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="37"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
       <c r="F19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G19" s="25"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="36">
+      <c r="A20" s="22">
         <v>8</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="37"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
       <c r="F21" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="25"/>
+      <c r="G21" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3488,6 +3394,42 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3510,15 +3452,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3526,13 +3468,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3540,15 +3482,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3556,13 +3498,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3593,195 +3535,177 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
+      <c r="A6" s="22">
         <v>1</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="26" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="37"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="36">
+      <c r="A8" s="22">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="36">
+      <c r="A10" s="22">
         <v>3</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="37"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="36">
+      <c r="A12" s="22">
         <v>4</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="37"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
       <c r="F13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="36">
+      <c r="A14" s="22">
         <v>5</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="26" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="35" t="s">
+      <c r="G14" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G15" s="25"/>
+      <c r="G15" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3796,6 +3720,24 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3822,15 +3764,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3838,13 +3780,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3852,15 +3794,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3868,13 +3810,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3908,143 +3850,139 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
+      <c r="A6" s="22">
         <v>1</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="28" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="37"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="41"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="36">
+      <c r="A8" s="22">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="H8" s="57" t="s">
+      <c r="H8" s="49" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="41"/>
-      <c r="H9" s="58"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="50"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="36">
+      <c r="A10" s="22">
         <v>3</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="28" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="37"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="41"/>
-      <c r="H11" s="32"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H12" s="55"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="55"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="46"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="56"/>
+      <c r="A14" s="36"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:12" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
@@ -4065,7 +4003,7 @@
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="54" t="s">
+      <c r="G15" s="18" t="s">
         <v>9</v>
       </c>
       <c r="H15" s="8" t="s">
@@ -4073,67 +4011,62 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="36">
-        <v>1</v>
-      </c>
-      <c r="B16" s="38" t="s">
+      <c r="A16" s="22">
+        <v>4</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="28" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="G17" s="41"/>
-      <c r="H17" s="32"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H18" s="59"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="59"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="46"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="55"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
     </row>
     <row r="21" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
@@ -4154,7 +4087,7 @@
       <c r="F21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="54" t="s">
+      <c r="G21" s="18" t="s">
         <v>9</v>
       </c>
       <c r="H21" s="8" t="s">
@@ -4162,105 +4095,100 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="36">
-        <v>1</v>
-      </c>
-      <c r="B22" s="38" t="s">
+      <c r="A22" s="22">
+        <v>5</v>
+      </c>
+      <c r="B22" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="31" t="s">
+      <c r="H22" s="28" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="37"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
       <c r="F23" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="41"/>
-      <c r="H23" s="32"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="29"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="36">
-        <v>2</v>
-      </c>
-      <c r="B24" s="38" t="s">
+      <c r="A24" s="22">
+        <v>6</v>
+      </c>
+      <c r="B24" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="H24" s="57" t="s">
+      <c r="H24" s="49" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="37"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
       <c r="F25" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G25" s="41"/>
-      <c r="H25" s="58"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H26" s="55"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="50"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="59"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="46"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="55"/>
+      <c r="A28" s="36"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
     </row>
     <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
@@ -4281,7 +4209,7 @@
       <c r="F29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G29" s="54" t="s">
+      <c r="G29" s="18" t="s">
         <v>9</v>
       </c>
       <c r="H29" s="8" t="s">
@@ -4289,53 +4217,75 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="36">
-        <v>1</v>
-      </c>
-      <c r="B30" s="38" t="s">
+      <c r="A30" s="22">
+        <v>7</v>
+      </c>
+      <c r="B30" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="35" t="s">
+      <c r="D30" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="35" t="s">
+      <c r="E30" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G30" s="40" t="s">
+      <c r="G30" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="H30" s="31" t="s">
+      <c r="H30" s="28" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="37"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
       <c r="F31" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="G31" s="41"/>
-      <c r="H31" s="32"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="A27:G28"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A3:G4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A13:G14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="H8:H9"/>
@@ -4352,36 +4302,14 @@
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="A13:G14"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A3:G4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="A27:G28"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -4416,54 +4344,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="52"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="35"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="52"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="35"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="50"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="53"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="37"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -4494,63 +4422,63 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
+      <c r="A6" s="22">
         <v>1</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="28" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="37"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="36">
+      <c r="A8" s="22">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="26" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="9"/>
@@ -4558,402 +4486,353 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
       <c r="F9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="10"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="36">
+      <c r="A10" s="22">
         <v>3</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="33"/>
+      <c r="H10" s="20"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="37"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="34"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="50"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="33"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="50"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="33"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="36">
+      <c r="A14" s="22">
         <v>4</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="31"/>
+      <c r="G14" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" s="28"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="32"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="29"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="36">
+      <c r="A16" s="22">
         <v>5</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="35" t="s">
-        <v>18</v>
+      <c r="G16" s="26" t="s">
+        <v>74</v>
       </c>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="27"/>
       <c r="H17" s="10"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="36">
+      <c r="A18" s="22">
         <v>6</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="33"/>
+      <c r="G18" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="20"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="37"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
       <c r="F19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="25"/>
-      <c r="H19" s="34"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="21"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="50"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="33"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="50"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="33"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="36">
+      <c r="A22" s="22">
         <v>7</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="26" t="s">
         <v>59</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="31"/>
+      <c r="G22" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" s="28"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="37"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="32"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="29"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="36">
+      <c r="A24" s="22">
         <v>8</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="26" t="s">
         <v>59</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="35" t="s">
-        <v>18</v>
+      <c r="G24" s="26" t="s">
+        <v>74</v>
       </c>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="37"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
       <c r="F25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="25"/>
+      <c r="G25" s="27"/>
       <c r="H25" s="10"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="36">
+      <c r="A26" s="22">
         <v>9</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="35" t="s">
+      <c r="D26" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="26" t="s">
         <v>59</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="33"/>
+      <c r="G26" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" s="20"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="37"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
       <c r="F27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="25"/>
-      <c r="H27" s="34"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="21"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="A20:H21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A12:H13"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H4"/>
@@ -4969,6 +4848,55 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A12:H13"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="A20:H21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{09A6E995-6867-4571-9539-85B4B57268B9}"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13DED4A8-2692-4954-B59F-AC5443093628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7987E306-EEF5-4A7F-82DE-50DBE10092BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Kaunter Tiket'!$A$1:$H$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Kuarters!$A$1:$H$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PD Forest'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Pejabat!$A$1:$H$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pusat Sitaan Gentam'!$A$1:$G$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Taman Eko Rimba'!$A$1:$H$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Taman Negeri Kenaboi'!$A$1:$G$23</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="154">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -88,12 +88,6 @@
     <t>Blok Kuarters Pegawai</t>
   </si>
   <si>
-    <t>Dalam Keadaan Baik Dan Diduduki / Bangunan Pejabat</t>
-  </si>
-  <si>
-    <t>Perlu Penyelenggaraan Dan Tidak Diduduki / Bangunan Kuarters Pegawai</t>
-  </si>
-  <si>
     <t>Pejabat Renj Jempol</t>
   </si>
   <si>
@@ -106,12 +100,6 @@
     <t>2°48'33.0"N 102°23'33.8"E</t>
   </si>
   <si>
-    <t>Dalam Keadaan Baik Dan Diduduki / Bangunan Kuarters</t>
-  </si>
-  <si>
-    <t>Dalam Keadaan Baik Dan Tidak Diduduki / Bangunan Kuarters</t>
-  </si>
-  <si>
     <t>Kuala Pilah</t>
   </si>
   <si>
@@ -127,9 +115,6 @@
     <t>https://maps.app.goo.gl/xkAz7s3uw8r2982q9</t>
   </si>
   <si>
-    <t>Dalam Keadaan Baik Dan Diduduki / Bangunan Pengawal Keselamatan</t>
-  </si>
-  <si>
     <t>Blok Simpanan Sitaan</t>
   </si>
   <si>
@@ -145,9 +130,6 @@
     <t>Kg Tengkek, Batu Kikir</t>
   </si>
   <si>
-    <t>Bangunan Digunakan</t>
-  </si>
-  <si>
     <t>Gambar</t>
   </si>
   <si>
@@ -277,9 +259,6 @@
     <t xml:space="preserve">Dalam Keadaan Baik Dan Diduduki </t>
   </si>
   <si>
-    <t>Dalam Keadaan Baik Dan Diduduki</t>
-  </si>
-  <si>
     <t>Pejabat Sub Renj Mantin</t>
   </si>
   <si>
@@ -442,15 +421,6 @@
     <t>Blok Garaj PD Forest</t>
   </si>
   <si>
-    <t xml:space="preserve">Dalam Keadaan Baik Dan Diguna Pakai </t>
-  </si>
-  <si>
-    <t>Dalam Keadaan Baik Dan Diguna Pakai</t>
-  </si>
-  <si>
-    <t>Dalam Keadaan Baik Dan Tidak Diguna Pakai</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1-L3CNy2gkeuaMnbhqt0l33UL4FMto5eH/view?usp=sharing,https://drive.google.com/file/d/16XGy9sR2a0oiokqPSBaqFLgbo9fCnNG3/view?usp=sharing</t>
   </si>
   <si>
@@ -536,6 +506,12 @@
   </si>
   <si>
     <t xml:space="preserve">Perlu Penyelenggaraan Dan Tidak Diduduki </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status </t>
+  </si>
+  <si>
+    <t>Dalam Keadaan Baik Dan Tidak Digunakan</t>
   </si>
 </sst>
 </file>
@@ -720,7 +696,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -750,18 +726,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1196,60 +1160,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
+      <c r="A3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1266,10 +1230,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -1278,500 +1242,500 @@
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="22">
+      <c r="A6" s="18">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>39</v>
+      <c r="B6" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>133</v>
+        <v>24</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="29"/>
+        <v>23</v>
+      </c>
+      <c r="G7" s="23"/>
+      <c r="H7" s="25"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="22">
+      <c r="A8" s="18">
         <v>2</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>39</v>
+      <c r="B8" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>134</v>
+        <v>24</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
       <c r="F9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+        <v>23</v>
+      </c>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="38">
+      <c r="A10" s="34">
         <v>3</v>
       </c>
-      <c r="B10" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>39</v>
+      <c r="B10" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="H10" s="28"/>
+        <v>24</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="38"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
+        <v>23</v>
+      </c>
+      <c r="G11" s="23"/>
+      <c r="H11" s="25"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="22">
+      <c r="A12" s="18">
         <v>4</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>39</v>
+      <c r="B12" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
       <c r="F13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="29"/>
+        <v>23</v>
+      </c>
+      <c r="G13" s="23"/>
+      <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="22">
+      <c r="A14" s="18">
         <v>5</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>39</v>
+      <c r="B14" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="H14" s="28"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
       <c r="F15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="29"/>
+        <v>23</v>
+      </c>
+      <c r="G15" s="23"/>
+      <c r="H15" s="25"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="38">
+      <c r="A16" s="34">
         <v>6</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>39</v>
+      <c r="B16" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="H16" s="43"/>
+      <c r="H16" s="39"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="38"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
       <c r="F17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="29"/>
-      <c r="H17" s="44"/>
+        <v>23</v>
+      </c>
+      <c r="G17" s="23"/>
+      <c r="H17" s="40"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="22">
+      <c r="A18" s="18">
         <v>7</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>39</v>
+      <c r="B18" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="H18" s="20"/>
+        <v>24</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
       <c r="F19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="29"/>
-      <c r="H19" s="21"/>
+        <v>23</v>
+      </c>
+      <c r="G19" s="25"/>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="22"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="45"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="23"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="46"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="42"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="28"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="24"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="28"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="24"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="22"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="28"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="24"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="22"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="41"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="37"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="22"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="41"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="37"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="23"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="22"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="17"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="13"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="17"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="13"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="17"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="13"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="17"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="13"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H34" s="17"/>
+      <c r="H34" s="13"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H35" s="17"/>
+      <c r="H35" s="13"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G37" s="42"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G41" s="42"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="42"/>
-      <c r="J41" s="42"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="38"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G43" s="42"/>
-      <c r="H43" s="42"/>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G44" s="42"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="42"/>
-      <c r="J44" s="42"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="38"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G45" s="42"/>
-      <c r="H45" s="42"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="42"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="38"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G46" s="42"/>
-      <c r="H46" s="42"/>
-      <c r="I46" s="42"/>
-      <c r="J46" s="42"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="38"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G47" s="42"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="42"/>
-      <c r="J47" s="42"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="38"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G48" s="42"/>
-      <c r="H48" s="42"/>
-      <c r="I48" s="42"/>
-      <c r="J48" s="42"/>
+      <c r="G48" s="38"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
+      <c r="J48" s="38"/>
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G49" s="42"/>
-      <c r="H49" s="42"/>
-      <c r="I49" s="42"/>
-      <c r="J49" s="42"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="38"/>
+      <c r="J49" s="38"/>
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G50" s="42"/>
-      <c r="H50" s="42"/>
-      <c r="I50" s="42"/>
-      <c r="J50" s="42"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="99">
@@ -1890,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D54FEF-B8B0-455E-9719-4EECE694A16C}">
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" customWidth="1"/>
@@ -1906,54 +1870,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="31"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="35"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="33"/>
+      <c r="A3" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="37"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="33"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1962,16 +1926,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -1980,739 +1944,681 @@
         <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22">
+      <c r="A6" s="18">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>39</v>
+      <c r="D6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="H6" s="45" t="s">
-        <v>33</v>
+      <c r="G6" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="46"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22">
+      <c r="A8" s="18">
         <v>2</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>39</v>
+      <c r="D8" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>73</v>
+      <c r="G8" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
       <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22">
+      <c r="A10" s="18">
         <v>3</v>
       </c>
-      <c r="B10" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="26" t="s">
+      <c r="B10" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>39</v>
+      <c r="D10" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>35</v>
+      <c r="G10" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="29"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22">
+      <c r="A12" s="18">
         <v>4</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="26" t="s">
+      <c r="B12" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>39</v>
+      <c r="D12" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>36</v>
+      <c r="G12" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
       <c r="F13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="29"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22">
+      <c r="A14" s="18">
         <v>5</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="18">
+        <v>6</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="26" t="s">
+      <c r="G16" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H16" s="43" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="23"/>
+      <c r="H17" s="44"/>
+    </row>
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="29"/>
+    </row>
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="18">
+        <v>7</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="41" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-    </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="22">
-        <v>6</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="47" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="23"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="48"/>
-    </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="32" t="s">
+      <c r="C20" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="33"/>
-    </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="32"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="22">
-        <v>7</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>44</v>
+      <c r="D20" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>38</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H20" s="45"/>
+      <c r="G20" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="23"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
       <c r="F21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="46"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="42"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="22">
+      <c r="A22" s="18">
         <v>8</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="26" t="s">
+      <c r="B22" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>44</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>38</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H22" s="28"/>
+      <c r="G22" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H22" s="24"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="28"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="24"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22">
+      <c r="A24" s="18">
         <v>9</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="19"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="23"/>
+      <c r="H25" s="25"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="18">
+        <v>10</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H26" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="26" t="s">
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="19"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="18">
+        <v>11</v>
+      </c>
+      <c r="B28" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="7" t="s">
+      <c r="C28" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G24" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H24" s="28" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="5" t="s">
+      <c r="G28" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="19"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="29"/>
-    </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="22">
-        <v>10</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="29"/>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="28"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="29"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="18">
+        <v>12</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H32" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="G26" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="41" t="s">
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="19"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-    </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="22">
-        <v>11</v>
-      </c>
-      <c r="B28" s="24" t="s">
+      <c r="G33" s="23"/>
+      <c r="H33" s="42"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="18">
+        <v>13</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="7" t="s">
+      <c r="G34" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H34" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="G28" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="H28" s="41" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="23"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="5" t="s">
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="19"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G35" s="23"/>
+      <c r="H35" s="24"/>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="18">
+        <v>14</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H36" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-    </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="17"/>
-    </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="17"/>
-    </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="17"/>
-    </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="17"/>
-    </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="17"/>
-    </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="17"/>
-    </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="33"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="33"/>
+      <c r="A37" s="19"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G37" s="23"/>
+      <c r="H37" s="25"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="22">
-        <v>12</v>
-      </c>
-      <c r="B38" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D38" s="26" t="s">
+      <c r="A38" s="18">
+        <v>15</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H38" s="11"/>
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="19"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="11"/>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="18">
+        <v>16</v>
+      </c>
+      <c r="B40" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="H38" s="45" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="23"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G39" s="27"/>
-      <c r="H39" s="46"/>
-    </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="22">
-        <v>13</v>
-      </c>
-      <c r="B40" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="H40" s="28" t="s">
-        <v>93</v>
-      </c>
+      <c r="C40" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" s="6"/>
+      <c r="G40" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="H40" s="9"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="23"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G41" s="27"/>
-      <c r="H41" s="28"/>
-    </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="22">
-        <v>14</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D42" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="H42" s="28" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="23"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G43" s="27"/>
-      <c r="H43" s="29"/>
-    </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="22">
-        <v>15</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="26"/>
-      <c r="H44" s="11"/>
-    </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="23"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="11"/>
-    </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="22">
-        <v>16</v>
-      </c>
-      <c r="B46" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D46" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E46" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="23"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="10"/>
+      <c r="A41" s="19"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
     <mergeCell ref="H14:H15"/>
     <mergeCell ref="H16:H17"/>
-    <mergeCell ref="G46:G47"/>
     <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="G28:G29"/>
     <mergeCell ref="H28:H29"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A36:H37"/>
-    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A30:H31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="G38:G39"/>
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="B46:B47"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="C24:C25"/>
@@ -2807,14 +2713,14 @@
     <hyperlink ref="H24" r:id="rId15" xr:uid="{DAD5F602-20B1-420C-A71A-F100947483DF}"/>
     <hyperlink ref="H26" r:id="rId16" xr:uid="{D31AC8CF-A4BB-4C9E-B22B-29F22A8F60A5}"/>
     <hyperlink ref="H28" r:id="rId17" xr:uid="{151049AE-803B-48F6-BBC4-0E67775E894B}"/>
-    <hyperlink ref="H38" r:id="rId18" xr:uid="{996CE196-A38F-4809-96BC-C29C09152A5F}"/>
-    <hyperlink ref="H40" r:id="rId19" xr:uid="{465C1FFD-FC17-4DCC-B800-9D541E2DFD49}"/>
-    <hyperlink ref="H42" r:id="rId20" xr:uid="{8037C977-2882-407E-8610-AA6EA33F1A19}"/>
+    <hyperlink ref="H32" r:id="rId18" xr:uid="{996CE196-A38F-4809-96BC-C29C09152A5F}"/>
+    <hyperlink ref="H34" r:id="rId19" xr:uid="{465C1FFD-FC17-4DCC-B800-9D541E2DFD49}"/>
+    <hyperlink ref="H36" r:id="rId20" xr:uid="{8037C977-2882-407E-8610-AA6EA33F1A19}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId21"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="53" max="7" man="1"/>
+    <brk id="47" max="7" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2834,15 +2740,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2850,13 +2756,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2864,15 +2770,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="A3" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2880,13 +2786,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2904,10 +2810,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -2917,72 +2823,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22">
+      <c r="A6" s="18">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="26" t="s">
+      <c r="G6" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22">
+      <c r="A8" s="18">
         <v>2</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="26" t="s">
+      <c r="B8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3024,15 +2930,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3040,13 +2946,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3054,15 +2960,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="A3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3070,13 +2976,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3094,10 +3000,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3107,276 +3013,276 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22">
+      <c r="A6" s="18">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18">
+        <v>2</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="18">
+        <v>3</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="19"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="18">
+        <v>4</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="19"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="18">
+        <v>5</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="19"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="18">
+        <v>6</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="19"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="18">
+        <v>7</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="19"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="18">
+        <v>8</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="27"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22">
-        <v>2</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="27"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="22">
-        <v>3</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="27"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="22">
-        <v>4</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" s="27"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="22">
-        <v>5</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="27"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="22">
-        <v>6</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="23"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="27"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="22">
-        <v>7</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="27"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="22">
-        <v>8</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>42</v>
+      <c r="C20" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>36</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="23"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
       <c r="F21" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="27"/>
+        <v>64</v>
+      </c>
+      <c r="G21" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -3452,15 +3358,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3468,13 +3374,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3482,15 +3388,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="A3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3498,13 +3404,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3522,10 +3428,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
@@ -3535,174 +3441,174 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22">
+      <c r="A6" s="18">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>42</v>
+      <c r="B6" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="27"/>
+        <v>20</v>
+      </c>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22">
+      <c r="A8" s="18">
         <v>2</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>42</v>
+      <c r="B8" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
       <c r="F9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="27"/>
+        <v>20</v>
+      </c>
+      <c r="G9" s="23"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="22">
+      <c r="A10" s="18">
         <v>3</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>42</v>
+      <c r="B10" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="27"/>
+        <v>20</v>
+      </c>
+      <c r="G11" s="23"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="22">
+      <c r="A12" s="18">
         <v>4</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>42</v>
+      <c r="B12" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>36</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
       <c r="F13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="27"/>
+        <v>20</v>
+      </c>
+      <c r="G13" s="23"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="22">
+      <c r="A14" s="18">
         <v>5</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>42</v>
+      <c r="B14" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>36</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
       <c r="F15" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="27"/>
+        <v>59</v>
+      </c>
+      <c r="G15" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -3764,15 +3670,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3780,13 +3686,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3794,15 +3700,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="A3" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3810,13 +3716,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3834,155 +3740,155 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22">
+      <c r="A6" s="18">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="26" t="s">
+      <c r="B6" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="29"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22">
+      <c r="A8" s="18">
         <v>2</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="26" t="s">
+      <c r="B8" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="H8" s="45" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="H8" s="49" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="50"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="46"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="22">
+      <c r="A10" s="18">
         <v>3</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>39</v>
+      <c r="B10" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>143</v>
+        <v>22</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="29"/>
+        <v>59</v>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="25"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
+      <c r="A13" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="36"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="19"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:12" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
@@ -3995,78 +3901,78 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="22">
+      <c r="A16" s="18">
         <v>4</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>44</v>
+      <c r="B16" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>38</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="G16" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="28" t="s">
-        <v>139</v>
+        <v>127</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="23"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
       <c r="F17" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="29"/>
+        <v>128</v>
+      </c>
+      <c r="G17" s="27"/>
+      <c r="H17" s="25"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
+      <c r="A19" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
     </row>
     <row r="21" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
@@ -4079,116 +3985,116 @@
         <v>3</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="14" t="s">
         <v>9</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="22">
+      <c r="A22" s="18">
         <v>5</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" s="26" t="s">
+      <c r="B22" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="19"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G23" s="27"/>
+      <c r="H23" s="25"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="18">
+        <v>6</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" s="45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="19"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G25" s="27"/>
+      <c r="H25" s="46"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G22" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="H22" s="28" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="29"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="22">
-        <v>6</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G24" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G25" s="31"/>
-      <c r="H25" s="50"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="36"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
     </row>
     <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
@@ -4201,58 +4107,58 @@
         <v>3</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="14" t="s">
         <v>9</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="22">
+      <c r="A30" s="18">
         <v>7</v>
       </c>
-      <c r="B30" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>44</v>
+      <c r="B30" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>38</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="G30" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="H30" s="28" t="s">
-        <v>160</v>
+        <v>147</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
       <c r="F31" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G31" s="31"/>
-      <c r="H31" s="29"/>
+        <v>148</v>
+      </c>
+      <c r="G31" s="27"/>
+      <c r="H31" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="54">
@@ -4344,54 +4250,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="31"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="35"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="33"/>
+      <c r="A3" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="37"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="33"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -4400,434 +4306,434 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22">
+      <c r="A6" s="18">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>39</v>
+      <c r="D6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>34</v>
+      <c r="G6" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="25"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22">
+      <c r="A8" s="18">
         <v>2</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="30" t="s">
+      <c r="B8" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>18</v>
+      <c r="G8" s="22" t="s">
+        <v>68</v>
       </c>
       <c r="H8" s="9"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
       <c r="F9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="27"/>
+        <v>14</v>
+      </c>
+      <c r="G9" s="23"/>
       <c r="H9" s="10"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22">
+      <c r="A10" s="18">
         <v>3</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="30" t="s">
+      <c r="B10" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="20"/>
+      <c r="G10" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="16"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="21"/>
+        <v>14</v>
+      </c>
+      <c r="G11" s="23"/>
+      <c r="H11" s="17"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="33"/>
+      <c r="A12" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="33"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="29"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22">
+      <c r="A14" s="18">
         <v>4</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>44</v>
+      <c r="B14" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>38</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H14" s="28"/>
+      <c r="G14" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="H14" s="24"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
       <c r="F15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="29"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="25"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="22">
+      <c r="A16" s="18">
         <v>5</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>44</v>
+      <c r="B16" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>38</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>74</v>
+        <v>15</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>68</v>
       </c>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="23"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
       <c r="F17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="27"/>
+        <v>14</v>
+      </c>
+      <c r="G17" s="23"/>
       <c r="H17" s="10"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="22">
+      <c r="A18" s="18">
         <v>6</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>44</v>
+      <c r="B18" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>38</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="H18" s="20"/>
+        <v>15</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="16"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
       <c r="F19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="21"/>
+        <v>14</v>
+      </c>
+      <c r="G19" s="23"/>
+      <c r="H19" s="17"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="33"/>
+      <c r="A20" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="29"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="33"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="29"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="22">
+      <c r="A22" s="18">
         <v>7</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>59</v>
+      <c r="B22" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>53</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H22" s="28"/>
+      <c r="G22" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="24"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="29"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="25"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22">
+      <c r="A24" s="18">
         <v>8</v>
       </c>
-      <c r="B24" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>59</v>
+      <c r="B24" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>53</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>74</v>
+        <v>15</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>68</v>
       </c>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
       <c r="F25" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="27"/>
+        <v>14</v>
+      </c>
+      <c r="G25" s="23"/>
       <c r="H25" s="10"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="22">
+      <c r="A26" s="18">
         <v>9</v>
       </c>
-      <c r="B26" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>59</v>
+      <c r="B26" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>53</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" s="20"/>
+        <v>15</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" s="16"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
       <c r="F27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27" s="27"/>
-      <c r="H27" s="21"/>
+        <v>14</v>
+      </c>
+      <c r="G27" s="23"/>
+      <c r="H27" s="17"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7987E306-EEF5-4A7F-82DE-50DBE10092BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510BF360-C896-4273-9732-2B272FAB7A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -4425,7 +4425,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="H10" s="16"/>
       <c r="K10" s="2"/>
@@ -4531,7 +4531,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
@@ -4677,7 +4677,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
@@ -4717,7 +4717,7 @@
         <v>15</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="H26" s="16"/>
       <c r="K26" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510BF360-C896-4273-9732-2B272FAB7A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920C8358-BDC5-49F8-9D0F-68E67C4BBD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="155">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>Dalam Keadaan Baik Dan Tidak Digunakan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aset Rosak Serta Perlu Penyelenggaraan Dan Tidak Diduduki </t>
   </si>
 </sst>
 </file>
@@ -4491,7 +4494,7 @@
         <v>6</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H14" s="24"/>
       <c r="K14" s="2"/>
@@ -4531,7 +4534,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
@@ -4637,7 +4640,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H22" s="24"/>
       <c r="K22" s="2"/>
@@ -4677,7 +4680,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
@@ -4717,7 +4720,7 @@
         <v>15</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H26" s="16"/>
       <c r="K26" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920C8358-BDC5-49F8-9D0F-68E67C4BBD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE521721-BC09-4AB9-B6FB-AAB1AB2BD613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="154">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -512,9 +512,6 @@
   </si>
   <si>
     <t>Dalam Keadaan Baik Dan Tidak Digunakan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aset Rosak Serta Perlu Penyelenggaraan Dan Tidak Diduduki </t>
   </si>
 </sst>
 </file>
@@ -4494,7 +4491,7 @@
         <v>6</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H14" s="24"/>
       <c r="K14" s="2"/>
@@ -4534,7 +4531,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
@@ -4640,7 +4637,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H22" s="24"/>
       <c r="K22" s="2"/>
@@ -4680,7 +4677,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
@@ -4720,7 +4717,7 @@
         <v>15</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H26" s="16"/>
       <c r="K26" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE521721-BC09-4AB9-B6FB-AAB1AB2BD613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADD35D1-5DFA-4AED-9A2E-6CE06CD47670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="153">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -506,9 +506,6 @@
   </si>
   <si>
     <t xml:space="preserve">Perlu Penyelenggaraan Dan Tidak Diduduki </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status </t>
   </si>
   <si>
     <t>Dalam Keadaan Baik Dan Tidak Digunakan</t>
@@ -1485,7 +1482,7 @@
         <v>24</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H18" s="16"/>
     </row>
@@ -2365,7 +2362,7 @@
         <v>79</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H28" s="37" t="s">
         <v>81</v>
@@ -3066,7 +3063,7 @@
         <v>22</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3749,7 +3746,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>152</v>
+        <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>26</v>
@@ -4321,7 +4318,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>152</v>
+        <v>9</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>26</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADD35D1-5DFA-4AED-9A2E-6CE06CD47670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AFAA93-EDFC-4E8F-9C60-814F5CC44F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="151">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -292,9 +292,6 @@
     <t>2°28'20.3"N 102°13'54.8"E</t>
   </si>
   <si>
-    <t>Dalam Keadaan Baik Dan Tidak Diduduki</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/18PYaffP-sjWduJyRAyPOdlZV2Xy7Txer/view?usp=sharing,https://drive.google.com/file/d/19-HzjW4bIhsRIpyEfiOt81JFy3rEwaYj/view?usp=sharing,https://drive.google.com/file/d/1g9RhW9AFBHOOimXZ3NErgj7IBsJpXGfn/view?usp=sharing</t>
   </si>
   <si>
@@ -499,16 +496,13 @@
     <t>https://maps.app.goo.gl/5LFxR6uAtn4LhNQE6</t>
   </si>
   <si>
-    <t>Perlu Penyelenggaraan Dan Tidak Diduduki</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1MMBxS8irr5zyWbBP7mB-ymgWlmZqxvXD/view?usp=sharing,https://drive.google.com/file/d/1-6GqoLt0XhSdeCUKF1kMXrIv5hYr4PIY/view?usp=sharing</t>
   </si>
   <si>
-    <t xml:space="preserve">Perlu Penyelenggaraan Dan Tidak Diduduki </t>
-  </si>
-  <si>
     <t>Dalam Keadaan Baik Dan Tidak Digunakan</t>
+  </si>
+  <si>
+    <t>Perlu Penyelenggaraan Dan Tidak Digunakan</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>25</v>
@@ -1262,10 +1256,10 @@
         <v>24</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1285,7 +1279,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>25</v>
@@ -1300,10 +1294,10 @@
         <v>24</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1323,7 +1317,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>25</v>
@@ -1338,7 +1332,7 @@
         <v>24</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H10" s="24"/>
     </row>
@@ -1359,7 +1353,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="26" t="s">
         <v>25</v>
@@ -1374,7 +1368,7 @@
         <v>24</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H12" s="24"/>
     </row>
@@ -1395,7 +1389,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>25</v>
@@ -1410,7 +1404,7 @@
         <v>24</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H14" s="24"/>
     </row>
@@ -1431,7 +1425,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>25</v>
@@ -1446,7 +1440,7 @@
         <v>24</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H16" s="39"/>
     </row>
@@ -1467,7 +1461,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>25</v>
@@ -1482,7 +1476,7 @@
         <v>24</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H18" s="16"/>
     </row>
@@ -1964,7 +1958,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H6" s="41" t="s">
         <v>27</v>
@@ -2002,7 +1996,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>67</v>
@@ -2025,7 +2019,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>8</v>
@@ -2040,7 +2034,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>29</v>
@@ -2063,7 +2057,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>8</v>
@@ -2078,7 +2072,7 @@
         <v>6</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H12" s="24" t="s">
         <v>30</v>
@@ -2116,7 +2110,7 @@
         <v>15</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H14" s="37" t="s">
         <v>65</v>
@@ -2139,7 +2133,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C16" s="26" t="s">
         <v>13</v>
@@ -2154,7 +2148,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H16" s="43" t="s">
         <v>66</v>
@@ -2214,7 +2208,7 @@
         <v>6</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H20" s="41"/>
     </row>
@@ -2250,7 +2244,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H22" s="24"/>
     </row>
@@ -2286,7 +2280,7 @@
         <v>72</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H24" s="24" t="s">
         <v>73</v>
@@ -2324,7 +2318,7 @@
         <v>75</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H26" s="37" t="s">
         <v>76</v>
@@ -2362,10 +2356,10 @@
         <v>79</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2419,13 +2413,13 @@
         <v>53</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H32" s="41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2435,7 +2429,7 @@
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
       <c r="F33" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G33" s="23"/>
       <c r="H33" s="42"/>
@@ -2457,13 +2451,13 @@
         <v>53</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2473,7 +2467,7 @@
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
       <c r="F35" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G35" s="23"/>
       <c r="H35" s="24"/>
@@ -2483,7 +2477,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C36" s="26" t="s">
         <v>57</v>
@@ -2495,13 +2489,13 @@
         <v>53</v>
       </c>
       <c r="F36" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H36" s="24" t="s">
         <v>84</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="H36" s="24" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2511,7 +2505,7 @@
       <c r="D37" s="23"/>
       <c r="E37" s="23"/>
       <c r="F37" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G37" s="23"/>
       <c r="H37" s="25"/>
@@ -2521,7 +2515,7 @@
         <v>15</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" s="26" t="s">
         <v>57</v>
@@ -2530,7 +2524,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="5"/>
       <c r="G38" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H38" s="11"/>
     </row>
@@ -2562,7 +2556,7 @@
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H40" s="9"/>
     </row>
@@ -2839,7 +2833,7 @@
         <v>22</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -2873,7 +2867,7 @@
         <v>22</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3014,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>49</v>
@@ -3048,7 +3042,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>49</v>
@@ -3063,7 +3057,7 @@
         <v>22</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3082,7 +3076,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>49</v>
@@ -3097,7 +3091,7 @@
         <v>22</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3116,7 +3110,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C12" s="26" t="s">
         <v>49</v>
@@ -3131,7 +3125,7 @@
         <v>22</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -3150,7 +3144,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>49</v>
@@ -3165,7 +3159,7 @@
         <v>22</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -3184,7 +3178,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C16" s="26" t="s">
         <v>49</v>
@@ -3199,7 +3193,7 @@
         <v>22</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -3218,7 +3212,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C18" s="26" t="s">
         <v>49</v>
@@ -3233,7 +3227,7 @@
         <v>22</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -3252,7 +3246,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C20" s="26" t="s">
         <v>49</v>
@@ -3267,7 +3261,7 @@
         <v>22</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -3442,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>48</v>
@@ -3457,7 +3451,7 @@
         <v>22</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -3476,7 +3470,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>48</v>
@@ -3491,7 +3485,7 @@
         <v>22</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3510,7 +3504,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>48</v>
@@ -3525,7 +3519,7 @@
         <v>22</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3544,7 +3538,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" s="26" t="s">
         <v>48</v>
@@ -3559,7 +3553,7 @@
         <v>22</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -3578,7 +3572,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>48</v>
@@ -3593,7 +3587,7 @@
         <v>22</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -3757,7 +3751,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>52</v>
@@ -3772,10 +3766,10 @@
         <v>22</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -3795,7 +3789,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>52</v>
@@ -3810,10 +3804,10 @@
         <v>22</v>
       </c>
       <c r="G8" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="H8" s="45" t="s">
         <v>131</v>
-      </c>
-      <c r="H8" s="45" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3833,7 +3827,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>52</v>
@@ -3848,10 +3842,10 @@
         <v>22</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3868,7 +3862,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
@@ -3918,10 +3912,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>40</v>
@@ -3930,13 +3924,13 @@
         <v>38</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -3946,14 +3940,14 @@
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
       <c r="F17" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G17" s="27"/>
       <c r="H17" s="25"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="28"/>
@@ -4002,25 +3996,25 @@
         <v>5</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E22" s="22" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -4030,7 +4024,7 @@
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
       <c r="F23" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G23" s="27"/>
       <c r="H23" s="25"/>
@@ -4040,25 +4034,25 @@
         <v>6</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H24" s="45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -4068,14 +4062,14 @@
       <c r="D25" s="23"/>
       <c r="E25" s="23"/>
       <c r="F25" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G25" s="27"/>
       <c r="H25" s="46"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
@@ -4124,7 +4118,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C30" s="26" t="s">
         <v>45</v>
@@ -4136,13 +4130,13 @@
         <v>38</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -4152,7 +4146,7 @@
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="F31" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G31" s="27"/>
       <c r="H31" s="25"/>
@@ -4344,7 +4338,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H6" s="24" t="s">
         <v>28</v>
@@ -4367,7 +4361,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>13</v>
@@ -4382,7 +4376,7 @@
         <v>15</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="H8" s="9"/>
       <c r="K8" s="2"/>
@@ -4407,7 +4401,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>13</v>
@@ -4422,7 +4416,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H10" s="16"/>
       <c r="K10" s="2"/>
@@ -4473,7 +4467,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>42</v>
@@ -4488,7 +4482,7 @@
         <v>6</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H14" s="24"/>
       <c r="K14" s="2"/>
@@ -4513,7 +4507,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" s="22" t="s">
         <v>42</v>
@@ -4528,7 +4522,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
@@ -4553,7 +4547,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C18" s="22" t="s">
         <v>42</v>
@@ -4568,7 +4562,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="H18" s="16"/>
       <c r="K18" s="2"/>
@@ -4619,7 +4613,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" s="26" t="s">
         <v>57</v>
@@ -4634,7 +4628,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H22" s="24"/>
       <c r="K22" s="2"/>
@@ -4659,7 +4653,7 @@
         <v>8</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>58</v>
@@ -4674,7 +4668,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
@@ -4699,7 +4693,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>58</v>
@@ -4714,7 +4708,7 @@
         <v>15</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H26" s="16"/>
       <c r="K26" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AFAA93-EDFC-4E8F-9C60-814F5CC44F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0E57F9-AD35-4B91-8B54-DD8A35DE9C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -502,7 +502,7 @@
     <t>Dalam Keadaan Baik Dan Tidak Digunakan</t>
   </si>
   <si>
-    <t>Perlu Penyelenggaraan Dan Tidak Digunakan</t>
+    <t>Rosak Dan Perlu Penyelenggaraan Serta Tidak Digunakan</t>
   </si>
 </sst>
 </file>
@@ -728,11 +728,35 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -746,50 +770,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -808,6 +799,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1151,60 +1151,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1237,399 +1237,399 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="16" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="16" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="34">
+      <c r="A10" s="42">
         <v>3</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="24"/>
+      <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="34"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
+      <c r="A11" s="42"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
+      <c r="A12" s="26">
         <v>4</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="24"/>
+      <c r="H12" s="16"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="18">
+      <c r="A14" s="26">
         <v>5</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="24"/>
+      <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="34">
+      <c r="A16" s="42">
         <v>6</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="39"/>
+      <c r="H16" s="36"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="34"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="23"/>
-      <c r="H17" s="40"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="37"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="18">
+      <c r="A18" s="26">
         <v>7</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="H18" s="16"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
       <c r="F19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="25"/>
-      <c r="H19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="33"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="41"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="38"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="42"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="39"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="24"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="24"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="37"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="34"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="37"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="34"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
+      <c r="A29" s="27"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="25"/>
+      <c r="G30" s="17"/>
       <c r="H30" s="13"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="A31" s="27"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="25"/>
+      <c r="G31" s="17"/>
       <c r="H31" s="13"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="18"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="25"/>
+      <c r="G32" s="17"/>
       <c r="H32" s="13"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
+      <c r="A33" s="27"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="25"/>
+      <c r="G33" s="17"/>
       <c r="H33" s="13"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -1639,159 +1639,113 @@
       <c r="H35" s="13"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
-      <c r="J40" s="38"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="38"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
-      <c r="J42" s="38"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="35"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
-      <c r="J44" s="38"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
-      <c r="J45" s="38"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
+      <c r="J45" s="35"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
-      <c r="J46" s="38"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="38"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-      <c r="J48" s="38"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="35"/>
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="38"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="35"/>
+      <c r="I49" s="35"/>
+      <c r="J49" s="35"/>
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="G36:J50"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H4"/>
     <mergeCell ref="A10:A11"/>
@@ -1808,27 +1762,73 @@
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D10:D11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="B18:B19"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G36:J50"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H18:H19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{08DF4C9A-9F75-4524-A39E-D32455244FE2}"/>
@@ -1861,54 +1861,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="31"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="19"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="19"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="29"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="21"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="23"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1939,215 +1939,215 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="H6" s="38" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="42"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="39"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="16" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+      <c r="A10" s="26">
         <v>3</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
+      <c r="A12" s="26">
         <v>4</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18">
+      <c r="A14" s="26">
         <v>5</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="34" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18">
+      <c r="A16" s="26">
         <v>6</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="24" t="s">
         <v>130</v>
       </c>
       <c r="H16" s="43" t="s">
@@ -2155,423 +2155,511 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="23"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="44"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18">
+      <c r="A20" s="26">
         <v>7</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H20" s="41"/>
+      <c r="H20" s="38"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
       <c r="F21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="23"/>
-      <c r="H21" s="42"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="39"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18">
+      <c r="A22" s="26">
         <v>8</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H22" s="24"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="24"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18">
+      <c r="A24" s="26">
         <v>9</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H24" s="24" t="s">
+      <c r="H24" s="16" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
       <c r="F25" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="18">
+      <c r="A26" s="26">
         <v>10</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H26" s="37" t="s">
+      <c r="H26" s="34" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
       <c r="F27" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18">
+      <c r="A28" s="26">
         <v>11</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="22" t="s">
+      <c r="G28" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="H28" s="37" t="s">
+      <c r="H28" s="34" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
+      <c r="A29" s="27"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
       <c r="F29" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="21"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="18">
+      <c r="A32" s="26">
         <v>12</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="22" t="s">
+      <c r="G32" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H32" s="41" t="s">
+      <c r="H32" s="38" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
+      <c r="A33" s="27"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
       <c r="F33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G33" s="23"/>
-      <c r="H33" s="42"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="39"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="18">
+      <c r="A34" s="26">
         <v>13</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H34" s="24" t="s">
+      <c r="H34" s="16" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
+      <c r="A35" s="27"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
       <c r="F35" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G35" s="23"/>
-      <c r="H35" s="24"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="18">
+      <c r="A36" s="26">
         <v>14</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G36" s="22" t="s">
+      <c r="G36" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="H36" s="24" t="s">
+      <c r="H36" s="16" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
+      <c r="A37" s="27"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
       <c r="F37" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G37" s="23"/>
-      <c r="H37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="18">
+      <c r="A38" s="26">
         <v>15</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="30" t="s">
         <v>57</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="24" t="s">
         <v>130</v>
       </c>
       <c r="H38" s="11"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="27"/>
+      <c r="A39" s="27"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="31"/>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
       <c r="F39" s="5"/>
-      <c r="G39" s="23"/>
+      <c r="G39" s="25"/>
       <c r="H39" s="11"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="18">
+      <c r="A40" s="26">
         <v>16</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D40" s="22" t="s">
+      <c r="D40" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E40" s="22" t="s">
+      <c r="E40" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F40" s="6"/>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="24" t="s">
         <v>130</v>
       </c>
       <c r="H40" s="9"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="19"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
+      <c r="A41" s="27"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="23"/>
+      <c r="G41" s="25"/>
       <c r="H41" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A18:H19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="C40:C41"/>
     <mergeCell ref="D40:D41"/>
@@ -2596,94 +2684,6 @@
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="H32:H33"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A18:H19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -2731,15 +2731,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2747,13 +2747,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2761,15 +2761,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2777,13 +2777,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2814,72 +2814,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="23"/>
+      <c r="G9" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2921,15 +2921,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2937,13 +2937,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2951,15 +2951,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2967,13 +2967,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3004,279 +3004,315 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="24" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="24" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="23"/>
+      <c r="G9" s="25"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+      <c r="A10" s="26">
         <v>3</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="23"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
+      <c r="A12" s="26">
         <v>4</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="25"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="18">
+      <c r="A14" s="26">
         <v>5</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G15" s="23"/>
+      <c r="G15" s="25"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="18">
+      <c r="A16" s="26">
         <v>6</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="23"/>
+      <c r="G17" s="25"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="18">
+      <c r="A18" s="26">
         <v>7</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
       <c r="F19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="23"/>
+      <c r="G19" s="25"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="18">
+      <c r="A20" s="26">
         <v>8</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
       <c r="F21" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G21" s="23"/>
+      <c r="G21" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3291,42 +3327,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3349,15 +3349,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3365,13 +3365,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3379,15 +3379,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3395,13 +3395,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3432,177 +3432,195 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="23"/>
+      <c r="G9" s="25"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+      <c r="A10" s="26">
         <v>3</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="23"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
+      <c r="A12" s="26">
         <v>4</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="25"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="18">
+      <c r="A14" s="26">
         <v>5</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="23"/>
+      <c r="G15" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3617,24 +3635,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3661,15 +3661,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3677,13 +3677,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3691,15 +3691,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3707,13 +3707,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3747,63 +3747,63 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="16" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="25"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="30" t="s">
         <v>130</v>
       </c>
       <c r="H8" s="45" t="s">
@@ -3811,74 +3811,74 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="31"/>
       <c r="H9" s="46"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+      <c r="A10" s="26">
         <v>3</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="16" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="25"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:12" ht="31.5" x14ac:dyDescent="0.2">
@@ -3908,62 +3908,62 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18">
+      <c r="A16" s="26">
         <v>4</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="16" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="25"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="17"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="32"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
     </row>
     <row r="21" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
@@ -3992,63 +3992,63 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="18">
+      <c r="A22" s="26">
         <v>5</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G22" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="H22" s="24" t="s">
+      <c r="H22" s="16" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
       <c r="F23" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="25"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="18">
+      <c r="A24" s="26">
         <v>6</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="30" t="s">
         <v>130</v>
       </c>
       <c r="H24" s="45" t="s">
@@ -4056,36 +4056,36 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
       <c r="F25" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G25" s="27"/>
+      <c r="G25" s="31"/>
       <c r="H25" s="46"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="32"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
     </row>
     <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
@@ -4114,59 +4114,69 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="18">
+      <c r="A30" s="26">
         <v>7</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="H30" s="24" t="s">
+      <c r="H30" s="16" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="A31" s="27"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
       <c r="F31" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="25"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A3:G4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="A27:G28"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="A19:G20"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H22:H23"/>
@@ -4183,30 +4193,20 @@
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="A19:G20"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="A27:G28"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A3:G4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -4241,54 +4241,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="31"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="19"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="19"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="29"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="21"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="23"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -4319,63 +4319,63 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="16" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="24" t="s">
         <v>130</v>
       </c>
       <c r="H8" s="9"/>
@@ -4383,145 +4383,145 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="23"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="10"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+      <c r="A10" s="26">
         <v>3</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="H10" s="16"/>
+      <c r="H10" s="32"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="17"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="33"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18">
+      <c r="A14" s="26">
         <v>4</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="H14" s="24"/>
+      <c r="H14" s="16"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="17"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18">
+      <c r="A16" s="26">
         <v>5</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="24" t="s">
         <v>150</v>
       </c>
       <c r="H16" s="9"/>
@@ -4529,145 +4529,145 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="23"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="10"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18">
+      <c r="A18" s="26">
         <v>6</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="H18" s="16"/>
+      <c r="H18" s="32"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
       <c r="F19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="23"/>
-      <c r="H19" s="17"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="33"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18">
+      <c r="A22" s="26">
         <v>7</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="H22" s="24"/>
+      <c r="H22" s="16"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="17"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18">
+      <c r="A24" s="26">
         <v>8</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="24" t="s">
         <v>150</v>
       </c>
       <c r="H24" s="9"/>
@@ -4675,61 +4675,110 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
       <c r="F25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="23"/>
+      <c r="G25" s="25"/>
       <c r="H25" s="10"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="18">
+      <c r="A26" s="26">
         <v>9</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="H26" s="16"/>
+      <c r="H26" s="32"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
       <c r="F27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="17"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="33"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="A20:H21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A12:H13"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H4"/>
@@ -4745,55 +4794,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="A12:H13"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="A20:H21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{09A6E995-6867-4571-9539-85B4B57268B9}"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0E57F9-AD35-4B91-8B54-DD8A35DE9C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B947B1C1-AA8B-460B-A3DF-A539E7335119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="150">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -500,9 +500,6 @@
   </si>
   <si>
     <t>Dalam Keadaan Baik Dan Tidak Digunakan</t>
-  </si>
-  <si>
-    <t>Rosak Dan Perlu Penyelenggaraan Serta Tidak Digunakan</t>
   </si>
 </sst>
 </file>
@@ -728,35 +725,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -764,11 +743,8 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -776,11 +752,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -800,14 +791,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1151,60 +1148,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1237,399 +1234,399 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="20">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="31" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="31" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
       <c r="F9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="16"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="31"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="42">
+      <c r="A10" s="25">
         <v>3</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="16"/>
+      <c r="H10" s="31"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="42"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="22"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="26">
+      <c r="A12" s="20">
         <v>4</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="16"/>
+      <c r="H12" s="31"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
       <c r="F13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="22"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
+      <c r="A14" s="20">
         <v>5</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="16"/>
+      <c r="H14" s="31"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="42">
+      <c r="A16" s="25">
         <v>6</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="36"/>
+      <c r="H16" s="34"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="42"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
       <c r="F17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="25"/>
-      <c r="H17" s="37"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="35"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="26">
+      <c r="A18" s="20">
         <v>7</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="38"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
       <c r="F19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="33"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="39"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="38"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="36"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="39"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="37"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="26"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="31"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="16"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="31"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="26"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="16"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="31"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="26"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="34"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="32"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="26"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="34"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="32"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="27"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
+      <c r="A29" s="21"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="26"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="17"/>
+      <c r="G30" s="22"/>
       <c r="H30" s="13"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="27"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="17"/>
+      <c r="G31" s="22"/>
       <c r="H31" s="13"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="26"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="17"/>
+      <c r="G32" s="22"/>
       <c r="H32" s="13"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="27"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="17"/>
+      <c r="G33" s="22"/>
       <c r="H33" s="13"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -1639,97 +1636,180 @@
       <c r="H35" s="13"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="35"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G41" s="35"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="35"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="35"/>
-      <c r="J42" s="35"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="35"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G45" s="35"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="35"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="33"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="35"/>
+      <c r="G47" s="33"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G48" s="35"/>
-      <c r="H48" s="35"/>
-      <c r="I48" s="35"/>
-      <c r="J48" s="35"/>
+      <c r="G48" s="33"/>
+      <c r="H48" s="33"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G49" s="35"/>
-      <c r="H49" s="35"/>
-      <c r="I49" s="35"/>
-      <c r="J49" s="35"/>
+      <c r="G49" s="33"/>
+      <c r="H49" s="33"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G50" s="35"/>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35"/>
-      <c r="J50" s="35"/>
+      <c r="G50" s="33"/>
+      <c r="H50" s="33"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="99">
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G36:J50"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B8:B9"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="B12:B13"/>
@@ -1746,89 +1826,6 @@
     <mergeCell ref="E16:E17"/>
     <mergeCell ref="G16:G17"/>
     <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="G36:J50"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H18:H19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{08DF4C9A-9F75-4524-A39E-D32455244FE2}"/>
@@ -1861,54 +1858,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="40"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="19"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="40"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="21"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="41"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="23"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="42"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1939,215 +1936,215 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="20">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="38" t="s">
+      <c r="H6" s="36" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="39"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="37"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="31" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
       <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="16"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="31"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="A10" s="20">
         <v>3</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="31" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="22"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="26">
+      <c r="A12" s="20">
         <v>4</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="31" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
       <c r="F13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="22"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
+      <c r="A14" s="20">
         <v>5</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="34" t="s">
+      <c r="H14" s="32" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26">
+      <c r="A16" s="20">
         <v>6</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="16" t="s">
         <v>130</v>
       </c>
       <c r="H16" s="43" t="s">
@@ -2155,423 +2152,511 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
       <c r="F17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="44"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="21"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="21"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="26">
+      <c r="A20" s="20">
         <v>7</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H20" s="38"/>
+      <c r="H20" s="36"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="25"/>
-      <c r="H21" s="39"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="37"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="26">
+      <c r="A22" s="20">
         <v>8</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="G22" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H22" s="16"/>
+      <c r="H22" s="31"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="16"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="31"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26">
+      <c r="A24" s="20">
         <v>9</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="24" t="s">
+      <c r="G24" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H24" s="16" t="s">
+      <c r="H24" s="31" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G25" s="25"/>
-      <c r="H25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="22"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="26">
+      <c r="A26" s="20">
         <v>10</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G26" s="24" t="s">
+      <c r="G26" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H26" s="34" t="s">
+      <c r="H26" s="32" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
       <c r="F27" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="26">
+      <c r="A28" s="20">
         <v>11</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="32" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="27"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
+      <c r="A29" s="21"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
       <c r="F29" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="21"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="41"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="21"/>
+      <c r="A31" s="27"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="41"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="26">
+      <c r="A32" s="20">
         <v>12</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="16" t="s">
         <v>53</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="24" t="s">
+      <c r="G32" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H32" s="38" t="s">
+      <c r="H32" s="36" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="27"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
       <c r="F33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G33" s="25"/>
-      <c r="H33" s="39"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="37"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="26">
+      <c r="A34" s="20">
         <v>13</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C34" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="16" t="s">
         <v>53</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G34" s="24" t="s">
+      <c r="G34" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H34" s="16" t="s">
+      <c r="H34" s="31" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="27"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
       <c r="F35" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G35" s="25"/>
-      <c r="H35" s="16"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="31"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="26">
+      <c r="A36" s="20">
         <v>14</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="D36" s="24" t="s">
+      <c r="D36" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="16" t="s">
         <v>53</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G36" s="24" t="s">
+      <c r="G36" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="31" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="27"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
+      <c r="A37" s="21"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
       <c r="F37" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G37" s="25"/>
-      <c r="H37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="22"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="26">
+      <c r="A38" s="20">
         <v>15</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="23" t="s">
         <v>57</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="24" t="s">
+      <c r="G38" s="16" t="s">
         <v>130</v>
       </c>
       <c r="H38" s="11"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="27"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="31"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="24"/>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
       <c r="F39" s="5"/>
-      <c r="G39" s="25"/>
+      <c r="G39" s="17"/>
       <c r="H39" s="11"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="26">
+      <c r="A40" s="20">
         <v>16</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D40" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E40" s="16" t="s">
         <v>53</v>
       </c>
       <c r="F40" s="6"/>
-      <c r="G40" s="24" t="s">
+      <c r="G40" s="16" t="s">
         <v>130</v>
       </c>
       <c r="H40" s="9"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="27"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="25"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A30:H31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A14:A15"/>
     <mergeCell ref="D28:D29"/>
     <mergeCell ref="E28:E29"/>
     <mergeCell ref="A1:H2"/>
@@ -2596,94 +2681,6 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A30:H31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="H32:H33"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -2731,15 +2728,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2747,13 +2744,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2761,15 +2758,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2777,13 +2774,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2814,72 +2811,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="20">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2921,15 +2918,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2937,13 +2934,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2951,15 +2948,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2967,13 +2964,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3004,315 +3001,279 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="20">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="16" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="16" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="A10" s="20">
         <v>3</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="26">
+      <c r="A12" s="20">
         <v>4</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
       <c r="F13" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
+      <c r="A14" s="20">
         <v>5</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G15" s="25"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="26">
+      <c r="A16" s="20">
         <v>6</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
       <c r="F17" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="17"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="26">
+      <c r="A18" s="20">
         <v>7</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
       <c r="F19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="25"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="26">
+      <c r="A20" s="20">
         <v>8</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G21" s="25"/>
+      <c r="G21" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3327,6 +3288,42 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3349,15 +3346,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3365,13 +3362,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3379,15 +3376,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3395,13 +3392,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3432,195 +3429,177 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="20">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="A10" s="20">
         <v>3</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="26">
+      <c r="A12" s="20">
         <v>4</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
       <c r="F13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
+      <c r="A14" s="20">
         <v>5</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="25"/>
+      <c r="G15" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G4"/>
@@ -3635,6 +3614,24 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3661,15 +3658,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3677,13 +3674,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3691,15 +3688,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3707,13 +3704,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3747,63 +3744,63 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="20">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="31" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="17"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="23" t="s">
         <v>130</v>
       </c>
       <c r="H8" s="45" t="s">
@@ -3811,74 +3808,74 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="46"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="A10" s="20">
         <v>3</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="31" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="17"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="22"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:12" ht="31.5" x14ac:dyDescent="0.2">
@@ -3908,62 +3905,62 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26">
+      <c r="A16" s="20">
         <v>4</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G16" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="31" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
       <c r="F17" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="17"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="22"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
     </row>
     <row r="21" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
@@ -3992,63 +3989,63 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="26">
+      <c r="A22" s="20">
         <v>5</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="G22" s="30" t="s">
+      <c r="G22" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="31" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="17"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="22"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="26">
+      <c r="A24" s="20">
         <v>6</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="30" t="s">
+      <c r="G24" s="23" t="s">
         <v>130</v>
       </c>
       <c r="H24" s="45" t="s">
@@ -4056,36 +4053,36 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G25" s="31"/>
+      <c r="G25" s="24"/>
       <c r="H25" s="46"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
     </row>
     <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
@@ -4114,53 +4111,73 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="26">
+      <c r="A30" s="20">
         <v>7</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G30" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="H30" s="16" t="s">
+      <c r="G30" s="23"/>
+      <c r="H30" s="31" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="27"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
       <c r="F31" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G31" s="31"/>
-      <c r="H31" s="17"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="A27:G28"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A3:G4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A13:G14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="H8:H9"/>
@@ -4177,36 +4194,14 @@
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="A13:G14"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A3:G4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="A27:G28"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -4241,54 +4236,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="40"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="19"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="40"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="21"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="41"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="23"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="42"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -4319,466 +4314,399 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="20">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="H6" s="16" t="s">
+      <c r="G6" s="16"/>
+      <c r="H6" s="31" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="24" t="s">
-        <v>130</v>
-      </c>
+      <c r="G8" s="16"/>
       <c r="H8" s="9"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
       <c r="F9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="17"/>
       <c r="H9" s="10"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="26">
+      <c r="A10" s="20">
         <v>3</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="H10" s="32"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="38"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="33"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="39"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="21"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="41"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="21"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="41"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="26">
+      <c r="A14" s="20">
         <v>4</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="H14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="31"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="22"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26">
+      <c r="A16" s="20">
         <v>5</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="24" t="s">
-        <v>150</v>
-      </c>
+      <c r="G16" s="16"/>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
       <c r="F17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="10"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="26">
+      <c r="A18" s="20">
         <v>6</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="H18" s="32"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="38"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
       <c r="F19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="25"/>
-      <c r="H19" s="33"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="39"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="21"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="41"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="21"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="41"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="26">
+      <c r="A22" s="20">
         <v>7</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="16" t="s">
         <v>53</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="H22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="31"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="22"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26">
+      <c r="A24" s="20">
         <v>8</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="16" t="s">
         <v>53</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="24" t="s">
-        <v>150</v>
-      </c>
+      <c r="G24" s="16"/>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="25"/>
+      <c r="G25" s="17"/>
       <c r="H25" s="10"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="26">
+      <c r="A26" s="20">
         <v>9</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="16" t="s">
         <v>53</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="H26" s="32"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="38"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
       <c r="F27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G27" s="25"/>
-      <c r="H27" s="33"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="39"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="A20:H21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A12:H13"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H4"/>
@@ -4794,6 +4722,55 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A12:H13"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="A20:H21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{09A6E995-6867-4571-9539-85B4B57268B9}"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B947B1C1-AA8B-460B-A3DF-A539E7335119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A67B723-727F-48D7-A0FF-1F7822D825FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="152">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -500,6 +500,12 @@
   </si>
   <si>
     <t>Dalam Keadaan Baik Dan Tidak Digunakan</t>
+  </si>
+  <si>
+    <t>Rosak Dan Perlu Selenggara</t>
+  </si>
+  <si>
+    <t>Perlu Selenggara Dan Tidak Digunakan</t>
   </si>
 </sst>
 </file>
@@ -684,7 +690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -711,9 +717,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1148,60 +1151,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1234,496 +1237,496 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="30" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="22"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="21"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="20">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="30" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="31"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="30"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="25">
+      <c r="A10" s="24">
         <v>3</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="31"/>
+      <c r="H10" s="30"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="25"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="22"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="20">
+      <c r="A12" s="19">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="31"/>
+      <c r="H12" s="30"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="17"/>
-      <c r="H13" s="22"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="20">
+      <c r="A14" s="19">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="31"/>
+      <c r="H14" s="30"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="17"/>
-      <c r="H15" s="22"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="21"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="25">
+      <c r="A16" s="24">
         <v>6</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="25"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="35"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="34"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="20">
+      <c r="A18" s="19">
         <v>7</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="H18" s="38"/>
+      <c r="H18" s="37"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="39"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="38"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="36"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="35"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="37"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="36"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="20"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="31"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="30"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="31"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="30"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="20"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="31"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="30"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="20"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="32"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="31"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="20"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="32"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="31"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="13"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="12"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="13"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="12"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="13"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="12"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="13"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="12"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H34" s="13"/>
+      <c r="H34" s="12"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H35" s="13"/>
+      <c r="H35" s="12"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="33"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G49" s="33"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.2">
-      <c r="G50" s="33"/>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="99">
@@ -1858,54 +1861,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="40"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="39"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="40"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="39"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="40"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="42"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="41"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1936,639 +1939,647 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="H6" s="35" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="37"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="36"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="30" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="31"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="30"/>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20">
+      <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="30" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="22"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20">
+      <c r="A12" s="19">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="31" t="s">
+      <c r="H12" s="30" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="17"/>
-      <c r="H13" s="22"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="21"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20">
+      <c r="A14" s="19">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="31" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20">
+      <c r="A16" s="19">
         <v>6</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="43" t="s">
+      <c r="H16" s="42" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="44"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="43"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="41"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="40"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="41"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="40"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20">
+      <c r="A20" s="19">
         <v>7</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H20" s="36"/>
+      <c r="H20" s="35"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
       <c r="F21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="17"/>
-      <c r="H21" s="37"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="36"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20">
+      <c r="A22" s="19">
         <v>8</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H22" s="31"/>
+      <c r="H22" s="30"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="17"/>
-      <c r="H23" s="31"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="30"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20">
+      <c r="A24" s="19">
         <v>9</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H24" s="31" t="s">
+      <c r="H24" s="30" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G25" s="17"/>
-      <c r="H25" s="22"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="21"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20">
+      <c r="A26" s="19">
         <v>10</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H26" s="32" t="s">
+      <c r="H26" s="31" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20">
+      <c r="A28" s="19">
         <v>11</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="H28" s="32" t="s">
+      <c r="H28" s="31" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
       <c r="F29" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="41"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="40"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="41"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="40"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20">
+      <c r="A32" s="19">
         <v>12</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H32" s="36" t="s">
+      <c r="H32" s="35" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
       <c r="F33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G33" s="17"/>
-      <c r="H33" s="37"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="36"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20">
+      <c r="A34" s="19">
         <v>13</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H34" s="31" t="s">
+      <c r="H34" s="30" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
       <c r="F35" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G35" s="17"/>
-      <c r="H35" s="31"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="30"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20">
+      <c r="A36" s="19">
         <v>14</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="E36" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H36" s="31" t="s">
+      <c r="H36" s="30" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
       <c r="F37" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G37" s="17"/>
-      <c r="H37" s="22"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="21"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20">
+      <c r="A38" s="19">
         <v>15</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="16" t="s">
+      <c r="D38" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" s="15" t="s">
         <v>130</v>
       </c>
       <c r="H38" s="11"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="17"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="16"/>
       <c r="H39" s="11"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20">
+      <c r="A40" s="19">
         <v>16</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="16" t="s">
+      <c r="F40" s="7"/>
+      <c r="G40" s="15" t="s">
         <v>130</v>
       </c>
       <c r="H40" s="9"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="17"/>
+      <c r="G41" s="16"/>
       <c r="H41" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="114">
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A30:H31"/>
     <mergeCell ref="A32:A33"/>
@@ -2578,6 +2589,8 @@
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="H32:H33"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
     <mergeCell ref="C40:C41"/>
     <mergeCell ref="D40:D41"/>
     <mergeCell ref="E40:E41"/>
@@ -2728,15 +2741,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2744,13 +2757,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2758,15 +2771,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2774,13 +2787,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2811,72 +2824,72 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="17"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2918,15 +2931,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2934,13 +2947,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2948,15 +2961,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2964,13 +2977,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3001,276 +3014,276 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="15" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="17"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="15" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="20">
+      <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="17"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="20">
+      <c r="A12" s="19">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="17"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="20">
+      <c r="A14" s="19">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G15" s="17"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="20">
+      <c r="A16" s="19">
         <v>6</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="17"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="20">
+      <c r="A18" s="19">
         <v>7</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="17"/>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="20">
+      <c r="A20" s="19">
         <v>8</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
       <c r="F21" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G21" s="17"/>
+      <c r="G21" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -3346,15 +3359,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3362,13 +3375,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3376,15 +3389,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3392,13 +3405,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3429,174 +3442,174 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="17"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="20">
+      <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="17"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="20">
+      <c r="A12" s="19">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="17"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="20">
+      <c r="A14" s="19">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="17"/>
+      <c r="G15" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -3658,15 +3671,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3674,13 +3687,13 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -3688,15 +3701,15 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -3704,13 +3717,13 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3744,139 +3757,139 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="30" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="24"/>
-      <c r="H7" s="22"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="21"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="44" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="24"/>
-      <c r="H9" s="46"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="45"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="20">
+      <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="30" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="24"/>
-      <c r="H11" s="22"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="15"/>
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="14"/>
     </row>
     <row r="15" spans="1:12" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
@@ -3897,7 +3910,7 @@
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="13" t="s">
         <v>9</v>
       </c>
       <c r="H15" s="8" t="s">
@@ -3905,62 +3918,62 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20">
+      <c r="A16" s="19">
         <v>4</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="30" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="24"/>
-      <c r="H17" s="22"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="21"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
@@ -3981,7 +3994,7 @@
       <c r="F21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="13" t="s">
         <v>9</v>
       </c>
       <c r="H21" s="8" t="s">
@@ -3989,100 +4002,100 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="20">
+      <c r="A22" s="19">
         <v>5</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="H22" s="31" t="s">
+      <c r="H22" s="30" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="24"/>
-      <c r="H23" s="22"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="21"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="20">
+      <c r="A24" s="19">
         <v>6</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="44" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G25" s="24"/>
-      <c r="H25" s="46"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="45"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
+      <c r="A28" s="27"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="31.5" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
@@ -4103,7 +4116,7 @@
       <c r="F29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="G29" s="13" t="s">
         <v>9</v>
       </c>
       <c r="H29" s="8" t="s">
@@ -4111,40 +4124,42 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="20">
+      <c r="A30" s="19">
         <v>7</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G30" s="23"/>
-      <c r="H30" s="31" t="s">
+      <c r="G30" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="30" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G31" s="24"/>
-      <c r="H31" s="22"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="54">
@@ -4236,54 +4251,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="40"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="39"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="40"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="39"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="40"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="42"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="41"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -4314,394 +4329,408 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="31" t="s">
+      <c r="G6" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="H6" s="30" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="22"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="21"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="16"/>
+      <c r="G8" s="15"/>
       <c r="H8" s="9"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="16"/>
       <c r="H9" s="10"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20">
+      <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="38"/>
+      <c r="G10" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="H10" s="37"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="39"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="38"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="41"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="40"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="41"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="40"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20">
+      <c r="A14" s="19">
         <v>4</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="31"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="30"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="17"/>
-      <c r="H15" s="22"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="21"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20">
+      <c r="A16" s="19">
         <v>5</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="16"/>
+      <c r="G16" s="15" t="s">
+        <v>151</v>
+      </c>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="17"/>
+      <c r="G17" s="16"/>
       <c r="H17" s="10"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20">
+      <c r="A18" s="19">
         <v>6</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="38"/>
+      <c r="G18" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="H18" s="37"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="39"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="38"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="41"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="40"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="41"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="40"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20">
+      <c r="A22" s="19">
         <v>7</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="31"/>
+      <c r="G22" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="30"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="17"/>
-      <c r="H23" s="22"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="21"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20">
+      <c r="A24" s="19">
         <v>8</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="16"/>
+      <c r="G24" s="15" t="s">
+        <v>151</v>
+      </c>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="17"/>
+      <c r="G25" s="16"/>
       <c r="H25" s="10"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20">
+      <c r="A26" s="19">
         <v>9</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="38"/>
+      <c r="G26" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" s="37"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G27" s="17"/>
-      <c r="H27" s="39"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="38"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A67B723-727F-48D7-A0FF-1F7822D825FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310D713E-002A-429C-9E0F-BD8F7BA70286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="151">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -502,10 +502,7 @@
     <t>Dalam Keadaan Baik Dan Tidak Digunakan</t>
   </si>
   <si>
-    <t>Rosak Dan Perlu Selenggara</t>
-  </si>
-  <si>
-    <t>Perlu Selenggara Dan Tidak Digunakan</t>
+    <t>Rosak Dan Perlu Selenggara Serta Tidak Digunakan</t>
   </si>
 </sst>
 </file>
@@ -4142,7 +4139,7 @@
       <c r="F30" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="15" t="s">
         <v>150</v>
       </c>
       <c r="H30" s="30" t="s">
@@ -4158,7 +4155,7 @@
       <c r="F31" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G31" s="23"/>
+      <c r="G31" s="16"/>
       <c r="H31" s="21"/>
     </row>
   </sheetData>
@@ -4348,7 +4345,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H6" s="30" t="s">
         <v>28</v>
@@ -4424,7 +4421,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H10" s="37"/>
       <c r="K10" s="2"/>
@@ -4528,7 +4525,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H16" s="9"/>
       <c r="K16" s="2"/>
@@ -4568,7 +4565,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H18" s="37"/>
       <c r="K18" s="2"/>
@@ -4634,7 +4631,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H22" s="30"/>
       <c r="K22" s="2"/>
@@ -4674,7 +4671,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H24" s="9"/>
       <c r="K24" s="2"/>
@@ -4714,7 +4711,7 @@
         <v>15</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H26" s="37"/>
       <c r="K26" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310D713E-002A-429C-9E0F-BD8F7BA70286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC361A3-9EA1-4357-ACEA-B819E587E74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="151">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -4382,7 +4382,9 @@
       <c r="F8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="15"/>
+      <c r="G8" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="H8" s="9"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -4486,7 +4488,9 @@
       <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="15"/>
+      <c r="G14" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="H14" s="30"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC361A3-9EA1-4357-ACEA-B819E587E74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92104E7-8AAA-48BB-B742-C4B1D31B3FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="151">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -1331,7 +1331,9 @@
       <c r="G10" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="30"/>
+      <c r="H10" s="30" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="24"/>
@@ -1831,9 +1833,10 @@
     <hyperlink ref="F7" r:id="rId1" xr:uid="{08DF4C9A-9F75-4524-A39E-D32455244FE2}"/>
     <hyperlink ref="H6" r:id="rId2" xr:uid="{0E376E79-FCE9-48B0-8EAF-4D83CAA38CDB}"/>
     <hyperlink ref="H8" r:id="rId3" xr:uid="{155D159D-7B91-4625-A34E-FB6AA605219D}"/>
+    <hyperlink ref="H10" r:id="rId4" xr:uid="{AF01EDA0-C19B-4C71-8D17-2F2D05EEA4AB}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId4"/>
+  <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId5"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="19" max="7" man="1"/>
   </rowBreaks>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92104E7-8AAA-48BB-B742-C4B1D31B3FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4363EE83-2BA2-4227-8482-E56322709149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="156">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -503,6 +503,21 @@
   </si>
   <si>
     <t>Rosak Dan Perlu Selenggara Serta Tidak Digunakan</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1i_m_CoWXqCTQN61NouEoFNoQ8Qgd45O6/view?usp=sharing,https://drive.google.com/file/d/1Lg9CN250FkG1WBFYopwZblYtUO1rMxUN/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LhMg0aAfXGXr2IDy9B4a1_UDmswSGQGq/view?usp=sharing,https://drive.google.com/file/d/146TJNJu5eiW4i6pbXnYdygEv8imHfEb6/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vqhj5Paqk1NXyGfYneaYM0J_prFOxdta/view?usp=sharing,https://drive.google.com/file/d/1AkRQqdkMOvYudE11K9rValJUxH-2RD_D/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Kg6-4DzoWCrqI7BCPpqDn3y9pNNn7Teb/view?usp=sharing,https://drive.google.com/file/d/1DAR4pvN2KHQpALEs9h9jULyw8GuxXsIi/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mY5uIuxn4HKKSmu0kbVIg2ZLS9BOCOeE/view?usp=sharing,https://drive.google.com/file/d/17bVIZH9mjHJ7trQ0UvIddvEHm2x4Xee-/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -687,7 +702,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -778,12 +793,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1332,7 +1341,7 @@
         <v>130</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1369,7 +1378,9 @@
       <c r="G12" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="30"/>
+      <c r="H12" s="30" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="20"/>
@@ -1405,7 +1416,9 @@
       <c r="G14" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="30"/>
+      <c r="H14" s="30" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="20"/>
@@ -1441,7 +1454,9 @@
       <c r="G16" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="33"/>
+      <c r="H16" s="30" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="24"/>
@@ -1453,7 +1468,7 @@
         <v>23</v>
       </c>
       <c r="G17" s="16"/>
-      <c r="H17" s="34"/>
+      <c r="H17" s="21"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="19">
@@ -1477,7 +1492,9 @@
       <c r="G18" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="H18" s="37"/>
+      <c r="H18" s="42" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="20"/>
@@ -1489,7 +1506,7 @@
         <v>23</v>
       </c>
       <c r="G19" s="21"/>
-      <c r="H19" s="38"/>
+      <c r="H19" s="43"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="19"/>
@@ -1499,7 +1516,7 @@
       <c r="E20" s="15"/>
       <c r="F20" s="7"/>
       <c r="G20" s="15"/>
-      <c r="H20" s="35"/>
+      <c r="H20" s="33"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="20"/>
@@ -1509,7 +1526,7 @@
       <c r="E21" s="16"/>
       <c r="F21" s="5"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="36"/>
+      <c r="H21" s="34"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="19"/>
@@ -1833,10 +1850,14 @@
     <hyperlink ref="F7" r:id="rId1" xr:uid="{08DF4C9A-9F75-4524-A39E-D32455244FE2}"/>
     <hyperlink ref="H6" r:id="rId2" xr:uid="{0E376E79-FCE9-48B0-8EAF-4D83CAA38CDB}"/>
     <hyperlink ref="H8" r:id="rId3" xr:uid="{155D159D-7B91-4625-A34E-FB6AA605219D}"/>
-    <hyperlink ref="H10" r:id="rId4" xr:uid="{AF01EDA0-C19B-4C71-8D17-2F2D05EEA4AB}"/>
+    <hyperlink ref="H10" r:id="rId4" xr:uid="{FEBF1FD0-A6E2-4666-B8F3-D762DE7F8A31}"/>
+    <hyperlink ref="H12" r:id="rId5" xr:uid="{C328C4B4-80E8-4D90-BFB3-B806FC32ACDB}"/>
+    <hyperlink ref="H14" r:id="rId6" xr:uid="{13FAADE7-6BCB-4433-9F8F-3B9D4228FC42}"/>
+    <hyperlink ref="H16" r:id="rId7" xr:uid="{AAA07EE0-99DE-4D2F-9EE3-3D0012E8A238}"/>
+    <hyperlink ref="H18" r:id="rId8" xr:uid="{BC00B7D9-61CE-4F8B-8F68-4BFC1EBAA6EE}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId5"/>
+  <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId9"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="19" max="7" man="1"/>
   </rowBreaks>
@@ -1870,7 +1891,7 @@
       <c r="E1" s="25"/>
       <c r="F1" s="25"/>
       <c r="G1" s="25"/>
-      <c r="H1" s="39"/>
+      <c r="H1" s="37"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
@@ -1882,7 +1903,7 @@
       <c r="E2" s="25"/>
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
-      <c r="H2" s="39"/>
+      <c r="H2" s="37"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
@@ -1896,7 +1917,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
       <c r="G3" s="26"/>
-      <c r="H3" s="40"/>
+      <c r="H3" s="38"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
@@ -1908,7 +1929,7 @@
       <c r="E4" s="27"/>
       <c r="F4" s="27"/>
       <c r="G4" s="27"/>
-      <c r="H4" s="41"/>
+      <c r="H4" s="39"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -1960,7 +1981,7 @@
       <c r="G6" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="33" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1974,7 +1995,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="16"/>
-      <c r="H7" s="36"/>
+      <c r="H7" s="34"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
@@ -2150,7 +2171,7 @@
       <c r="G16" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="40" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2164,7 +2185,7 @@
         <v>14</v>
       </c>
       <c r="G17" s="16"/>
-      <c r="H17" s="43"/>
+      <c r="H17" s="41"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="26" t="s">
@@ -2176,7 +2197,7 @@
       <c r="E18" s="26"/>
       <c r="F18" s="26"/>
       <c r="G18" s="26"/>
-      <c r="H18" s="40"/>
+      <c r="H18" s="38"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="26"/>
@@ -2186,7 +2207,7 @@
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
-      <c r="H19" s="40"/>
+      <c r="H19" s="38"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19">
@@ -2210,7 +2231,7 @@
       <c r="G20" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H20" s="35"/>
+      <c r="H20" s="33"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="20"/>
@@ -2222,7 +2243,7 @@
         <v>7</v>
       </c>
       <c r="G21" s="16"/>
-      <c r="H21" s="36"/>
+      <c r="H21" s="34"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
@@ -2384,7 +2405,7 @@
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
-      <c r="H30" s="40"/>
+      <c r="H30" s="38"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="26"/>
@@ -2394,7 +2415,7 @@
       <c r="E31" s="26"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
-      <c r="H31" s="40"/>
+      <c r="H31" s="38"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19">
@@ -2418,7 +2439,7 @@
       <c r="G32" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H32" s="35" t="s">
+      <c r="H32" s="33" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2432,7 +2453,7 @@
         <v>82</v>
       </c>
       <c r="G33" s="16"/>
-      <c r="H33" s="36"/>
+      <c r="H33" s="34"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="19">
@@ -3816,7 +3837,7 @@
       <c r="G8" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="42" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3830,7 +3851,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="23"/>
-      <c r="H9" s="45"/>
+      <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
@@ -4061,7 +4082,7 @@
       <c r="G24" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="42" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4075,7 +4096,7 @@
         <v>137</v>
       </c>
       <c r="G25" s="23"/>
-      <c r="H25" s="45"/>
+      <c r="H25" s="43"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="26" t="s">
@@ -4260,7 +4281,7 @@
       <c r="E1" s="25"/>
       <c r="F1" s="25"/>
       <c r="G1" s="25"/>
-      <c r="H1" s="39"/>
+      <c r="H1" s="37"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
@@ -4272,7 +4293,7 @@
       <c r="E2" s="25"/>
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
-      <c r="H2" s="39"/>
+      <c r="H2" s="37"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
@@ -4286,7 +4307,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
       <c r="G3" s="26"/>
-      <c r="H3" s="40"/>
+      <c r="H3" s="38"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
@@ -4298,7 +4319,7 @@
       <c r="E4" s="27"/>
       <c r="F4" s="27"/>
       <c r="G4" s="27"/>
-      <c r="H4" s="41"/>
+      <c r="H4" s="39"/>
       <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
@@ -4428,7 +4449,7 @@
       <c r="G10" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="H10" s="37"/>
+      <c r="H10" s="35"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
@@ -4442,7 +4463,7 @@
         <v>14</v>
       </c>
       <c r="G11" s="16"/>
-      <c r="H11" s="38"/>
+      <c r="H11" s="36"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
@@ -4456,7 +4477,7 @@
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
-      <c r="H12" s="40"/>
+      <c r="H12" s="38"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
@@ -4468,7 +4489,7 @@
       <c r="E13" s="26"/>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
-      <c r="H13" s="40"/>
+      <c r="H13" s="38"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
@@ -4574,7 +4595,7 @@
       <c r="G18" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="H18" s="37"/>
+      <c r="H18" s="35"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
@@ -4588,7 +4609,7 @@
         <v>14</v>
       </c>
       <c r="G19" s="16"/>
-      <c r="H19" s="38"/>
+      <c r="H19" s="36"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
@@ -4602,7 +4623,7 @@
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
-      <c r="H20" s="40"/>
+      <c r="H20" s="38"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
@@ -4614,7 +4635,7 @@
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
-      <c r="H21" s="40"/>
+      <c r="H21" s="38"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
@@ -4720,7 +4741,7 @@
       <c r="G26" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="H26" s="37"/>
+      <c r="H26" s="35"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
@@ -4734,7 +4755,7 @@
         <v>14</v>
       </c>
       <c r="G27" s="16"/>
-      <c r="H27" s="38"/>
+      <c r="H27" s="36"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamadizwan\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4363EE83-2BA2-4227-8482-E56322709149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C5EE44-BCD2-4AFA-930F-B14CF764CE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99D4D08D-56BC-422F-8C0F-7E726B28D309}"/>
   </bookViews>
   <sheets>
     <sheet name="Taman Eko Rimba" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="160">
   <si>
     <t>Senarai Aset Bangunan Di Bawah Selian Jabatan Perhutanan Negeri Sembilan</t>
   </si>
@@ -518,6 +518,18 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1mY5uIuxn4HKKSmu0kbVIg2ZLS9BOCOeE/view?usp=sharing,https://drive.google.com/file/d/17bVIZH9mjHJ7trQ0UvIddvEHm2x4Xee-/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17fGPWafOhaxEpBx8LsinVwbGtLvFVxxJ/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iUvJlQr3ByK2gkm8Z3Nj-CILM3PSh8mg/view?usp=sharing,https://drive.google.com/file/d/1ESFrgstQBowKzF_6jUWGPEFQLLMXZY7J/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/nedPe6jaG2cvtU3a9</t>
+  </si>
+  <si>
+    <t>2°56'33.0"N 102°15'45.4"E</t>
   </si>
 </sst>
 </file>
@@ -702,7 +714,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -728,9 +740,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1157,60 +1166,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1243,506 +1252,506 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>1</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="29" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="21"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <v>2</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="29" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="30"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="24">
+      <c r="A10" s="23">
         <v>3</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="14" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="29" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="21"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="20"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
+      <c r="A12" s="18">
         <v>4</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="14" t="s">
         <v>33</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="29" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="21"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
+      <c r="A14" s="18">
         <v>5